--- a/Relaciones totales libro-patrimonio/LIBRO LOCALIDAD.xlsx
+++ b/Relaciones totales libro-patrimonio/LIBRO LOCALIDAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Antonio\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCAC57A-CCFE-4BA7-BCA3-C29B17C3262F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831E9CD1-4148-4950-83AC-56DCCEFE90EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="539" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="157">
   <si>
     <t xml:space="preserve">Almeria </t>
   </si>
@@ -642,9 +642,6 @@
     <t>Nº municipios descritos por relato</t>
   </si>
   <si>
-    <t>Total de menciones  de una capital de provincia en todos los libros</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bart Kennedy (1861-1930, UK) </t>
   </si>
   <si>
@@ -663,12 +660,6 @@
     <t>Cathedral cities of Spain</t>
   </si>
   <si>
-    <t xml:space="preserve"> Cordoba</t>
-  </si>
-  <si>
-    <t>Malaga</t>
-  </si>
-  <si>
     <t>Ecija</t>
   </si>
   <si>
@@ -684,21 +675,9 @@
     <t xml:space="preserve"> Internet archive</t>
   </si>
   <si>
-    <t xml:space="preserve">La linea de la concepción </t>
-  </si>
-  <si>
     <t>Bobadilla (Antequera)</t>
   </si>
   <si>
-    <t xml:space="preserve">Rio Tinto y  Tharsis </t>
-  </si>
-  <si>
-    <t>marchena</t>
-  </si>
-  <si>
-    <t>mairena</t>
-  </si>
-  <si>
     <t>Collins, William Wiehe (1837, 1920, UK)</t>
   </si>
   <si>
@@ -708,18 +687,9 @@
     <t>Heroic  Spain</t>
   </si>
   <si>
-    <t>Sanlucar de barrameda</t>
-  </si>
-  <si>
     <t>Santiponce</t>
   </si>
   <si>
-    <t>baza</t>
-  </si>
-  <si>
-    <t>Puerto de Santa María</t>
-  </si>
-  <si>
     <t>Bates, Katharine Lee (1859-1929, USA)</t>
   </si>
   <si>
@@ -729,17 +699,140 @@
     <t>Elizabeth Boyle O`Reilly (1874-1922, USA)</t>
   </si>
   <si>
-    <t>A   la comunidad</t>
-  </si>
-  <si>
-    <t>Jerez (+sherry)</t>
+    <t>Rota</t>
+  </si>
+  <si>
+    <t>Tolox</t>
+  </si>
+  <si>
+    <t>Osuna</t>
+  </si>
+  <si>
+    <t>San roque</t>
+  </si>
+  <si>
+    <t>Comunidad autónoma</t>
+  </si>
+  <si>
+    <t>Andalucía y Andalusia</t>
+  </si>
+  <si>
+    <t>Sevilla y seville</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cordoba, cordova y córdoba</t>
+  </si>
+  <si>
+    <t>Cadiz y cádiz</t>
+  </si>
+  <si>
+    <t>Almeria y Almería</t>
+  </si>
+  <si>
+    <t>Malaga y Málaga</t>
+  </si>
+  <si>
+    <t>Jaen y Jaén</t>
+  </si>
+  <si>
+    <t>Loja</t>
+  </si>
+  <si>
+    <t>Marchena</t>
+  </si>
+  <si>
+    <t>Mairena</t>
+  </si>
+  <si>
+    <t>Mijas</t>
+  </si>
+  <si>
+    <t>Arriate</t>
+  </si>
+  <si>
+    <t>Total menciones a comunidad</t>
+  </si>
+  <si>
+    <t>Marbella</t>
+  </si>
+  <si>
+    <t>Almñecar</t>
+  </si>
+  <si>
+    <t>Lebrija</t>
+  </si>
+  <si>
+    <t>Adra</t>
+  </si>
+  <si>
+    <t>Barbate</t>
+  </si>
+  <si>
+    <t>Motril</t>
+  </si>
+  <si>
+    <t>Martos</t>
+  </si>
+  <si>
+    <t>Morón</t>
+  </si>
+  <si>
+    <t>Sanlucar</t>
+  </si>
+  <si>
+    <t>San Fernando</t>
+  </si>
+  <si>
+    <t>Lucena</t>
+  </si>
+  <si>
+    <t>Andújar</t>
+  </si>
+  <si>
+    <t>Moguer</t>
+  </si>
+  <si>
+    <t>MUNICIPIOS DE PROVINCIA (NO CAPITALES)</t>
+  </si>
+  <si>
+    <t>Baza</t>
+  </si>
+  <si>
+    <t>Bailén</t>
+  </si>
+  <si>
+    <t>La Carolina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palos </t>
+  </si>
+  <si>
+    <t>Montilla</t>
+  </si>
+  <si>
+    <t>Jerez/sherry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rio Tinto/Tharsis </t>
+  </si>
+  <si>
+    <t>Alcalá Guadaira</t>
+  </si>
+  <si>
+    <t>Puerto Santa María</t>
+  </si>
+  <si>
+    <t>Total de menciones  de una capital de provincia en todos los libros (1670 menciones)</t>
+  </si>
+  <si>
+    <t>Total menciones a municpios no capitales (487 menciones)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -854,29 +947,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="8" tint="0.59999389629810485"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="8" tint="0.59999389629810485"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -909,7 +981,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -996,12 +1068,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1019,7 +1085,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1054,37 +1120,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1162,15 +1197,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color indexed="64"/>
       </left>
@@ -1186,40 +1212,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -1261,21 +1257,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color indexed="64"/>
       </left>
@@ -1284,30 +1265,6 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="slantDashDot">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1325,12 +1282,75 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1414,43 +1434,244 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1477,297 +1698,99 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2180,1375 +2203,2146 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN22"/>
+  <dimension ref="A1:BG24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="77.5546875" style="26" customWidth="1"/>
-    <col min="2" max="2" width="53.109375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="23.5546875" style="7" customWidth="1"/>
-    <col min="5" max="5" width="28.109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" style="7" customWidth="1"/>
-    <col min="7" max="7" width="14" style="7" customWidth="1"/>
-    <col min="8" max="8" width="17.88671875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="17.5546875" style="7" customWidth="1"/>
-    <col min="10" max="10" width="16.21875" style="7" customWidth="1"/>
-    <col min="11" max="11" width="14" style="7" customWidth="1"/>
-    <col min="12" max="12" width="16" style="7" customWidth="1"/>
-    <col min="13" max="13" width="16.33203125" style="7" customWidth="1"/>
-    <col min="14" max="14" width="20.6640625" style="7" customWidth="1"/>
-    <col min="15" max="15" width="17.21875" style="7" customWidth="1"/>
-    <col min="16" max="16" width="17.109375" style="7" customWidth="1"/>
-    <col min="17" max="17" width="15.33203125" style="7" customWidth="1"/>
-    <col min="18" max="18" width="15.5546875" style="7" customWidth="1"/>
-    <col min="19" max="19" width="21.109375" style="7" customWidth="1"/>
-    <col min="20" max="20" width="21.33203125" style="7" customWidth="1"/>
-    <col min="21" max="21" width="19.5546875" style="7" customWidth="1"/>
-    <col min="22" max="22" width="27.33203125" style="7" customWidth="1"/>
-    <col min="23" max="23" width="26.6640625" style="7" customWidth="1"/>
-    <col min="24" max="24" width="27.33203125" style="7" customWidth="1"/>
-    <col min="25" max="25" width="32.21875" style="7" customWidth="1"/>
-    <col min="26" max="26" width="34" style="7" customWidth="1"/>
-    <col min="27" max="27" width="25.88671875" style="7" customWidth="1"/>
-    <col min="28" max="28" width="22.77734375" style="7" customWidth="1"/>
-    <col min="29" max="29" width="25.21875" style="7" customWidth="1"/>
-    <col min="30" max="30" width="16.109375" style="7" customWidth="1"/>
-    <col min="31" max="31" width="24.44140625" style="7" customWidth="1"/>
-    <col min="32" max="32" width="24" style="7" customWidth="1"/>
-    <col min="33" max="33" width="20.5546875" style="7" customWidth="1"/>
-    <col min="34" max="34" width="17.77734375" style="7" customWidth="1"/>
-    <col min="35" max="35" width="25.5546875" style="7" customWidth="1"/>
-    <col min="36" max="36" width="17.109375" style="7" customWidth="1"/>
-    <col min="37" max="37" width="46.6640625" style="7" customWidth="1"/>
-    <col min="38" max="38" width="33.109375" style="7" customWidth="1"/>
-    <col min="39" max="39" width="23.109375" style="7" customWidth="1"/>
-    <col min="40" max="40" width="21.77734375" style="7" customWidth="1"/>
-    <col min="41" max="41" width="25.21875" style="7" customWidth="1"/>
-    <col min="42" max="42" width="17.77734375" style="7" customWidth="1"/>
-    <col min="43" max="16384" width="8.88671875" style="7"/>
+    <col min="1" max="1" width="66.109375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="44.44140625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="47" style="7" customWidth="1"/>
+    <col min="6" max="12" width="28.77734375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="24.77734375" style="7" customWidth="1"/>
+    <col min="14" max="14" width="16.33203125" style="7" customWidth="1"/>
+    <col min="15" max="15" width="12.21875" style="7" customWidth="1"/>
+    <col min="16" max="17" width="19.5546875" style="7" customWidth="1"/>
+    <col min="18" max="18" width="29.109375" style="7" customWidth="1"/>
+    <col min="19" max="20" width="19.5546875" style="7" customWidth="1"/>
+    <col min="21" max="21" width="22" style="7" customWidth="1"/>
+    <col min="22" max="22" width="12.6640625" style="7" customWidth="1"/>
+    <col min="23" max="23" width="14.6640625" style="7" customWidth="1"/>
+    <col min="24" max="24" width="11.88671875" style="7" customWidth="1"/>
+    <col min="25" max="25" width="22.44140625" style="7" customWidth="1"/>
+    <col min="26" max="27" width="16.88671875" style="7" customWidth="1"/>
+    <col min="28" max="28" width="21.109375" style="7" customWidth="1"/>
+    <col min="29" max="29" width="11.5546875" style="7" customWidth="1"/>
+    <col min="30" max="30" width="9.6640625" style="7" customWidth="1"/>
+    <col min="31" max="31" width="13.6640625" style="7" customWidth="1"/>
+    <col min="32" max="32" width="24.88671875" style="7" customWidth="1"/>
+    <col min="33" max="34" width="11.21875" style="7" customWidth="1"/>
+    <col min="35" max="35" width="13.33203125" style="7" customWidth="1"/>
+    <col min="36" max="36" width="16.109375" style="7" customWidth="1"/>
+    <col min="37" max="37" width="10" style="7" customWidth="1"/>
+    <col min="38" max="38" width="16.88671875" style="7" customWidth="1"/>
+    <col min="39" max="39" width="12.21875" style="7" customWidth="1"/>
+    <col min="40" max="40" width="9.88671875" style="7" customWidth="1"/>
+    <col min="41" max="44" width="14.88671875" style="7" customWidth="1"/>
+    <col min="45" max="45" width="11.6640625" style="7" customWidth="1"/>
+    <col min="46" max="46" width="11.109375" style="7" customWidth="1"/>
+    <col min="47" max="47" width="11.88671875" style="7" customWidth="1"/>
+    <col min="48" max="48" width="13.77734375" style="7" customWidth="1"/>
+    <col min="49" max="49" width="12.109375" style="7" customWidth="1"/>
+    <col min="50" max="50" width="11.77734375" style="7" customWidth="1"/>
+    <col min="51" max="53" width="8.88671875" style="7"/>
+    <col min="54" max="54" width="14.6640625" style="7" customWidth="1"/>
+    <col min="55" max="56" width="8.88671875" style="7"/>
+    <col min="57" max="57" width="12.6640625" style="7" customWidth="1"/>
+    <col min="58" max="58" width="8.88671875" style="7"/>
+    <col min="59" max="59" width="14.21875" style="7" customWidth="1"/>
+    <col min="60" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="25" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+    <row r="1" spans="1:59" s="25" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="89" t="s">
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="56" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1" s="129" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
+      <c r="M1" s="130"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="128" t="s">
+        <v>145</v>
+      </c>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
+      <c r="X1" s="128"/>
+      <c r="Y1" s="128"/>
+      <c r="Z1" s="128"/>
+      <c r="AA1" s="128"/>
+      <c r="AB1" s="128"/>
+      <c r="AC1" s="128"/>
+      <c r="AD1" s="128"/>
+      <c r="AE1" s="128"/>
+      <c r="AF1" s="128"/>
+      <c r="AG1" s="128"/>
+      <c r="AH1" s="128"/>
+      <c r="AI1" s="128"/>
+      <c r="AJ1" s="128"/>
+      <c r="AK1" s="128"/>
+      <c r="AL1" s="128"/>
+      <c r="AM1" s="128"/>
+      <c r="AN1" s="128"/>
+      <c r="AO1" s="128"/>
+      <c r="AP1" s="128"/>
+      <c r="AQ1" s="128"/>
+      <c r="AR1" s="128"/>
+      <c r="AS1" s="128"/>
+      <c r="AT1" s="128"/>
+      <c r="AU1" s="128"/>
+      <c r="AV1" s="128"/>
+      <c r="AW1" s="128"/>
+      <c r="AX1" s="128"/>
+      <c r="AY1" s="128"/>
+      <c r="AZ1" s="128"/>
+      <c r="BA1" s="128"/>
+      <c r="BB1" s="128"/>
+      <c r="BC1" s="128"/>
+      <c r="BD1" s="128"/>
+      <c r="BE1" s="128"/>
+      <c r="BF1" s="128"/>
+      <c r="BG1" s="128"/>
+    </row>
+    <row r="2" spans="1:59" ht="71.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="89" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="G2" s="59" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="59" t="s">
+        <v>121</v>
+      </c>
+      <c r="I2" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="J2" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2" s="59" t="s">
+        <v>125</v>
+      </c>
+      <c r="L2" s="59" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" s="59" t="s">
+        <v>123</v>
+      </c>
+      <c r="N2" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="O2" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" s="60" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q2" s="60" t="s">
+        <v>110</v>
+      </c>
+      <c r="R2" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="S2" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="T2" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="U2" s="60" t="s">
+        <v>152</v>
+      </c>
+      <c r="V2" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="W2" s="60" t="s">
+        <v>127</v>
+      </c>
+      <c r="X2" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y2" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z2" s="118" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA2" s="60" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB2" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="AC2" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD2" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE2" s="60" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF2" s="60" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG2" s="60" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH2" s="60" t="s">
+        <v>137</v>
+      </c>
+      <c r="AI2" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="AJ2" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK2" s="60" t="s">
+        <v>146</v>
+      </c>
+      <c r="AL2" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM2" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN2" s="60" t="s">
+        <v>133</v>
+      </c>
+      <c r="AO2" s="60" t="s">
+        <v>134</v>
+      </c>
+      <c r="AP2" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="AQ2" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="AR2" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS2" s="60" t="s">
+        <v>130</v>
+      </c>
+      <c r="AT2" s="60" t="s">
+        <v>129</v>
+      </c>
+      <c r="AU2" s="60" t="s">
+        <v>115</v>
+      </c>
+      <c r="AV2" s="60" t="s">
+        <v>116</v>
+      </c>
+      <c r="AW2" s="60" t="s">
+        <v>117</v>
+      </c>
+      <c r="AX2" s="60" t="s">
+        <v>140</v>
+      </c>
+      <c r="AY2" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="AZ2" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="BA2" s="60" t="s">
+        <v>138</v>
+      </c>
+      <c r="BB2" s="60" t="s">
+        <v>141</v>
+      </c>
+      <c r="BC2" s="60" t="s">
+        <v>142</v>
+      </c>
+      <c r="BD2" s="60" t="s">
+        <v>143</v>
+      </c>
+      <c r="BE2" s="60" t="s">
+        <v>144</v>
+      </c>
+      <c r="BF2" s="60" t="s">
+        <v>147</v>
+      </c>
+      <c r="BG2" s="60" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:59" ht="43.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="61" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="63">
+        <v>1900</v>
+      </c>
+      <c r="D3" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="65">
+        <v>26</v>
+      </c>
+      <c r="F3" s="66">
+        <v>64</v>
+      </c>
+      <c r="G3" s="66">
+        <v>48</v>
+      </c>
+      <c r="H3" s="66">
+        <v>14</v>
+      </c>
+      <c r="I3" s="66">
+        <v>21</v>
+      </c>
+      <c r="J3" s="66">
+        <v>2</v>
+      </c>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="67">
+        <v>7</v>
+      </c>
+      <c r="O3" s="67"/>
+      <c r="P3" s="67">
+        <v>6</v>
+      </c>
+      <c r="Q3" s="67">
+        <v>1</v>
+      </c>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67">
+        <v>1</v>
+      </c>
+      <c r="U3" s="67"/>
+      <c r="V3" s="67"/>
+      <c r="W3" s="67"/>
+      <c r="X3" s="67"/>
+      <c r="Y3" s="67"/>
+      <c r="Z3" s="119"/>
+      <c r="AA3" s="67"/>
+      <c r="AB3" s="57"/>
+      <c r="AC3" s="67">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="67"/>
+      <c r="AE3" s="67"/>
+      <c r="AF3" s="67">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="67"/>
+      <c r="AH3" s="57"/>
+      <c r="AI3" s="121"/>
+      <c r="AJ3" s="57"/>
+      <c r="AK3" s="67"/>
+      <c r="AL3" s="57"/>
+      <c r="AM3" s="57"/>
+      <c r="AN3" s="57"/>
+      <c r="AO3" s="57"/>
+      <c r="AP3" s="57"/>
+      <c r="AQ3" s="57"/>
+      <c r="AR3" s="57"/>
+      <c r="AS3" s="57"/>
+      <c r="AT3" s="57"/>
+      <c r="AU3" s="57"/>
+      <c r="AV3" s="57"/>
+      <c r="AW3" s="57"/>
+      <c r="AX3" s="67">
+        <v>1</v>
+      </c>
+      <c r="AY3" s="57"/>
+      <c r="AZ3" s="57"/>
+      <c r="BA3" s="57"/>
+      <c r="BB3" s="57"/>
+      <c r="BC3" s="57"/>
+      <c r="BD3" s="57"/>
+      <c r="BE3" s="57"/>
+      <c r="BF3" s="57"/>
+      <c r="BG3" s="57"/>
+    </row>
+    <row r="4" spans="1:59" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="30">
+        <v>1902</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="52">
+        <v>17</v>
+      </c>
+      <c r="F4" s="42">
+        <v>11</v>
+      </c>
+      <c r="G4" s="42">
+        <v>6</v>
+      </c>
+      <c r="H4" s="42">
+        <v>5</v>
+      </c>
+      <c r="I4" s="42">
+        <v>7</v>
+      </c>
+      <c r="J4" s="42">
+        <v>10</v>
+      </c>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42">
+        <v>1</v>
+      </c>
+      <c r="M4" s="42"/>
+      <c r="N4" s="46">
+        <v>12</v>
+      </c>
+      <c r="O4" s="46">
+        <v>7</v>
+      </c>
+      <c r="P4" s="46">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46">
+        <v>1</v>
+      </c>
+      <c r="S4" s="46">
+        <v>2</v>
+      </c>
+      <c r="T4" s="46"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
+      <c r="Y4" s="46"/>
+      <c r="Z4" s="101"/>
+      <c r="AA4" s="46"/>
+      <c r="AB4" s="46"/>
+      <c r="AC4" s="46"/>
+      <c r="AD4" s="46"/>
+      <c r="AE4" s="46"/>
+      <c r="AF4" s="46"/>
+      <c r="AG4" s="46">
+        <v>2</v>
+      </c>
+      <c r="AH4" s="46"/>
+      <c r="AI4" s="101"/>
+      <c r="AJ4" s="46"/>
+      <c r="AK4" s="46"/>
+      <c r="AL4" s="46">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="46"/>
+      <c r="AN4" s="46"/>
+      <c r="AO4" s="46"/>
+      <c r="AP4" s="46"/>
+      <c r="AQ4" s="46"/>
+      <c r="AR4" s="46"/>
+      <c r="AS4" s="46">
+        <v>1</v>
+      </c>
+      <c r="AT4" s="46">
+        <v>1</v>
+      </c>
+      <c r="AU4" s="46">
+        <v>1</v>
+      </c>
+      <c r="AV4" s="46">
+        <v>1</v>
+      </c>
+      <c r="AW4" s="46">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="46"/>
+      <c r="AY4" s="46"/>
+      <c r="AZ4" s="46"/>
+      <c r="BA4" s="46"/>
+      <c r="BB4" s="46"/>
+      <c r="BC4" s="46"/>
+      <c r="BD4" s="46"/>
+      <c r="BE4" s="46"/>
+      <c r="BF4" s="46"/>
+      <c r="BG4" s="46"/>
+    </row>
+    <row r="5" spans="1:59" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="30">
+        <v>1903</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="52">
+        <v>8</v>
+      </c>
+      <c r="F5" s="42">
+        <v>35</v>
+      </c>
+      <c r="G5" s="42">
+        <v>18</v>
+      </c>
+      <c r="H5" s="42">
+        <v>24</v>
+      </c>
+      <c r="I5" s="42">
+        <v>15</v>
+      </c>
+      <c r="J5" s="42">
+        <v>13</v>
+      </c>
+      <c r="K5" s="42">
+        <v>6</v>
+      </c>
+      <c r="L5" s="42">
         <v>4</v>
       </c>
-      <c r="F1" s="85" t="s">
+      <c r="M5" s="43">
+        <v>4</v>
+      </c>
+      <c r="N5" s="46">
+        <v>4</v>
+      </c>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46">
+        <v>1</v>
+      </c>
+      <c r="R5" s="46"/>
+      <c r="S5" s="46"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46">
+        <v>14</v>
+      </c>
+      <c r="V5" s="46"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="46">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="46">
+        <v>9</v>
+      </c>
+      <c r="Z5" s="101"/>
+      <c r="AA5" s="46"/>
+      <c r="AB5" s="46"/>
+      <c r="AC5" s="46"/>
+      <c r="AD5" s="46">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="46"/>
+      <c r="AF5" s="46"/>
+      <c r="AG5" s="46"/>
+      <c r="AH5" s="46"/>
+      <c r="AI5" s="101"/>
+      <c r="AJ5" s="46"/>
+      <c r="AK5" s="46"/>
+      <c r="AL5" s="46"/>
+      <c r="AM5" s="46"/>
+      <c r="AN5" s="46"/>
+      <c r="AO5" s="46"/>
+      <c r="AP5" s="46"/>
+      <c r="AQ5" s="46"/>
+      <c r="AR5" s="46"/>
+      <c r="AS5" s="46"/>
+      <c r="AT5" s="46"/>
+      <c r="AU5" s="46"/>
+      <c r="AV5" s="46"/>
+      <c r="AW5" s="46"/>
+      <c r="AX5" s="46"/>
+      <c r="AY5" s="46"/>
+      <c r="AZ5" s="46"/>
+      <c r="BA5" s="46"/>
+      <c r="BB5" s="46"/>
+      <c r="BC5" s="46"/>
+      <c r="BD5" s="46"/>
+      <c r="BE5" s="46"/>
+      <c r="BF5" s="46"/>
+      <c r="BG5" s="46"/>
+    </row>
+    <row r="6" spans="1:59" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="68" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="30">
+        <v>1904</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="52">
+        <v>5</v>
+      </c>
+      <c r="F6" s="42">
+        <v>53</v>
+      </c>
+      <c r="G6" s="42">
+        <v>43</v>
+      </c>
+      <c r="H6" s="42">
+        <v>5</v>
+      </c>
+      <c r="I6" s="42">
+        <v>1</v>
+      </c>
+      <c r="J6" s="42">
+        <v>4</v>
+      </c>
+      <c r="K6" s="42">
+        <v>9</v>
+      </c>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="46">
+        <v>8</v>
+      </c>
+      <c r="O6" s="46">
+        <v>4</v>
+      </c>
+      <c r="P6" s="46">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="46"/>
+      <c r="R6" s="46">
+        <v>5</v>
+      </c>
+      <c r="S6" s="46"/>
+      <c r="T6" s="46"/>
+      <c r="U6" s="46"/>
+      <c r="V6" s="46"/>
+      <c r="W6" s="46"/>
+      <c r="X6" s="46"/>
+      <c r="Y6" s="46"/>
+      <c r="Z6" s="101"/>
+      <c r="AA6" s="46"/>
+      <c r="AB6" s="46"/>
+      <c r="AC6" s="46"/>
+      <c r="AD6" s="47"/>
+      <c r="AE6" s="46"/>
+      <c r="AF6" s="46"/>
+      <c r="AG6" s="46"/>
+      <c r="AH6" s="46"/>
+      <c r="AI6" s="101"/>
+      <c r="AJ6" s="46"/>
+      <c r="AK6" s="46"/>
+      <c r="AL6" s="46"/>
+      <c r="AM6" s="46"/>
+      <c r="AN6" s="46"/>
+      <c r="AO6" s="46"/>
+      <c r="AP6" s="46"/>
+      <c r="AQ6" s="46"/>
+      <c r="AR6" s="46"/>
+      <c r="AS6" s="46"/>
+      <c r="AT6" s="46"/>
+      <c r="AU6" s="46"/>
+      <c r="AV6" s="46"/>
+      <c r="AW6" s="46"/>
+      <c r="AX6" s="46"/>
+      <c r="AY6" s="46"/>
+      <c r="AZ6" s="46"/>
+      <c r="BA6" s="46"/>
+      <c r="BB6" s="46"/>
+      <c r="BC6" s="46"/>
+      <c r="BD6" s="46"/>
+      <c r="BE6" s="46"/>
+      <c r="BF6" s="46"/>
+      <c r="BG6" s="46"/>
+    </row>
+    <row r="7" spans="1:59" ht="46.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="69" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="71">
+        <v>1905</v>
+      </c>
+      <c r="D7" s="72" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="73">
+        <v>39</v>
+      </c>
+      <c r="F7" s="74">
+        <v>72</v>
+      </c>
+      <c r="G7" s="74">
+        <v>17</v>
+      </c>
+      <c r="H7" s="74">
+        <v>22</v>
+      </c>
+      <c r="I7" s="74">
+        <v>13</v>
+      </c>
+      <c r="J7" s="74">
+        <v>9</v>
+      </c>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="75">
+        <v>16</v>
+      </c>
+      <c r="O7" s="75">
+        <v>1</v>
+      </c>
+      <c r="P7" s="75">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="75"/>
+      <c r="R7" s="75"/>
+      <c r="S7" s="75"/>
+      <c r="T7" s="75">
+        <v>13</v>
+      </c>
+      <c r="U7" s="75"/>
+      <c r="V7" s="75"/>
+      <c r="W7" s="75">
+        <v>10</v>
+      </c>
+      <c r="X7" s="75"/>
+      <c r="Y7" s="75"/>
+      <c r="Z7" s="120">
+        <v>4</v>
+      </c>
+      <c r="AA7" s="75"/>
+      <c r="AB7" s="75"/>
+      <c r="AC7" s="75"/>
+      <c r="AD7" s="75"/>
+      <c r="AE7" s="75">
+        <v>4</v>
+      </c>
+      <c r="AF7" s="75"/>
+      <c r="AG7" s="75"/>
+      <c r="AH7" s="75"/>
+      <c r="AI7" s="120"/>
+      <c r="AJ7" s="75"/>
+      <c r="AK7" s="75"/>
+      <c r="AL7" s="75"/>
+      <c r="AM7" s="75"/>
+      <c r="AN7" s="75"/>
+      <c r="AO7" s="75"/>
+      <c r="AP7" s="75"/>
+      <c r="AQ7" s="75"/>
+      <c r="AR7" s="75"/>
+      <c r="AS7" s="75"/>
+      <c r="AT7" s="75"/>
+      <c r="AU7" s="75"/>
+      <c r="AV7" s="75"/>
+      <c r="AW7" s="75"/>
+      <c r="AX7" s="75"/>
+      <c r="AY7" s="75"/>
+      <c r="AZ7" s="75"/>
+      <c r="BA7" s="75"/>
+      <c r="BB7" s="75"/>
+      <c r="BC7" s="75"/>
+      <c r="BD7" s="75"/>
+      <c r="BE7" s="75"/>
+      <c r="BF7" s="75"/>
+      <c r="BG7" s="75"/>
+    </row>
+    <row r="8" spans="1:59" ht="43.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="77" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="78">
+        <v>1908</v>
+      </c>
+      <c r="D8" s="79" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="80">
+        <v>27</v>
+      </c>
+      <c r="F8" s="81">
+        <v>92</v>
+      </c>
+      <c r="G8" s="81">
+        <v>90</v>
+      </c>
+      <c r="H8" s="81">
+        <v>42</v>
+      </c>
+      <c r="I8" s="81">
+        <v>25</v>
+      </c>
+      <c r="J8" s="81">
+        <v>12</v>
+      </c>
+      <c r="K8" s="81">
+        <v>2</v>
+      </c>
+      <c r="L8" s="81">
+        <v>1</v>
+      </c>
+      <c r="M8" s="81">
+        <v>5</v>
+      </c>
+      <c r="N8" s="57">
+        <v>9</v>
+      </c>
+      <c r="O8" s="57">
+        <v>5</v>
+      </c>
+      <c r="P8" s="82">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="57">
+        <v>6</v>
+      </c>
+      <c r="R8" s="57">
+        <v>1</v>
+      </c>
+      <c r="S8" s="57">
+        <v>2</v>
+      </c>
+      <c r="T8" s="57"/>
+      <c r="U8" s="57"/>
+      <c r="V8" s="57"/>
+      <c r="W8" s="57"/>
+      <c r="X8" s="57"/>
+      <c r="Y8" s="57"/>
+      <c r="Z8" s="121">
+        <v>2</v>
+      </c>
+      <c r="AA8" s="57">
+        <v>2</v>
+      </c>
+      <c r="AB8" s="47">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="57">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="57">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="57"/>
+      <c r="AF8" s="57">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="47"/>
+      <c r="AH8" s="47">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="47"/>
+      <c r="AJ8" s="47">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="57">
+        <v>2</v>
+      </c>
+      <c r="AL8" s="47">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="47">
+        <v>2</v>
+      </c>
+      <c r="AN8" s="47">
+        <v>2</v>
+      </c>
+      <c r="AO8" s="47">
+        <v>2</v>
+      </c>
+      <c r="AP8" s="47">
+        <v>1</v>
+      </c>
+      <c r="AQ8" s="47"/>
+      <c r="AR8" s="47"/>
+      <c r="AS8" s="47"/>
+      <c r="AT8" s="47"/>
+      <c r="AU8" s="47"/>
+      <c r="AV8" s="47"/>
+      <c r="AW8" s="47"/>
+      <c r="AX8" s="57"/>
+      <c r="AY8" s="47">
+        <v>1</v>
+      </c>
+      <c r="AZ8" s="47">
+        <v>1</v>
+      </c>
+      <c r="BA8" s="47">
+        <v>1</v>
+      </c>
+      <c r="BB8" s="47"/>
+      <c r="BC8" s="47"/>
+      <c r="BD8" s="47"/>
+      <c r="BE8" s="47"/>
+      <c r="BF8" s="47"/>
+      <c r="BG8" s="47"/>
+    </row>
+    <row r="9" spans="1:59" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="83" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="37">
+        <v>1908</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="54">
+        <v>16</v>
+      </c>
+      <c r="F9" s="45">
+        <v>62</v>
+      </c>
+      <c r="G9" s="45">
+        <v>16</v>
+      </c>
+      <c r="H9" s="45">
+        <v>55</v>
+      </c>
+      <c r="I9" s="45">
+        <v>2</v>
+      </c>
+      <c r="J9" s="45">
+        <v>1</v>
+      </c>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45">
+        <v>4</v>
+      </c>
+      <c r="M9" s="45"/>
+      <c r="N9" s="49">
+        <v>33</v>
+      </c>
+      <c r="O9" s="49">
+        <v>14</v>
+      </c>
+      <c r="P9" s="50"/>
+      <c r="Q9" s="49">
+        <v>10</v>
+      </c>
+      <c r="R9" s="49"/>
+      <c r="S9" s="49">
+        <v>1</v>
+      </c>
+      <c r="T9" s="49"/>
+      <c r="U9" s="49"/>
+      <c r="V9" s="49"/>
+      <c r="W9" s="49"/>
+      <c r="X9" s="49"/>
+      <c r="Y9" s="49"/>
+      <c r="Z9" s="122"/>
+      <c r="AA9" s="49"/>
+      <c r="AB9" s="46"/>
+      <c r="AC9" s="49"/>
+      <c r="AD9" s="49"/>
+      <c r="AE9" s="49"/>
+      <c r="AF9" s="49"/>
+      <c r="AG9" s="46"/>
+      <c r="AH9" s="46"/>
+      <c r="AI9" s="46"/>
+      <c r="AJ9" s="46"/>
+      <c r="AK9" s="49"/>
+      <c r="AL9" s="46"/>
+      <c r="AM9" s="46"/>
+      <c r="AN9" s="46"/>
+      <c r="AO9" s="46"/>
+      <c r="AP9" s="46"/>
+      <c r="AQ9" s="46"/>
+      <c r="AR9" s="46"/>
+      <c r="AS9" s="46"/>
+      <c r="AT9" s="46"/>
+      <c r="AU9" s="46"/>
+      <c r="AV9" s="46"/>
+      <c r="AW9" s="46"/>
+      <c r="AX9" s="49"/>
+      <c r="AY9" s="46"/>
+      <c r="AZ9" s="46"/>
+      <c r="BA9" s="46"/>
+      <c r="BB9" s="46"/>
+      <c r="BC9" s="46"/>
+      <c r="BD9" s="46"/>
+      <c r="BE9" s="46"/>
+      <c r="BF9" s="46"/>
+      <c r="BG9" s="46"/>
+    </row>
+    <row r="10" spans="1:59" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="32">
+        <v>1909</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="52">
+        <v>1</v>
+      </c>
+      <c r="F10" s="42">
+        <v>34</v>
+      </c>
+      <c r="G10" s="42">
+        <v>17</v>
+      </c>
+      <c r="H10" s="42">
+        <v>18</v>
+      </c>
+      <c r="I10" s="42">
+        <v>14</v>
+      </c>
+      <c r="J10" s="42">
+        <v>6</v>
+      </c>
+      <c r="K10" s="42">
+        <v>1</v>
+      </c>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="46"/>
+      <c r="O10" s="46">
+        <v>0</v>
+      </c>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="46">
+        <v>3</v>
+      </c>
+      <c r="R10" s="46"/>
+      <c r="S10" s="46">
+        <v>1</v>
+      </c>
+      <c r="T10" s="46"/>
+      <c r="U10" s="46"/>
+      <c r="V10" s="46"/>
+      <c r="W10" s="46"/>
+      <c r="X10" s="46"/>
+      <c r="Y10" s="46"/>
+      <c r="Z10" s="101"/>
+      <c r="AA10" s="46"/>
+      <c r="AB10" s="46"/>
+      <c r="AC10" s="46"/>
+      <c r="AD10" s="46">
+        <v>2</v>
+      </c>
+      <c r="AE10" s="46"/>
+      <c r="AF10" s="46"/>
+      <c r="AG10" s="46"/>
+      <c r="AH10" s="46"/>
+      <c r="AI10" s="46"/>
+      <c r="AJ10" s="46">
+        <v>2</v>
+      </c>
+      <c r="AK10" s="46"/>
+      <c r="AL10" s="46"/>
+      <c r="AM10" s="46"/>
+      <c r="AN10" s="46"/>
+      <c r="AO10" s="46"/>
+      <c r="AP10" s="46"/>
+      <c r="AQ10" s="46">
+        <v>1</v>
+      </c>
+      <c r="AR10" s="46"/>
+      <c r="AS10" s="46"/>
+      <c r="AT10" s="46"/>
+      <c r="AU10" s="46"/>
+      <c r="AV10" s="46"/>
+      <c r="AW10" s="46"/>
+      <c r="AX10" s="46"/>
+      <c r="AY10" s="46"/>
+      <c r="AZ10" s="46"/>
+      <c r="BA10" s="46"/>
+      <c r="BB10" s="46">
+        <v>1</v>
+      </c>
+      <c r="BC10" s="46"/>
+      <c r="BD10" s="46"/>
+      <c r="BE10" s="46"/>
+      <c r="BF10" s="46"/>
+      <c r="BG10" s="46"/>
+    </row>
+    <row r="11" spans="1:59" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="84" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="32">
+        <v>1909</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="52">
+        <v>3</v>
+      </c>
+      <c r="F11" s="42">
+        <v>18</v>
+      </c>
+      <c r="G11" s="42">
+        <v>12</v>
+      </c>
+      <c r="H11" s="42">
+        <v>12</v>
+      </c>
+      <c r="I11" s="42">
+        <v>9</v>
+      </c>
+      <c r="J11" s="42">
+        <v>11</v>
+      </c>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="46">
+        <v>1</v>
+      </c>
+      <c r="O11" s="46"/>
+      <c r="P11" s="51"/>
+      <c r="Q11" s="46">
+        <v>1</v>
+      </c>
+      <c r="R11" s="46"/>
+      <c r="S11" s="46"/>
+      <c r="T11" s="46"/>
+      <c r="U11" s="46"/>
+      <c r="V11" s="46"/>
+      <c r="W11" s="46"/>
+      <c r="X11" s="46"/>
+      <c r="Y11" s="46"/>
+      <c r="Z11" s="101"/>
+      <c r="AA11" s="46"/>
+      <c r="AB11" s="46"/>
+      <c r="AC11" s="46"/>
+      <c r="AD11" s="46"/>
+      <c r="AE11" s="46"/>
+      <c r="AF11" s="46"/>
+      <c r="AG11" s="46"/>
+      <c r="AH11" s="46"/>
+      <c r="AI11" s="46"/>
+      <c r="AJ11" s="46"/>
+      <c r="AK11" s="46"/>
+      <c r="AL11" s="46"/>
+      <c r="AM11" s="46"/>
+      <c r="AN11" s="46"/>
+      <c r="AO11" s="46"/>
+      <c r="AP11" s="46"/>
+      <c r="AQ11" s="46"/>
+      <c r="AR11" s="46"/>
+      <c r="AS11" s="46"/>
+      <c r="AT11" s="46"/>
+      <c r="AU11" s="46"/>
+      <c r="AV11" s="46"/>
+      <c r="AW11" s="46"/>
+      <c r="AX11" s="46"/>
+      <c r="AY11" s="46"/>
+      <c r="AZ11" s="46"/>
+      <c r="BA11" s="46"/>
+      <c r="BB11" s="46"/>
+      <c r="BC11" s="46"/>
+      <c r="BD11" s="46"/>
+      <c r="BE11" s="46"/>
+      <c r="BF11" s="46"/>
+      <c r="BG11" s="46"/>
+    </row>
+    <row r="12" spans="1:59" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="30">
+        <v>1910</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="52">
+        <v>13</v>
+      </c>
+      <c r="F12" s="42">
+        <v>12</v>
+      </c>
+      <c r="G12" s="42">
+        <v>3</v>
+      </c>
+      <c r="H12" s="42">
+        <v>6</v>
+      </c>
+      <c r="I12" s="42">
+        <v>4</v>
+      </c>
+      <c r="J12" s="42">
+        <v>2</v>
+      </c>
+      <c r="K12" s="42">
+        <v>5</v>
+      </c>
+      <c r="L12" s="42">
+        <v>1</v>
+      </c>
+      <c r="M12" s="42"/>
+      <c r="N12" s="46">
+        <v>9</v>
+      </c>
+      <c r="O12" s="46"/>
+      <c r="P12" s="51">
+        <v>9</v>
+      </c>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="46">
+        <v>2</v>
+      </c>
+      <c r="U12" s="46"/>
+      <c r="V12" s="46">
+        <v>14</v>
+      </c>
+      <c r="W12" s="46">
+        <v>1</v>
+      </c>
+      <c r="X12" s="46"/>
+      <c r="Y12" s="46"/>
+      <c r="Z12" s="101"/>
+      <c r="AA12" s="46"/>
+      <c r="AB12" s="46">
+        <v>2</v>
+      </c>
+      <c r="AC12" s="46"/>
+      <c r="AD12" s="46"/>
+      <c r="AE12" s="46"/>
+      <c r="AF12" s="46"/>
+      <c r="AG12" s="46">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="46">
+        <v>2</v>
+      </c>
+      <c r="AI12" s="46"/>
+      <c r="AJ12" s="46"/>
+      <c r="AK12" s="46"/>
+      <c r="AL12" s="46"/>
+      <c r="AM12" s="46"/>
+      <c r="AN12" s="46"/>
+      <c r="AO12" s="46"/>
+      <c r="AP12" s="46">
+        <v>1</v>
+      </c>
+      <c r="AQ12" s="46"/>
+      <c r="AR12" s="46">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="46"/>
+      <c r="AT12" s="46"/>
+      <c r="AU12" s="46"/>
+      <c r="AV12" s="46"/>
+      <c r="AW12" s="46"/>
+      <c r="AX12" s="46"/>
+      <c r="AY12" s="46"/>
+      <c r="AZ12" s="46"/>
+      <c r="BA12" s="46"/>
+      <c r="BB12" s="46"/>
+      <c r="BC12" s="46">
+        <v>1</v>
+      </c>
+      <c r="BD12" s="46">
+        <v>1</v>
+      </c>
+      <c r="BE12" s="46">
+        <v>1</v>
+      </c>
+      <c r="BF12" s="46"/>
+      <c r="BG12" s="46"/>
+    </row>
+    <row r="13" spans="1:59" s="34" customFormat="1" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="93" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="95">
+        <v>1910</v>
+      </c>
+      <c r="D13" s="96" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="97">
+        <v>8</v>
+      </c>
+      <c r="F13" s="98">
+        <v>56</v>
+      </c>
+      <c r="G13" s="98">
+        <v>14</v>
+      </c>
+      <c r="H13" s="98">
+        <v>8</v>
+      </c>
+      <c r="I13" s="98">
+        <v>17</v>
+      </c>
+      <c r="J13" s="98"/>
+      <c r="K13" s="98"/>
+      <c r="L13" s="98"/>
+      <c r="M13" s="98"/>
+      <c r="N13" s="99">
+        <v>1</v>
+      </c>
+      <c r="O13" s="99"/>
+      <c r="P13" s="100">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="99">
+        <v>3</v>
+      </c>
+      <c r="R13" s="99">
+        <v>1</v>
+      </c>
+      <c r="S13" s="99"/>
+      <c r="T13" s="99"/>
+      <c r="U13" s="99"/>
+      <c r="V13" s="99"/>
+      <c r="W13" s="99"/>
+      <c r="X13" s="99"/>
+      <c r="Y13" s="99"/>
+      <c r="Z13" s="123">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="99"/>
+      <c r="AB13" s="127"/>
+      <c r="AC13" s="99"/>
+      <c r="AD13" s="99"/>
+      <c r="AE13" s="99"/>
+      <c r="AF13" s="99"/>
+      <c r="AG13" s="127"/>
+      <c r="AH13" s="127"/>
+      <c r="AI13" s="127"/>
+      <c r="AJ13" s="127"/>
+      <c r="AK13" s="99"/>
+      <c r="AL13" s="127"/>
+      <c r="AM13" s="127"/>
+      <c r="AN13" s="127"/>
+      <c r="AO13" s="127"/>
+      <c r="AP13" s="127"/>
+      <c r="AQ13" s="127">
+        <v>1</v>
+      </c>
+      <c r="AR13" s="127"/>
+      <c r="AS13" s="127"/>
+      <c r="AT13" s="127"/>
+      <c r="AU13" s="127"/>
+      <c r="AV13" s="127"/>
+      <c r="AW13" s="127"/>
+      <c r="AX13" s="99"/>
+      <c r="AY13" s="127"/>
+      <c r="AZ13" s="127"/>
+      <c r="BA13" s="127"/>
+      <c r="BB13" s="127"/>
+      <c r="BC13" s="127"/>
+      <c r="BD13" s="127"/>
+      <c r="BE13" s="127"/>
+      <c r="BF13" s="127"/>
+      <c r="BG13" s="127"/>
+    </row>
+    <row r="14" spans="1:59" ht="40.200000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="90" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="91" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="91">
+        <v>1911</v>
+      </c>
+      <c r="D14" s="92" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="53">
+        <v>13</v>
+      </c>
+      <c r="F14" s="44">
+        <v>25</v>
+      </c>
+      <c r="G14" s="44">
+        <v>11</v>
+      </c>
+      <c r="H14" s="44">
+        <v>11</v>
+      </c>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44">
+        <v>2</v>
+      </c>
+      <c r="K14" s="44">
+        <v>9</v>
+      </c>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
+      <c r="N14" s="47">
+        <v>7</v>
+      </c>
+      <c r="O14" s="47">
+        <v>6</v>
+      </c>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="47">
+        <v>2</v>
+      </c>
+      <c r="S14" s="47">
+        <v>1</v>
+      </c>
+      <c r="T14" s="47"/>
+      <c r="U14" s="47"/>
+      <c r="V14" s="47"/>
+      <c r="W14" s="47"/>
+      <c r="X14" s="47"/>
+      <c r="Y14" s="47"/>
+      <c r="Z14" s="124">
+        <v>2</v>
+      </c>
+      <c r="AA14" s="47"/>
+      <c r="AB14" s="57"/>
+      <c r="AC14" s="47"/>
+      <c r="AD14" s="47">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="47"/>
+      <c r="AF14" s="47"/>
+      <c r="AG14" s="57"/>
+      <c r="AH14" s="57"/>
+      <c r="AI14" s="121"/>
+      <c r="AJ14" s="57"/>
+      <c r="AK14" s="47"/>
+      <c r="AL14" s="57"/>
+      <c r="AM14" s="57"/>
+      <c r="AN14" s="57"/>
+      <c r="AO14" s="57"/>
+      <c r="AP14" s="57"/>
+      <c r="AQ14" s="57"/>
+      <c r="AR14" s="57">
+        <v>1</v>
+      </c>
+      <c r="AS14" s="57"/>
+      <c r="AT14" s="57"/>
+      <c r="AU14" s="57"/>
+      <c r="AV14" s="57"/>
+      <c r="AW14" s="57"/>
+      <c r="AX14" s="47"/>
+      <c r="AY14" s="57"/>
+      <c r="AZ14" s="57"/>
+      <c r="BA14" s="57"/>
+      <c r="BB14" s="57"/>
+      <c r="BC14" s="57"/>
+      <c r="BD14" s="57"/>
+      <c r="BE14" s="57"/>
+      <c r="BF14" s="57">
+        <v>1</v>
+      </c>
+      <c r="BG14" s="57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:59" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="83" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="37">
+        <v>1912</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="54">
+        <v>5</v>
+      </c>
+      <c r="F15" s="45">
+        <v>30</v>
+      </c>
+      <c r="G15" s="45">
+        <v>15</v>
+      </c>
+      <c r="H15" s="45">
+        <v>12</v>
+      </c>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45">
+        <v>1</v>
+      </c>
+      <c r="K15" s="45"/>
+      <c r="L15" s="45"/>
+      <c r="M15" s="45"/>
+      <c r="N15" s="49"/>
+      <c r="O15" s="49"/>
+      <c r="P15" s="50"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="49"/>
+      <c r="U15" s="49"/>
+      <c r="V15" s="49"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="49"/>
+      <c r="Y15" s="49"/>
+      <c r="Z15" s="122"/>
+      <c r="AA15" s="49"/>
+      <c r="AB15" s="46"/>
+      <c r="AC15" s="49"/>
+      <c r="AD15" s="49"/>
+      <c r="AE15" s="49"/>
+      <c r="AF15" s="49">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="46"/>
+      <c r="AH15" s="46"/>
+      <c r="AI15" s="101"/>
+      <c r="AJ15" s="46"/>
+      <c r="AK15" s="49"/>
+      <c r="AL15" s="46"/>
+      <c r="AM15" s="46"/>
+      <c r="AN15" s="46"/>
+      <c r="AO15" s="46"/>
+      <c r="AP15" s="46"/>
+      <c r="AQ15" s="46"/>
+      <c r="AR15" s="46"/>
+      <c r="AS15" s="46"/>
+      <c r="AT15" s="46"/>
+      <c r="AU15" s="46"/>
+      <c r="AV15" s="46"/>
+      <c r="AW15" s="46"/>
+      <c r="AX15" s="49"/>
+      <c r="AY15" s="46"/>
+      <c r="AZ15" s="46"/>
+      <c r="BA15" s="46"/>
+      <c r="BB15" s="46"/>
+      <c r="BC15" s="46"/>
+      <c r="BD15" s="46"/>
+      <c r="BE15" s="46"/>
+      <c r="BF15" s="46"/>
+      <c r="BG15" s="46"/>
+    </row>
+    <row r="16" spans="1:59" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="30">
+        <v>1913</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="52">
+        <v>12</v>
+      </c>
+      <c r="F16" s="42">
+        <v>96</v>
+      </c>
+      <c r="G16" s="42">
+        <v>29</v>
+      </c>
+      <c r="H16" s="42">
+        <v>48</v>
+      </c>
+      <c r="I16" s="42">
+        <v>5</v>
+      </c>
+      <c r="J16" s="42">
+        <v>4</v>
+      </c>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="46">
+        <v>26</v>
+      </c>
+      <c r="O16" s="46">
+        <v>19</v>
+      </c>
+      <c r="P16" s="51">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="46">
+        <v>3</v>
+      </c>
+      <c r="R16" s="46">
+        <v>5</v>
+      </c>
+      <c r="S16" s="46">
+        <v>15</v>
+      </c>
+      <c r="T16" s="46"/>
+      <c r="U16" s="46"/>
+      <c r="V16" s="46"/>
+      <c r="W16" s="46"/>
+      <c r="X16" s="46"/>
+      <c r="Y16" s="46"/>
+      <c r="Z16" s="101"/>
+      <c r="AA16" s="46"/>
+      <c r="AB16" s="46"/>
+      <c r="AC16" s="46"/>
+      <c r="AD16" s="46"/>
+      <c r="AE16" s="46"/>
+      <c r="AF16" s="46"/>
+      <c r="AG16" s="46"/>
+      <c r="AH16" s="46"/>
+      <c r="AI16" s="101">
+        <v>3</v>
+      </c>
+      <c r="AJ16" s="46"/>
+      <c r="AK16" s="46"/>
+      <c r="AL16" s="46"/>
+      <c r="AM16" s="46"/>
+      <c r="AN16" s="46"/>
+      <c r="AO16" s="46"/>
+      <c r="AP16" s="46"/>
+      <c r="AQ16" s="46"/>
+      <c r="AR16" s="46"/>
+      <c r="AS16" s="46"/>
+      <c r="AT16" s="46"/>
+      <c r="AU16" s="46"/>
+      <c r="AV16" s="46"/>
+      <c r="AW16" s="46"/>
+      <c r="AX16" s="46"/>
+      <c r="AY16" s="46"/>
+      <c r="AZ16" s="46"/>
+      <c r="BA16" s="46"/>
+      <c r="BB16" s="46"/>
+      <c r="BC16" s="46"/>
+      <c r="BD16" s="46"/>
+      <c r="BE16" s="46"/>
+      <c r="BF16" s="46"/>
+      <c r="BG16" s="46"/>
+    </row>
+    <row r="17" spans="1:59" s="35" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="71">
+        <v>1914</v>
+      </c>
+      <c r="D17" s="72" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="73">
+        <v>1</v>
+      </c>
+      <c r="F17" s="74">
+        <v>36</v>
+      </c>
+      <c r="G17" s="74">
+        <v>43</v>
+      </c>
+      <c r="H17" s="74">
+        <v>30</v>
+      </c>
+      <c r="I17" s="74">
+        <v>18</v>
+      </c>
+      <c r="J17" s="74"/>
+      <c r="K17" s="74"/>
+      <c r="L17" s="74"/>
+      <c r="M17" s="74"/>
+      <c r="N17" s="75">
         <v>24</v>
       </c>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="86"/>
-      <c r="L1" s="86"/>
-      <c r="M1" s="86"/>
-      <c r="N1" s="87"/>
-      <c r="O1" s="87"/>
-      <c r="P1" s="87"/>
-      <c r="Q1" s="87"/>
-      <c r="R1" s="87"/>
-      <c r="S1" s="87"/>
-      <c r="T1" s="87"/>
-      <c r="U1" s="87"/>
-      <c r="V1" s="87"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y1" s="88"/>
-      <c r="Z1" s="88"/>
-      <c r="AA1" s="88"/>
-      <c r="AB1" s="88"/>
-      <c r="AC1" s="88"/>
-      <c r="AD1" s="88"/>
-      <c r="AE1" s="88"/>
-      <c r="AF1" s="88"/>
-      <c r="AG1" s="88"/>
-      <c r="AH1" s="30"/>
-      <c r="AI1" s="30"/>
-      <c r="AJ1" s="79"/>
-      <c r="AM1" s="31"/>
-      <c r="AN1" s="31"/>
+      <c r="O17" s="75">
+        <v>13</v>
+      </c>
+      <c r="P17" s="85">
+        <v>6</v>
+      </c>
+      <c r="Q17" s="75"/>
+      <c r="R17" s="75">
+        <v>9</v>
+      </c>
+      <c r="S17" s="75"/>
+      <c r="T17" s="75"/>
+      <c r="U17" s="75"/>
+      <c r="V17" s="75"/>
+      <c r="W17" s="75"/>
+      <c r="X17" s="75">
+        <v>8</v>
+      </c>
+      <c r="Y17" s="75"/>
+      <c r="Z17" s="120"/>
+      <c r="AA17" s="75">
+        <v>4</v>
+      </c>
+      <c r="AB17" s="75"/>
+      <c r="AC17" s="75"/>
+      <c r="AD17" s="75"/>
+      <c r="AE17" s="75"/>
+      <c r="AF17" s="75"/>
+      <c r="AG17" s="75"/>
+      <c r="AH17" s="75"/>
+      <c r="AI17" s="120"/>
+      <c r="AJ17" s="75"/>
+      <c r="AK17" s="75"/>
+      <c r="AL17" s="75"/>
+      <c r="AM17" s="75"/>
+      <c r="AN17" s="75"/>
+      <c r="AO17" s="75"/>
+      <c r="AP17" s="75"/>
+      <c r="AQ17" s="75"/>
+      <c r="AR17" s="75"/>
+      <c r="AS17" s="75"/>
+      <c r="AT17" s="75"/>
+      <c r="AU17" s="75"/>
+      <c r="AV17" s="75"/>
+      <c r="AW17" s="75"/>
+      <c r="AX17" s="75"/>
+      <c r="AY17" s="75"/>
+      <c r="AZ17" s="75"/>
+      <c r="BA17" s="75"/>
+      <c r="BB17" s="75"/>
+      <c r="BC17" s="75"/>
+      <c r="BD17" s="75"/>
+      <c r="BE17" s="75"/>
+      <c r="BF17" s="75"/>
+      <c r="BG17" s="75"/>
     </row>
-    <row r="2" spans="1:40" ht="71.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="92" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="92" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="129" t="s">
-        <v>124</v>
-      </c>
-      <c r="F2" s="93" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="93" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="93" t="s">
-        <v>102</v>
-      </c>
-      <c r="I2" s="93" t="s">
-        <v>80</v>
-      </c>
-      <c r="J2" s="93" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="93" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" s="93" t="s">
-        <v>103</v>
-      </c>
-      <c r="M2" s="93" t="s">
-        <v>84</v>
-      </c>
-      <c r="N2" s="94" t="s">
-        <v>41</v>
-      </c>
-      <c r="O2" s="94" t="s">
-        <v>52</v>
-      </c>
-      <c r="P2" s="94" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q2" s="94" t="s">
-        <v>104</v>
-      </c>
-      <c r="R2" s="94" t="s">
-        <v>42</v>
-      </c>
-      <c r="S2" s="94" t="s">
-        <v>76</v>
-      </c>
-      <c r="T2" s="94" t="s">
-        <v>125</v>
-      </c>
-      <c r="U2" s="94" t="s">
-        <v>88</v>
-      </c>
-      <c r="V2" s="94" t="s">
-        <v>111</v>
-      </c>
-      <c r="W2" s="94" t="s">
-        <v>48</v>
-      </c>
-      <c r="X2" s="94" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y2" s="94" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z2" s="94" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA2" s="94" t="s">
-        <v>112</v>
-      </c>
-      <c r="AB2" s="94" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC2" s="94" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD2" s="94" t="s">
-        <v>118</v>
-      </c>
-      <c r="AE2" s="94" t="s">
-        <v>119</v>
-      </c>
-      <c r="AF2" s="94" t="s">
-        <v>120</v>
-      </c>
-      <c r="AG2" s="94" t="s">
-        <v>72</v>
-      </c>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="33"/>
-    </row>
-    <row r="3" spans="1:40" ht="43.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="95" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="96" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="97">
-        <v>1900</v>
-      </c>
-      <c r="D3" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="99">
-        <v>26</v>
-      </c>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100">
-        <v>21</v>
-      </c>
-      <c r="H3" s="100">
-        <v>14</v>
-      </c>
-      <c r="I3" s="100">
-        <v>48</v>
-      </c>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100">
-        <v>2</v>
-      </c>
-      <c r="M3" s="100">
-        <v>64</v>
-      </c>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101">
-        <v>1</v>
-      </c>
-      <c r="R3" s="101">
-        <v>1</v>
-      </c>
-      <c r="S3" s="101"/>
-      <c r="T3" s="101">
-        <v>6</v>
-      </c>
-      <c r="U3" s="101">
-        <v>7</v>
-      </c>
-      <c r="V3" s="101"/>
-      <c r="W3" s="101"/>
-      <c r="X3" s="101"/>
-      <c r="Y3" s="101"/>
-      <c r="Z3" s="101"/>
-      <c r="AA3" s="101"/>
-      <c r="AB3" s="101"/>
-      <c r="AC3" s="101">
-        <v>1</v>
-      </c>
-      <c r="AD3" s="101">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="101"/>
-      <c r="AF3" s="101">
-        <v>1</v>
-      </c>
-      <c r="AG3" s="102"/>
-      <c r="AH3" s="23"/>
-    </row>
-    <row r="4" spans="1:40" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="103" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="52">
-        <v>1902</v>
-      </c>
-      <c r="D4" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" s="80">
-        <v>44</v>
-      </c>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69">
-        <v>10</v>
-      </c>
-      <c r="H4" s="69">
-        <v>5</v>
-      </c>
-      <c r="I4" s="69">
-        <v>6</v>
-      </c>
-      <c r="J4" s="69">
-        <v>1</v>
-      </c>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69">
-        <v>10</v>
-      </c>
-      <c r="M4" s="69">
-        <v>11</v>
-      </c>
-      <c r="N4" s="73">
-        <v>7</v>
-      </c>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73">
-        <v>2</v>
-      </c>
-      <c r="U4" s="73">
-        <v>12</v>
-      </c>
-      <c r="V4" s="73"/>
-      <c r="W4" s="73">
-        <v>2</v>
-      </c>
-      <c r="X4" s="73"/>
-      <c r="Y4" s="73">
-        <v>3</v>
-      </c>
-      <c r="Z4" s="73">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="73"/>
-      <c r="AB4" s="73"/>
-      <c r="AC4" s="73"/>
-      <c r="AD4" s="73"/>
-      <c r="AE4" s="73"/>
-      <c r="AF4" s="73"/>
-      <c r="AG4" s="104"/>
-    </row>
-    <row r="5" spans="1:40" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="103" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="52">
-        <v>1903</v>
-      </c>
-      <c r="D5" s="53" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="80">
-        <v>15</v>
-      </c>
-      <c r="F5" s="70">
-        <v>4</v>
-      </c>
-      <c r="G5" s="69">
-        <v>15</v>
-      </c>
-      <c r="H5" s="69">
-        <v>26</v>
-      </c>
-      <c r="I5" s="69">
-        <v>24</v>
-      </c>
-      <c r="J5" s="69">
-        <v>4</v>
-      </c>
-      <c r="K5" s="69">
-        <v>6</v>
-      </c>
-      <c r="L5" s="69">
-        <v>14</v>
-      </c>
-      <c r="M5" s="69">
-        <v>37</v>
-      </c>
-      <c r="N5" s="73"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="73">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="73"/>
-      <c r="R5" s="73"/>
-      <c r="S5" s="73">
-        <v>9</v>
-      </c>
-      <c r="T5" s="73"/>
-      <c r="U5" s="73">
-        <v>4</v>
-      </c>
-      <c r="V5" s="73">
-        <v>14</v>
-      </c>
-      <c r="W5" s="73"/>
-      <c r="X5" s="73"/>
-      <c r="Y5" s="73"/>
-      <c r="Z5" s="73"/>
-      <c r="AA5" s="73"/>
-      <c r="AB5" s="73"/>
-      <c r="AC5" s="73"/>
-      <c r="AD5" s="73"/>
-      <c r="AE5" s="73"/>
-      <c r="AF5" s="73"/>
-      <c r="AG5" s="104"/>
-    </row>
-    <row r="6" spans="1:40" ht="38.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="103" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="52">
-        <v>1904</v>
-      </c>
-      <c r="D6" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="80">
-        <v>10</v>
-      </c>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69">
-        <v>1</v>
-      </c>
-      <c r="H6" s="69">
-        <v>5</v>
-      </c>
-      <c r="I6" s="69">
-        <v>43</v>
-      </c>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69">
-        <v>9</v>
-      </c>
-      <c r="L6" s="69">
-        <v>4</v>
-      </c>
-      <c r="M6" s="69">
-        <v>53</v>
-      </c>
-      <c r="N6" s="73">
-        <v>4</v>
-      </c>
-      <c r="O6" s="73"/>
-      <c r="P6" s="73"/>
-      <c r="Q6" s="73"/>
-      <c r="R6" s="73"/>
-      <c r="S6" s="73"/>
-      <c r="T6" s="73"/>
-      <c r="U6" s="73">
-        <v>8</v>
-      </c>
-      <c r="V6" s="73"/>
-      <c r="W6" s="73"/>
-      <c r="X6" s="73"/>
-      <c r="Y6" s="74"/>
-      <c r="Z6" s="73">
-        <v>5</v>
-      </c>
-      <c r="AA6" s="73"/>
-      <c r="AB6" s="73"/>
-      <c r="AC6" s="73"/>
-      <c r="AD6" s="73"/>
-      <c r="AE6" s="73"/>
-      <c r="AF6" s="73"/>
-      <c r="AG6" s="104"/>
-    </row>
-    <row r="7" spans="1:40" ht="46.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="105" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="106" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="107">
-        <v>1905</v>
-      </c>
-      <c r="D7" s="108" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="109">
-        <v>74</v>
-      </c>
-      <c r="F7" s="110"/>
-      <c r="G7" s="110">
-        <v>13</v>
-      </c>
-      <c r="H7" s="110">
-        <v>22</v>
-      </c>
-      <c r="I7" s="110">
-        <v>17</v>
-      </c>
-      <c r="J7" s="110"/>
-      <c r="K7" s="110"/>
-      <c r="L7" s="110">
-        <v>9</v>
-      </c>
-      <c r="M7" s="110">
-        <v>81</v>
-      </c>
-      <c r="N7" s="111">
-        <v>1</v>
-      </c>
-      <c r="O7" s="111"/>
-      <c r="P7" s="111"/>
-      <c r="Q7" s="111">
-        <v>13</v>
-      </c>
-      <c r="R7" s="111"/>
-      <c r="S7" s="111"/>
-      <c r="T7" s="111">
-        <v>13</v>
-      </c>
-      <c r="U7" s="111">
-        <v>16</v>
-      </c>
-      <c r="V7" s="111"/>
-      <c r="W7" s="111"/>
-      <c r="X7" s="111"/>
-      <c r="Y7" s="111"/>
-      <c r="Z7" s="111"/>
-      <c r="AA7" s="111">
-        <v>10</v>
-      </c>
-      <c r="AB7" s="111">
-        <v>4</v>
-      </c>
-      <c r="AC7" s="111"/>
-      <c r="AD7" s="111"/>
-      <c r="AE7" s="111"/>
-      <c r="AF7" s="111"/>
-      <c r="AG7" s="112"/>
-      <c r="AI7" s="91"/>
-    </row>
-    <row r="8" spans="1:40" ht="43.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="113" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="114" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="115">
-        <v>1908</v>
-      </c>
-      <c r="D8" s="116" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="117">
-        <v>46</v>
-      </c>
-      <c r="F8" s="118">
-        <v>5</v>
-      </c>
-      <c r="G8" s="118">
-        <v>25</v>
-      </c>
-      <c r="H8" s="118">
-        <v>44</v>
-      </c>
-      <c r="I8" s="118">
-        <v>91</v>
-      </c>
-      <c r="J8" s="118">
-        <v>1</v>
-      </c>
-      <c r="K8" s="118">
-        <v>2</v>
-      </c>
-      <c r="L8" s="118">
-        <v>12</v>
-      </c>
-      <c r="M8" s="118">
-        <v>94</v>
-      </c>
-      <c r="N8" s="90">
-        <v>5</v>
-      </c>
-      <c r="O8" s="90"/>
-      <c r="P8" s="90"/>
-      <c r="Q8" s="90"/>
-      <c r="R8" s="90">
-        <v>4</v>
-      </c>
-      <c r="S8" s="90"/>
-      <c r="T8" s="119">
-        <v>5</v>
-      </c>
-      <c r="U8" s="90">
-        <v>9</v>
-      </c>
-      <c r="V8" s="90"/>
-      <c r="W8" s="90">
-        <v>2</v>
-      </c>
-      <c r="X8" s="90">
-        <v>2</v>
-      </c>
-      <c r="Y8" s="90"/>
-      <c r="Z8" s="90">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="90"/>
-      <c r="AB8" s="90"/>
-      <c r="AC8" s="90"/>
-      <c r="AD8" s="90"/>
-      <c r="AE8" s="90"/>
-      <c r="AF8" s="90"/>
-      <c r="AG8" s="120"/>
-    </row>
-    <row r="9" spans="1:40" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="121" t="s">
-        <v>122</v>
-      </c>
-      <c r="B9" s="59" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="60">
-        <v>1908</v>
-      </c>
-      <c r="D9" s="61" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="82">
-        <v>33</v>
-      </c>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72">
-        <v>2</v>
-      </c>
-      <c r="H9" s="72">
-        <v>57</v>
-      </c>
-      <c r="I9" s="72">
-        <v>16</v>
-      </c>
-      <c r="J9" s="72">
-        <v>4</v>
-      </c>
-      <c r="K9" s="72"/>
-      <c r="L9" s="72">
-        <v>1</v>
-      </c>
-      <c r="M9" s="72">
-        <v>62</v>
-      </c>
-      <c r="N9" s="76">
-        <v>14</v>
-      </c>
-      <c r="O9" s="76"/>
-      <c r="P9" s="76"/>
-      <c r="Q9" s="76"/>
-      <c r="R9" s="76"/>
-      <c r="S9" s="76"/>
-      <c r="T9" s="77"/>
-      <c r="U9" s="76">
-        <v>33</v>
-      </c>
-      <c r="V9" s="76"/>
-      <c r="W9" s="76"/>
-      <c r="X9" s="76"/>
-      <c r="Y9" s="76"/>
-      <c r="Z9" s="76"/>
-      <c r="AA9" s="76"/>
-      <c r="AB9" s="76"/>
-      <c r="AC9" s="76"/>
-      <c r="AD9" s="76"/>
-      <c r="AE9" s="76"/>
-      <c r="AF9" s="76"/>
-      <c r="AG9" s="122"/>
-      <c r="AH9" s="50"/>
-      <c r="AI9" s="50"/>
-    </row>
-    <row r="10" spans="1:40" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="123" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" s="62" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" s="54">
-        <v>1909</v>
-      </c>
-      <c r="D10" s="63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="80">
-        <v>5</v>
-      </c>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69">
-        <v>14</v>
-      </c>
-      <c r="H10" s="69">
-        <v>16</v>
-      </c>
-      <c r="I10" s="69">
-        <v>17</v>
-      </c>
-      <c r="J10" s="69"/>
-      <c r="K10" s="69">
-        <v>1</v>
-      </c>
-      <c r="L10" s="69">
-        <v>6</v>
-      </c>
-      <c r="M10" s="69">
-        <v>35</v>
-      </c>
-      <c r="N10" s="73">
-        <v>0</v>
-      </c>
-      <c r="O10" s="73"/>
-      <c r="P10" s="73"/>
-      <c r="Q10" s="73"/>
-      <c r="R10" s="73"/>
-      <c r="S10" s="73"/>
-      <c r="T10" s="78"/>
-      <c r="U10" s="73"/>
-      <c r="V10" s="73"/>
-      <c r="W10" s="73">
-        <v>1</v>
-      </c>
-      <c r="X10" s="73"/>
-      <c r="Y10" s="73"/>
-      <c r="Z10" s="73"/>
-      <c r="AA10" s="73"/>
-      <c r="AB10" s="73"/>
-      <c r="AC10" s="73"/>
-      <c r="AD10" s="73"/>
-      <c r="AE10" s="73"/>
-      <c r="AF10" s="73"/>
-      <c r="AG10" s="104"/>
-      <c r="AH10" s="50"/>
-      <c r="AI10" s="50"/>
-    </row>
-    <row r="11" spans="1:40" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="124" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="65" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="54">
-        <v>1909</v>
-      </c>
-      <c r="D11" s="66" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="80">
-        <v>4</v>
-      </c>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69">
-        <v>9</v>
-      </c>
-      <c r="H11" s="69">
-        <v>12</v>
-      </c>
-      <c r="I11" s="69">
-        <v>11</v>
-      </c>
-      <c r="J11" s="69"/>
-      <c r="K11" s="69"/>
-      <c r="L11" s="69">
-        <v>11</v>
-      </c>
-      <c r="M11" s="69">
-        <v>18</v>
-      </c>
-      <c r="N11" s="73"/>
-      <c r="O11" s="73"/>
-      <c r="P11" s="73"/>
-      <c r="Q11" s="73"/>
-      <c r="R11" s="73"/>
-      <c r="S11" s="73"/>
-      <c r="T11" s="78"/>
-      <c r="U11" s="73">
-        <v>1</v>
-      </c>
-      <c r="V11" s="73"/>
-      <c r="W11" s="73"/>
-      <c r="X11" s="73"/>
-      <c r="Y11" s="73"/>
-      <c r="Z11" s="73"/>
-      <c r="AA11" s="73"/>
-      <c r="AB11" s="73"/>
-      <c r="AC11" s="73"/>
-      <c r="AD11" s="73"/>
-      <c r="AE11" s="73"/>
-      <c r="AF11" s="73"/>
-      <c r="AG11" s="104"/>
-      <c r="AH11" s="50"/>
-      <c r="AI11" s="50"/>
-    </row>
-    <row r="12" spans="1:40" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="54" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="65" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="64">
-        <v>1910</v>
-      </c>
-      <c r="D12" s="63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="80">
-        <v>19</v>
-      </c>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69">
-        <v>4</v>
-      </c>
-      <c r="H12" s="69">
-        <v>6</v>
-      </c>
-      <c r="I12" s="69">
-        <v>10</v>
-      </c>
-      <c r="J12" s="69">
-        <v>3</v>
-      </c>
-      <c r="K12" s="69">
-        <v>5</v>
-      </c>
-      <c r="L12" s="69">
-        <v>2</v>
-      </c>
-      <c r="M12" s="69">
-        <v>11</v>
-      </c>
-      <c r="N12" s="73"/>
-      <c r="O12" s="73">
-        <v>14</v>
-      </c>
-      <c r="P12" s="73"/>
-      <c r="Q12" s="73">
-        <v>2</v>
-      </c>
-      <c r="R12" s="73"/>
-      <c r="S12" s="73"/>
-      <c r="T12" s="78">
-        <v>8</v>
-      </c>
-      <c r="U12" s="73">
-        <v>11</v>
-      </c>
-      <c r="V12" s="73"/>
-      <c r="W12" s="73"/>
-      <c r="X12" s="73"/>
-      <c r="Y12" s="73"/>
-      <c r="Z12" s="73"/>
-      <c r="AA12" s="73"/>
-      <c r="AB12" s="73"/>
-      <c r="AC12" s="73"/>
-      <c r="AD12" s="73"/>
-      <c r="AE12" s="73"/>
-      <c r="AF12" s="73"/>
-      <c r="AG12" s="143"/>
-      <c r="AH12" s="144"/>
-      <c r="AI12" s="50"/>
-    </row>
-    <row r="13" spans="1:40" s="56" customFormat="1" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="134" t="s">
-        <v>123</v>
-      </c>
-      <c r="B13" s="135" t="s">
-        <v>116</v>
-      </c>
-      <c r="C13" s="136">
-        <v>1910</v>
-      </c>
-      <c r="D13" s="137" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" s="138">
-        <v>8</v>
-      </c>
-      <c r="F13" s="139"/>
-      <c r="G13" s="139">
-        <v>17</v>
-      </c>
-      <c r="H13" s="139">
-        <v>8</v>
-      </c>
-      <c r="I13" s="139">
-        <v>14</v>
-      </c>
-      <c r="J13" s="139"/>
-      <c r="K13" s="139"/>
-      <c r="L13" s="139"/>
-      <c r="M13" s="139">
-        <v>56</v>
-      </c>
-      <c r="N13" s="140"/>
-      <c r="O13" s="140"/>
-      <c r="P13" s="140"/>
-      <c r="Q13" s="140"/>
-      <c r="R13" s="140"/>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141">
-        <v>1</v>
-      </c>
-      <c r="U13" s="140">
-        <v>1</v>
-      </c>
-      <c r="V13" s="140"/>
-      <c r="W13" s="140"/>
-      <c r="X13" s="140"/>
-      <c r="Y13" s="140"/>
-      <c r="Z13" s="140">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="140"/>
-      <c r="AB13" s="140"/>
-      <c r="AC13" s="140"/>
-      <c r="AD13" s="140"/>
-      <c r="AE13" s="140"/>
-      <c r="AF13" s="140"/>
-      <c r="AG13" s="142"/>
-      <c r="AH13" s="67"/>
-      <c r="AI13" s="67"/>
-    </row>
-    <row r="14" spans="1:40" s="57" customFormat="1" ht="40.200000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="130" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="131" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="131">
-        <v>1911</v>
-      </c>
-      <c r="D14" s="132" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="81">
-        <v>13</v>
-      </c>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71">
-        <v>11</v>
-      </c>
-      <c r="I14" s="71">
-        <v>11</v>
-      </c>
-      <c r="J14" s="71"/>
-      <c r="K14" s="71">
-        <v>9</v>
-      </c>
-      <c r="L14" s="71">
-        <v>2</v>
-      </c>
-      <c r="M14" s="71">
-        <v>25</v>
-      </c>
-      <c r="N14" s="74">
-        <v>6</v>
-      </c>
-      <c r="O14" s="74"/>
-      <c r="P14" s="74"/>
-      <c r="Q14" s="74"/>
-      <c r="R14" s="74"/>
-      <c r="S14" s="74"/>
-      <c r="T14" s="75"/>
-      <c r="U14" s="74">
-        <v>7</v>
-      </c>
-      <c r="V14" s="74"/>
-      <c r="W14" s="74">
-        <v>1</v>
-      </c>
-      <c r="X14" s="74"/>
-      <c r="Y14" s="74"/>
-      <c r="Z14" s="74">
-        <v>2</v>
-      </c>
-      <c r="AA14" s="74"/>
-      <c r="AB14" s="74"/>
-      <c r="AC14" s="74"/>
-      <c r="AD14" s="74"/>
-      <c r="AE14" s="74"/>
-      <c r="AF14" s="74"/>
-      <c r="AG14" s="133"/>
-      <c r="AH14" s="68"/>
-      <c r="AI14" s="68"/>
-    </row>
-    <row r="15" spans="1:40" s="57" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="121" t="s">
-        <v>100</v>
-      </c>
-      <c r="B15" s="59" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="60">
-        <v>1912</v>
-      </c>
-      <c r="D15" s="61" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="82">
-        <v>5</v>
-      </c>
-      <c r="F15" s="72"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72">
-        <v>13</v>
-      </c>
-      <c r="I15" s="72">
-        <v>15</v>
-      </c>
-      <c r="J15" s="72"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="72">
-        <v>1</v>
-      </c>
-      <c r="M15" s="72">
-        <v>35</v>
-      </c>
-      <c r="N15" s="76"/>
-      <c r="O15" s="76"/>
-      <c r="P15" s="76"/>
-      <c r="Q15" s="76"/>
-      <c r="R15" s="76"/>
-      <c r="S15" s="76"/>
-      <c r="T15" s="77"/>
-      <c r="U15" s="76"/>
-      <c r="V15" s="76"/>
-      <c r="W15" s="76"/>
-      <c r="X15" s="76"/>
-      <c r="Y15" s="76"/>
-      <c r="Z15" s="76"/>
-      <c r="AA15" s="76"/>
-      <c r="AB15" s="76"/>
-      <c r="AC15" s="76"/>
-      <c r="AD15" s="76"/>
-      <c r="AE15" s="76"/>
-      <c r="AF15" s="76"/>
-      <c r="AG15" s="122"/>
-      <c r="AH15" s="68"/>
-      <c r="AI15" s="68"/>
-    </row>
-    <row r="16" spans="1:40" s="57" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="123" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="65" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="64">
-        <v>1913</v>
-      </c>
-      <c r="D16" s="63" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="80">
-        <v>2</v>
-      </c>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69">
-        <v>5</v>
-      </c>
-      <c r="H16" s="69">
-        <v>48</v>
-      </c>
-      <c r="I16" s="69">
-        <v>36</v>
-      </c>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="69">
-        <v>4</v>
-      </c>
-      <c r="M16" s="69">
-        <v>97</v>
-      </c>
-      <c r="N16" s="73">
-        <v>19</v>
-      </c>
-      <c r="O16" s="73"/>
-      <c r="P16" s="73"/>
-      <c r="Q16" s="73"/>
-      <c r="R16" s="73"/>
-      <c r="S16" s="73"/>
-      <c r="T16" s="78"/>
-      <c r="U16" s="73">
-        <v>26</v>
-      </c>
-      <c r="V16" s="73"/>
-      <c r="W16" s="73">
-        <v>15</v>
-      </c>
-      <c r="X16" s="73"/>
-      <c r="Y16" s="73"/>
-      <c r="Z16" s="73">
-        <v>5</v>
-      </c>
-      <c r="AA16" s="73"/>
-      <c r="AB16" s="73"/>
-      <c r="AC16" s="73"/>
-      <c r="AD16" s="73"/>
-      <c r="AE16" s="73"/>
-      <c r="AF16" s="73"/>
-      <c r="AG16" s="104"/>
-      <c r="AH16" s="68"/>
-      <c r="AI16" s="68"/>
-    </row>
-    <row r="17" spans="1:38" s="58" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="105" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="106" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="107">
-        <v>1914</v>
-      </c>
-      <c r="D17" s="108" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="109">
-        <v>1</v>
-      </c>
-      <c r="F17" s="110"/>
-      <c r="G17" s="110">
-        <v>18</v>
-      </c>
-      <c r="H17" s="110">
-        <v>32</v>
-      </c>
-      <c r="I17" s="110">
-        <v>43</v>
-      </c>
-      <c r="J17" s="110"/>
-      <c r="K17" s="110"/>
-      <c r="L17" s="110"/>
-      <c r="M17" s="110">
-        <v>36</v>
-      </c>
-      <c r="N17" s="111">
-        <v>13</v>
-      </c>
-      <c r="O17" s="111"/>
-      <c r="P17" s="111">
-        <v>8</v>
-      </c>
-      <c r="Q17" s="111"/>
-      <c r="R17" s="111"/>
-      <c r="S17" s="111"/>
-      <c r="T17" s="125">
-        <v>5</v>
-      </c>
-      <c r="U17" s="111">
-        <v>24</v>
-      </c>
-      <c r="V17" s="111"/>
-      <c r="W17" s="111"/>
-      <c r="X17" s="111">
-        <v>4</v>
-      </c>
-      <c r="Y17" s="111"/>
-      <c r="Z17" s="111">
-        <v>9</v>
-      </c>
-      <c r="AA17" s="111"/>
-      <c r="AB17" s="111"/>
-      <c r="AC17" s="111"/>
-      <c r="AD17" s="111"/>
-      <c r="AE17" s="111"/>
-      <c r="AF17" s="111"/>
-      <c r="AG17" s="112"/>
-    </row>
-    <row r="18" spans="1:38" ht="33.6" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:59" ht="33.6" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A18" s="27"/>
       <c r="B18" s="28"/>
       <c r="C18" s="28"/>
       <c r="D18" s="28"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="126">
-        <f t="shared" ref="F18:AG18" si="0">SUM(F3:F17)</f>
+      <c r="E18" s="117">
+        <f t="shared" ref="E18:BG18" si="0">SUM(E3:E17)</f>
+        <v>194</v>
+      </c>
+      <c r="F18" s="86">
+        <f t="shared" ref="F18:G18" si="1">SUM(F3:F17)</f>
+        <v>696</v>
+      </c>
+      <c r="G18" s="86">
+        <f t="shared" si="1"/>
+        <v>382</v>
+      </c>
+      <c r="H18" s="86">
+        <f>SUM(H3:H17)</f>
+        <v>312</v>
+      </c>
+      <c r="I18" s="86">
+        <f t="shared" ref="I18:L18" si="2">SUM(I3:I17)</f>
+        <v>151</v>
+      </c>
+      <c r="J18" s="86">
+        <f t="shared" si="2"/>
+        <v>77</v>
+      </c>
+      <c r="K18" s="86">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="L18" s="86">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="M18" s="86">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G18" s="126">
+      <c r="N18" s="87">
         <f t="shared" si="0"/>
-        <v>154</v>
-      </c>
-      <c r="H18" s="126">
-        <f t="shared" si="0"/>
-        <v>319</v>
-      </c>
-      <c r="I18" s="126">
-        <f t="shared" si="0"/>
-        <v>402</v>
-      </c>
-      <c r="J18" s="126">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="K18" s="126">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="L18" s="126">
-        <f t="shared" si="0"/>
-        <v>78</v>
-      </c>
-      <c r="M18" s="126">
-        <f t="shared" si="0"/>
-        <v>715</v>
-      </c>
-      <c r="N18" s="127">
+        <v>157</v>
+      </c>
+      <c r="O18" s="87">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="O18" s="127">
+      <c r="P18" s="87">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="Q18" s="87">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="R18" s="87">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="S18" s="87">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="T18" s="87">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U18" s="87">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="P18" s="127">
+      <c r="V18" s="87">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="W18" s="87">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="X18" s="87">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="Q18" s="127">
+      <c r="Y18" s="87">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="R18" s="127">
+        <v>9</v>
+      </c>
+      <c r="Z18" s="87">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AA18" s="87">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AB18" s="87">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="AC18" s="87">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="S18" s="127">
+      <c r="AD18" s="88">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="T18" s="127">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="88">
         <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="U18" s="127">
-        <f t="shared" si="0"/>
-        <v>159</v>
-      </c>
-      <c r="V18" s="127">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="W18" s="127">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="X18" s="128">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="Y18" s="128">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="88">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Z18" s="128">
+      <c r="AG18" s="88">
         <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="AA18" s="128">
+        <v>3</v>
+      </c>
+      <c r="AH18" s="88">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AB18" s="128">
+        <v>3</v>
+      </c>
+      <c r="AI18" s="88">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AC18" s="128">
+        <v>3</v>
+      </c>
+      <c r="AJ18" s="88">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AD18" s="128">
+        <v>3</v>
+      </c>
+      <c r="AK18" s="88">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AE18" s="128">
+        <v>2</v>
+      </c>
+      <c r="AL18" s="88">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AF18" s="128">
+        <v>2</v>
+      </c>
+      <c r="AM18" s="125">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AG18" s="128">
+        <v>2</v>
+      </c>
+      <c r="AN18" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AO18" s="125">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AP18" s="125">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AQ18" s="125">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AR18" s="125">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AS18" s="125">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT18" s="125">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU18" s="125">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV18" s="125">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW18" s="125">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX18" s="125">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY18" s="125">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ18" s="125">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="BA18" s="125">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="BB18" s="125">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="BC18" s="125">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="BD18" s="125">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="BE18" s="125">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="BF18" s="125">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="BG18" s="125">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:38" ht="21" x14ac:dyDescent="0.3">
-      <c r="A19" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="B19" s="40"/>
-      <c r="F19" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="37"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="38"/>
-      <c r="R19" s="38"/>
-      <c r="S19" s="38"/>
-      <c r="T19" s="38"/>
-      <c r="U19" s="38"/>
-      <c r="V19" s="38"/>
-      <c r="W19" s="38"/>
-      <c r="X19" s="38"/>
-      <c r="Y19" s="38"/>
-      <c r="Z19" s="38"/>
-      <c r="AA19" s="38"/>
-      <c r="AB19" s="38"/>
-      <c r="AC19" s="38"/>
-      <c r="AD19" s="38"/>
-      <c r="AE19" s="38"/>
-      <c r="AF19" s="38"/>
-      <c r="AG19" s="38"/>
-      <c r="AH19" s="34"/>
-      <c r="AI19" s="34"/>
-      <c r="AJ19" s="34"/>
-      <c r="AK19" s="29"/>
-      <c r="AL19" s="29"/>
+    <row r="19" spans="1:59" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="106" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" s="107"/>
+      <c r="E19" s="131" t="s">
+        <v>131</v>
+      </c>
+      <c r="F19" s="134" t="s">
+        <v>155</v>
+      </c>
+      <c r="G19" s="134"/>
+      <c r="H19" s="134"/>
+      <c r="I19" s="134"/>
+      <c r="J19" s="134"/>
+      <c r="K19" s="134"/>
+      <c r="L19" s="134"/>
+      <c r="M19" s="134"/>
+      <c r="N19" s="132" t="s">
+        <v>156</v>
+      </c>
+      <c r="O19" s="132"/>
+      <c r="P19" s="132"/>
+      <c r="Q19" s="132"/>
+      <c r="R19" s="132"/>
+      <c r="S19" s="132"/>
+      <c r="T19" s="132"/>
+      <c r="U19" s="132"/>
+      <c r="V19" s="132"/>
+      <c r="W19" s="132"/>
+      <c r="X19" s="132"/>
+      <c r="Y19" s="132"/>
+      <c r="Z19" s="132"/>
+      <c r="AA19" s="132"/>
+      <c r="AB19" s="132"/>
+      <c r="AC19" s="132"/>
+      <c r="AD19" s="132"/>
+      <c r="AE19" s="132"/>
+      <c r="AF19" s="132"/>
+      <c r="AG19" s="132"/>
+      <c r="AH19" s="132"/>
+      <c r="AI19" s="132"/>
+      <c r="AJ19" s="132"/>
+      <c r="AK19" s="132"/>
+      <c r="AL19" s="132"/>
+      <c r="AM19" s="132"/>
+      <c r="AN19" s="132"/>
+      <c r="AO19" s="132"/>
+      <c r="AP19" s="132"/>
+      <c r="AQ19" s="132"/>
+      <c r="AR19" s="132"/>
+      <c r="AS19" s="132"/>
+      <c r="AT19" s="132"/>
+      <c r="AU19" s="132"/>
+      <c r="AV19" s="132"/>
+      <c r="AW19" s="132"/>
+      <c r="AX19" s="132"/>
+      <c r="AY19" s="132"/>
+      <c r="AZ19" s="132"/>
+      <c r="BA19" s="132"/>
+      <c r="BB19" s="132"/>
+      <c r="BC19" s="132"/>
+      <c r="BD19" s="132"/>
+      <c r="BE19" s="132"/>
+      <c r="BF19" s="132"/>
+      <c r="BG19" s="132"/>
     </row>
-    <row r="20" spans="1:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="41"/>
-      <c r="B20" s="40"/>
+    <row r="20" spans="1:59" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="108"/>
+      <c r="B20" s="107"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="135"/>
+      <c r="I20" s="135"/>
+      <c r="J20" s="135"/>
+      <c r="K20" s="135"/>
+      <c r="L20" s="135"/>
+      <c r="M20" s="135"/>
+      <c r="N20" s="133"/>
+      <c r="O20" s="133"/>
+      <c r="P20" s="133"/>
+      <c r="Q20" s="133"/>
+      <c r="R20" s="133"/>
+      <c r="S20" s="133"/>
+      <c r="T20" s="133"/>
+      <c r="U20" s="133"/>
+      <c r="V20" s="133"/>
+      <c r="W20" s="133"/>
+      <c r="X20" s="133"/>
+      <c r="Y20" s="133"/>
+      <c r="Z20" s="133"/>
+      <c r="AA20" s="133"/>
+      <c r="AB20" s="133"/>
+      <c r="AC20" s="133"/>
+      <c r="AD20" s="133"/>
+      <c r="AE20" s="133"/>
+      <c r="AF20" s="133"/>
+      <c r="AG20" s="133"/>
+      <c r="AH20" s="133"/>
+      <c r="AI20" s="133"/>
+      <c r="AJ20" s="133"/>
+      <c r="AK20" s="133"/>
+      <c r="AL20" s="133"/>
+      <c r="AM20" s="133"/>
+      <c r="AN20" s="133"/>
+      <c r="AO20" s="133"/>
+      <c r="AP20" s="133"/>
+      <c r="AQ20" s="133"/>
+      <c r="AR20" s="133"/>
+      <c r="AS20" s="133"/>
+      <c r="AT20" s="133"/>
+      <c r="AU20" s="133"/>
+      <c r="AV20" s="133"/>
+      <c r="AW20" s="133"/>
+      <c r="AX20" s="133"/>
+      <c r="AY20" s="133"/>
+      <c r="AZ20" s="133"/>
+      <c r="BA20" s="133"/>
+      <c r="BB20" s="133"/>
+      <c r="BC20" s="133"/>
+      <c r="BD20" s="133"/>
+      <c r="BE20" s="133"/>
+      <c r="BF20" s="133"/>
+      <c r="BG20" s="133"/>
     </row>
-    <row r="21" spans="1:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" s="36"/>
+    <row r="21" spans="1:59" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="102" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="103"/>
     </row>
-    <row r="22" spans="1:38" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="35"/>
-      <c r="B22" s="36"/>
+    <row r="22" spans="1:59" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="102"/>
+      <c r="B22" s="103"/>
     </row>
+    <row r="23" spans="1:59" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AV23" s="126"/>
+    </row>
+    <row r="24" spans="1:59" ht="16.2" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="A1:AJ22">
-    <sortCondition ref="N2:AH2"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="A1:AS22">
+    <sortCondition ref="O2:AN2"/>
   </sortState>
   <mergeCells count="8">
-    <mergeCell ref="AH19:AJ19"/>
+    <mergeCell ref="N19:BG20"/>
     <mergeCell ref="A21:B22"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="N1:W1"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="O1:BG1"/>
     <mergeCell ref="F1:M1"/>
-    <mergeCell ref="F19:M19"/>
-    <mergeCell ref="N19:AG19"/>
-    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:M20"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A10 A12 A14:A17">
-    <cfRule type="colorScale" priority="104">
+    <cfRule type="colorScale" priority="110">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3556,7 +4350,7 @@
         <color rgb="FFFCFCFF"/>
       </colorScale>
     </cfRule>
-    <cfRule type="dataBar" priority="105">
+    <cfRule type="dataBar" priority="111">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3570,53 +4364,53 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E17">
-    <cfRule type="cellIs" dxfId="9" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="25" operator="greaterThan">
       <formula>116.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F4">
-    <cfRule type="cellIs" dxfId="8" priority="15" operator="greaterThan">
+  <conditionalFormatting sqref="M3:M4">
+    <cfRule type="cellIs" dxfId="14" priority="21" operator="greaterThan">
       <formula>4.5</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="O3:O4">
+    <cfRule type="cellIs" dxfId="7" priority="13" operator="greaterThan">
+      <formula>24</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X3:X17">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="greaterThan">
+      <formula>53</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F4">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="greaterThan">
+      <formula>160</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G3:G4">
-    <cfRule type="cellIs" dxfId="7" priority="14" operator="greaterThan">
-      <formula>35</formula>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThan">
+      <formula>139</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H4">
-    <cfRule type="cellIs" dxfId="6" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
       <formula>110</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I4">
-    <cfRule type="cellIs" dxfId="5" priority="12" operator="greaterThan">
-      <formula>139</formula>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+      <formula>35</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J4">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K4">
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>12</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L4">
-    <cfRule type="cellIs" dxfId="3" priority="9" operator="greaterThan">
-      <formula>20</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3:M4">
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
-      <formula>160</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N4">
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="greaterThan">
-      <formula>24</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P17">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
-      <formula>53</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -3708,40 +4502,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="111" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
       <c r="E1" s="6"/>
       <c r="F1" s="7"/>
-      <c r="G1" s="46" t="s">
+      <c r="G1" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="47" t="s">
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="114" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="47"/>
-      <c r="Z1" s="47"/>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="114"/>
+      <c r="AB1" s="114"/>
       <c r="AC1" s="8" t="s">
         <v>26</v>
       </c>
@@ -4790,12 +5584,12 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
-      <c r="H20" s="42" t="s">
+      <c r="H20" s="109" t="s">
         <v>93</v>
       </c>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42"/>
+      <c r="I20" s="109"/>
+      <c r="J20" s="109"/>
+      <c r="K20" s="109"/>
       <c r="L20" s="21" t="s">
         <v>93</v>
       </c>
@@ -4808,40 +5602,40 @@
       <c r="Q20" s="21"/>
       <c r="R20" s="21"/>
       <c r="S20" s="21"/>
-      <c r="T20" s="42"/>
-      <c r="U20" s="42"/>
-      <c r="V20" s="42"/>
-      <c r="W20" s="42"/>
+      <c r="T20" s="109"/>
+      <c r="U20" s="109"/>
+      <c r="V20" s="109"/>
+      <c r="W20" s="109"/>
       <c r="X20" s="21" t="s">
         <v>93</v>
       </c>
       <c r="Y20" s="21"/>
       <c r="Z20" s="21"/>
       <c r="AA20" s="21"/>
-      <c r="AB20" s="42"/>
-      <c r="AC20" s="42"/>
-      <c r="AD20" s="42"/>
-      <c r="AE20" s="42"/>
+      <c r="AB20" s="109"/>
+      <c r="AC20" s="109"/>
+      <c r="AD20" s="109"/>
+      <c r="AE20" s="109"/>
       <c r="AF20" s="21" t="s">
         <v>93</v>
       </c>
       <c r="AG20" s="21"/>
       <c r="AH20" s="21"/>
       <c r="AI20" s="21"/>
-      <c r="AJ20" s="42"/>
-      <c r="AK20" s="42"/>
-      <c r="AL20" s="42"/>
-      <c r="AM20" s="42"/>
-      <c r="AN20" s="42"/>
-      <c r="AO20" s="42"/>
-      <c r="AP20" s="42"/>
-      <c r="AQ20" s="42"/>
+      <c r="AJ20" s="109"/>
+      <c r="AK20" s="109"/>
+      <c r="AL20" s="109"/>
+      <c r="AM20" s="109"/>
+      <c r="AN20" s="109"/>
+      <c r="AO20" s="109"/>
+      <c r="AP20" s="109"/>
+      <c r="AQ20" s="109"/>
     </row>
     <row r="21" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A21" s="48" t="s">
+      <c r="A21" s="115" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="49"/>
+      <c r="B21" s="116"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -4885,10 +5679,10 @@
       <c r="AQ21" s="7"/>
     </row>
     <row r="22" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="110" t="s">
         <v>90</v>
       </c>
-      <c r="B22" s="43"/>
+      <c r="B22" s="110"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -4932,8 +5726,8 @@
       <c r="AQ22" s="7"/>
     </row>
     <row r="23" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A23" s="43"/>
-      <c r="B23" s="43"/>
+      <c r="A23" s="110"/>
+      <c r="B23" s="110"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>

--- a/Relaciones totales libro-patrimonio/LIBRO LOCALIDAD.xlsx
+++ b/Relaciones totales libro-patrimonio/LIBRO LOCALIDAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Antonio\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831E9CD1-4148-4950-83AC-56DCCEFE90EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147904CA-7123-4320-85B9-F9ABDC8F46AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="539" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="160">
   <si>
     <t xml:space="preserve">Almeria </t>
   </si>
@@ -827,12 +827,21 @@
   <si>
     <t>Total menciones a municpios no capitales (487 menciones)</t>
   </si>
+  <si>
+    <t>Joseph Thompson Shaw (1874-1952, USA)</t>
+  </si>
+  <si>
+    <t>Harry Alverson Franck (1881-1962, USA)</t>
+  </si>
+  <si>
+    <t>Howells William Dean (1837-1920, USA)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -953,35 +962,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="18">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1080,7 +1062,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1350,7 +1356,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1455,30 +1461,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1506,18 +1497,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1525,24 +1504,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1587,16 +1548,10 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1608,12 +1563,6 @@
     <xf numFmtId="0" fontId="9" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1626,201 +1575,204 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2203,7 +2155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BG24"/>
+  <dimension ref="A1:JQ24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="66.109375" style="26" customWidth="1"/>
@@ -2252,255 +2204,255 @@
     <col min="60" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" s="25" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:277" s="25" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="56" t="s">
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="114" t="s">
         <v>118</v>
       </c>
-      <c r="F1" s="129" t="s">
+      <c r="F1" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="130"/>
-      <c r="H1" s="130"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="130"/>
-      <c r="L1" s="130"/>
-      <c r="M1" s="130"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="128" t="s">
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="123" t="s">
         <v>145</v>
       </c>
-      <c r="P1" s="128"/>
-      <c r="Q1" s="128"/>
-      <c r="R1" s="128"/>
-      <c r="S1" s="128"/>
-      <c r="T1" s="128"/>
-      <c r="U1" s="128"/>
-      <c r="V1" s="128"/>
-      <c r="W1" s="128"/>
-      <c r="X1" s="128"/>
-      <c r="Y1" s="128"/>
-      <c r="Z1" s="128"/>
-      <c r="AA1" s="128"/>
-      <c r="AB1" s="128"/>
-      <c r="AC1" s="128"/>
-      <c r="AD1" s="128"/>
-      <c r="AE1" s="128"/>
-      <c r="AF1" s="128"/>
-      <c r="AG1" s="128"/>
-      <c r="AH1" s="128"/>
-      <c r="AI1" s="128"/>
-      <c r="AJ1" s="128"/>
-      <c r="AK1" s="128"/>
-      <c r="AL1" s="128"/>
-      <c r="AM1" s="128"/>
-      <c r="AN1" s="128"/>
-      <c r="AO1" s="128"/>
-      <c r="AP1" s="128"/>
-      <c r="AQ1" s="128"/>
-      <c r="AR1" s="128"/>
-      <c r="AS1" s="128"/>
-      <c r="AT1" s="128"/>
-      <c r="AU1" s="128"/>
-      <c r="AV1" s="128"/>
-      <c r="AW1" s="128"/>
-      <c r="AX1" s="128"/>
-      <c r="AY1" s="128"/>
-      <c r="AZ1" s="128"/>
-      <c r="BA1" s="128"/>
-      <c r="BB1" s="128"/>
-      <c r="BC1" s="128"/>
-      <c r="BD1" s="128"/>
-      <c r="BE1" s="128"/>
-      <c r="BF1" s="128"/>
-      <c r="BG1" s="128"/>
+      <c r="O1" s="123"/>
+      <c r="P1" s="123"/>
+      <c r="Q1" s="123"/>
+      <c r="R1" s="123"/>
+      <c r="S1" s="123"/>
+      <c r="T1" s="123"/>
+      <c r="U1" s="123"/>
+      <c r="V1" s="123"/>
+      <c r="W1" s="123"/>
+      <c r="X1" s="123"/>
+      <c r="Y1" s="123"/>
+      <c r="Z1" s="123"/>
+      <c r="AA1" s="123"/>
+      <c r="AB1" s="123"/>
+      <c r="AC1" s="123"/>
+      <c r="AD1" s="123"/>
+      <c r="AE1" s="123"/>
+      <c r="AF1" s="123"/>
+      <c r="AG1" s="123"/>
+      <c r="AH1" s="123"/>
+      <c r="AI1" s="123"/>
+      <c r="AJ1" s="123"/>
+      <c r="AK1" s="123"/>
+      <c r="AL1" s="123"/>
+      <c r="AM1" s="123"/>
+      <c r="AN1" s="123"/>
+      <c r="AO1" s="123"/>
+      <c r="AP1" s="123"/>
+      <c r="AQ1" s="123"/>
+      <c r="AR1" s="123"/>
+      <c r="AS1" s="123"/>
+      <c r="AT1" s="123"/>
+      <c r="AU1" s="123"/>
+      <c r="AV1" s="123"/>
+      <c r="AW1" s="123"/>
+      <c r="AX1" s="123"/>
+      <c r="AY1" s="123"/>
+      <c r="AZ1" s="123"/>
+      <c r="BA1" s="123"/>
+      <c r="BB1" s="123"/>
+      <c r="BC1" s="123"/>
+      <c r="BD1" s="123"/>
+      <c r="BE1" s="123"/>
+      <c r="BF1" s="123"/>
+      <c r="BG1" s="123"/>
     </row>
-    <row r="2" spans="1:59" ht="71.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="58" t="s">
+    <row r="2" spans="1:277" ht="71.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="58" t="s">
+      <c r="D2" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="89" t="s">
+      <c r="E2" s="70" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="59" t="s">
+      <c r="G2" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="I2" s="59" t="s">
+      <c r="I2" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="J2" s="59" t="s">
+      <c r="J2" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="K2" s="59" t="s">
+      <c r="K2" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="L2" s="59" t="s">
+      <c r="L2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="59" t="s">
+      <c r="M2" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="126" t="s">
         <v>88</v>
       </c>
-      <c r="O2" s="60" t="s">
+      <c r="O2" s="126" t="s">
         <v>41</v>
       </c>
-      <c r="P2" s="60" t="s">
+      <c r="P2" s="126" t="s">
         <v>151</v>
       </c>
-      <c r="Q2" s="60" t="s">
+      <c r="Q2" s="126" t="s">
         <v>110</v>
       </c>
-      <c r="R2" s="60" t="s">
+      <c r="R2" s="126" t="s">
         <v>106</v>
       </c>
-      <c r="S2" s="60" t="s">
+      <c r="S2" s="126" t="s">
         <v>48</v>
       </c>
-      <c r="T2" s="60" t="s">
+      <c r="T2" s="126" t="s">
         <v>101</v>
       </c>
-      <c r="U2" s="60" t="s">
+      <c r="U2" s="126" t="s">
         <v>152</v>
       </c>
-      <c r="V2" s="60" t="s">
+      <c r="V2" s="126" t="s">
         <v>52</v>
       </c>
-      <c r="W2" s="60" t="s">
+      <c r="W2" s="126" t="s">
         <v>127</v>
       </c>
-      <c r="X2" s="60" t="s">
+      <c r="X2" s="126" t="s">
         <v>57</v>
       </c>
-      <c r="Y2" s="60" t="s">
+      <c r="Y2" s="126" t="s">
         <v>76</v>
       </c>
-      <c r="Z2" s="118" t="s">
+      <c r="Z2" s="127" t="s">
         <v>68</v>
       </c>
-      <c r="AA2" s="60" t="s">
+      <c r="AA2" s="126" t="s">
         <v>71</v>
       </c>
-      <c r="AB2" s="60" t="s">
+      <c r="AB2" s="126" t="s">
         <v>153</v>
       </c>
-      <c r="AC2" s="60" t="s">
+      <c r="AC2" s="126" t="s">
         <v>42</v>
       </c>
-      <c r="AD2" s="60" t="s">
+      <c r="AD2" s="126" t="s">
         <v>126</v>
       </c>
-      <c r="AE2" s="60" t="s">
+      <c r="AE2" s="126" t="s">
         <v>128</v>
       </c>
-      <c r="AF2" s="60" t="s">
+      <c r="AF2" s="126" t="s">
         <v>154</v>
       </c>
-      <c r="AG2" s="60" t="s">
+      <c r="AG2" s="126" t="s">
         <v>114</v>
       </c>
-      <c r="AH2" s="60" t="s">
+      <c r="AH2" s="126" t="s">
         <v>137</v>
       </c>
-      <c r="AI2" s="60" t="s">
+      <c r="AI2" s="126" t="s">
         <v>150</v>
       </c>
-      <c r="AJ2" s="60" t="s">
+      <c r="AJ2" s="126" t="s">
         <v>64</v>
       </c>
-      <c r="AK2" s="60" t="s">
+      <c r="AK2" s="126" t="s">
         <v>146</v>
       </c>
-      <c r="AL2" s="60" t="s">
+      <c r="AL2" s="126" t="s">
         <v>91</v>
       </c>
-      <c r="AM2" s="60" t="s">
+      <c r="AM2" s="126" t="s">
         <v>132</v>
       </c>
-      <c r="AN2" s="60" t="s">
+      <c r="AN2" s="126" t="s">
         <v>133</v>
       </c>
-      <c r="AO2" s="60" t="s">
+      <c r="AO2" s="126" t="s">
         <v>134</v>
       </c>
-      <c r="AP2" s="60" t="s">
+      <c r="AP2" s="126" t="s">
         <v>139</v>
       </c>
-      <c r="AQ2" s="60" t="s">
+      <c r="AQ2" s="126" t="s">
         <v>149</v>
       </c>
-      <c r="AR2" s="60" t="s">
+      <c r="AR2" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="AS2" s="60" t="s">
+      <c r="AS2" s="126" t="s">
         <v>130</v>
       </c>
-      <c r="AT2" s="60" t="s">
+      <c r="AT2" s="126" t="s">
         <v>129</v>
       </c>
-      <c r="AU2" s="60" t="s">
+      <c r="AU2" s="126" t="s">
         <v>115</v>
       </c>
-      <c r="AV2" s="60" t="s">
+      <c r="AV2" s="126" t="s">
         <v>116</v>
       </c>
-      <c r="AW2" s="60" t="s">
+      <c r="AW2" s="126" t="s">
         <v>117</v>
       </c>
-      <c r="AX2" s="60" t="s">
+      <c r="AX2" s="126" t="s">
         <v>140</v>
       </c>
-      <c r="AY2" s="60" t="s">
+      <c r="AY2" s="126" t="s">
         <v>135</v>
       </c>
-      <c r="AZ2" s="60" t="s">
+      <c r="AZ2" s="126" t="s">
         <v>136</v>
       </c>
-      <c r="BA2" s="60" t="s">
+      <c r="BA2" s="126" t="s">
         <v>138</v>
       </c>
-      <c r="BB2" s="60" t="s">
+      <c r="BB2" s="126" t="s">
         <v>141</v>
       </c>
-      <c r="BC2" s="60" t="s">
+      <c r="BC2" s="126" t="s">
         <v>142</v>
       </c>
-      <c r="BD2" s="60" t="s">
+      <c r="BD2" s="126" t="s">
         <v>143</v>
       </c>
-      <c r="BE2" s="60" t="s">
+      <c r="BE2" s="126" t="s">
         <v>144</v>
       </c>
-      <c r="BF2" s="60" t="s">
+      <c r="BF2" s="126" t="s">
         <v>147</v>
       </c>
-      <c r="BG2" s="60" t="s">
+      <c r="BG2" s="126" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:59" ht="43.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:277" ht="43.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" s="61" t="s">
         <v>111</v>
       </c>
@@ -2510,93 +2462,93 @@
       <c r="C3" s="63">
         <v>1900</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="117" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="65">
+      <c r="E3" s="115">
         <v>26</v>
       </c>
-      <c r="F3" s="66">
+      <c r="F3" s="104">
         <v>64</v>
       </c>
-      <c r="G3" s="66">
+      <c r="G3" s="104">
         <v>48</v>
       </c>
-      <c r="H3" s="66">
+      <c r="H3" s="104">
         <v>14</v>
       </c>
-      <c r="I3" s="66">
+      <c r="I3" s="104">
         <v>21</v>
       </c>
-      <c r="J3" s="66">
+      <c r="J3" s="51">
         <v>2</v>
       </c>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="67">
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="52">
         <v>7</v>
       </c>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67">
+      <c r="O3" s="52"/>
+      <c r="P3" s="52">
         <v>6</v>
       </c>
-      <c r="Q3" s="67">
+      <c r="Q3" s="52">
         <v>1</v>
       </c>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67">
+      <c r="R3" s="52"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="52">
         <v>1</v>
       </c>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67"/>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
-      <c r="Z3" s="119"/>
-      <c r="AA3" s="67"/>
-      <c r="AB3" s="57"/>
-      <c r="AC3" s="67">
+      <c r="U3" s="52"/>
+      <c r="V3" s="52"/>
+      <c r="W3" s="52"/>
+      <c r="X3" s="52"/>
+      <c r="Y3" s="52"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="52"/>
+      <c r="AB3" s="48"/>
+      <c r="AC3" s="52">
         <v>1</v>
       </c>
-      <c r="AD3" s="67"/>
-      <c r="AE3" s="67"/>
-      <c r="AF3" s="67">
+      <c r="AD3" s="52"/>
+      <c r="AE3" s="52"/>
+      <c r="AF3" s="52">
         <v>1</v>
       </c>
-      <c r="AG3" s="67"/>
-      <c r="AH3" s="57"/>
-      <c r="AI3" s="121"/>
-      <c r="AJ3" s="57"/>
-      <c r="AK3" s="67"/>
-      <c r="AL3" s="57"/>
-      <c r="AM3" s="57"/>
-      <c r="AN3" s="57"/>
-      <c r="AO3" s="57"/>
-      <c r="AP3" s="57"/>
-      <c r="AQ3" s="57"/>
-      <c r="AR3" s="57"/>
-      <c r="AS3" s="57"/>
-      <c r="AT3" s="57"/>
-      <c r="AU3" s="57"/>
-      <c r="AV3" s="57"/>
-      <c r="AW3" s="57"/>
-      <c r="AX3" s="67">
+      <c r="AG3" s="52"/>
+      <c r="AH3" s="48"/>
+      <c r="AI3" s="81"/>
+      <c r="AJ3" s="48"/>
+      <c r="AK3" s="52"/>
+      <c r="AL3" s="48"/>
+      <c r="AM3" s="48"/>
+      <c r="AN3" s="48"/>
+      <c r="AO3" s="48"/>
+      <c r="AP3" s="48"/>
+      <c r="AQ3" s="48"/>
+      <c r="AR3" s="48"/>
+      <c r="AS3" s="48"/>
+      <c r="AT3" s="48"/>
+      <c r="AU3" s="48"/>
+      <c r="AV3" s="48"/>
+      <c r="AW3" s="48"/>
+      <c r="AX3" s="52">
         <v>1</v>
       </c>
-      <c r="AY3" s="57"/>
-      <c r="AZ3" s="57"/>
-      <c r="BA3" s="57"/>
-      <c r="BB3" s="57"/>
-      <c r="BC3" s="57"/>
-      <c r="BD3" s="57"/>
-      <c r="BE3" s="57"/>
-      <c r="BF3" s="57"/>
-      <c r="BG3" s="57"/>
+      <c r="AY3" s="48"/>
+      <c r="AZ3" s="48"/>
+      <c r="BA3" s="48"/>
+      <c r="BB3" s="48"/>
+      <c r="BC3" s="48"/>
+      <c r="BD3" s="48"/>
+      <c r="BE3" s="48"/>
+      <c r="BF3" s="48"/>
+      <c r="BG3" s="48"/>
     </row>
-    <row r="4" spans="1:59" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="68" t="s">
+    <row r="4" spans="1:277" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="53" t="s">
         <v>97</v>
       </c>
       <c r="B4" s="29" t="s">
@@ -2608,102 +2560,102 @@
       <c r="D4" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="52">
+      <c r="E4" s="116">
         <v>17</v>
       </c>
-      <c r="F4" s="42">
+      <c r="F4" s="105">
         <v>11</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="38">
         <v>6</v>
       </c>
-      <c r="H4" s="42">
+      <c r="H4" s="38">
         <v>5</v>
       </c>
-      <c r="I4" s="42">
+      <c r="I4" s="38">
         <v>7</v>
       </c>
-      <c r="J4" s="42">
+      <c r="J4" s="105">
         <v>10</v>
       </c>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42">
+      <c r="K4" s="38"/>
+      <c r="L4" s="38">
         <v>1</v>
       </c>
-      <c r="M4" s="42"/>
-      <c r="N4" s="46">
+      <c r="M4" s="38"/>
+      <c r="N4" s="131">
         <v>12</v>
       </c>
-      <c r="O4" s="46">
+      <c r="O4" s="41">
         <v>7</v>
       </c>
-      <c r="P4" s="46">
+      <c r="P4" s="41">
         <v>2</v>
       </c>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="46">
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41">
         <v>1</v>
       </c>
-      <c r="S4" s="46">
+      <c r="S4" s="41">
         <v>2</v>
       </c>
-      <c r="T4" s="46"/>
-      <c r="U4" s="46"/>
-      <c r="V4" s="46"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="46"/>
-      <c r="Y4" s="46"/>
-      <c r="Z4" s="101"/>
-      <c r="AA4" s="46"/>
-      <c r="AB4" s="46"/>
-      <c r="AC4" s="46"/>
-      <c r="AD4" s="46"/>
-      <c r="AE4" s="46"/>
-      <c r="AF4" s="46"/>
-      <c r="AG4" s="46">
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="41"/>
+      <c r="AB4" s="41"/>
+      <c r="AC4" s="41"/>
+      <c r="AD4" s="41"/>
+      <c r="AE4" s="41"/>
+      <c r="AF4" s="41"/>
+      <c r="AG4" s="131">
         <v>2</v>
       </c>
-      <c r="AH4" s="46"/>
-      <c r="AI4" s="101"/>
-      <c r="AJ4" s="46"/>
-      <c r="AK4" s="46"/>
-      <c r="AL4" s="46">
+      <c r="AH4" s="41"/>
+      <c r="AI4" s="77"/>
+      <c r="AJ4" s="41"/>
+      <c r="AK4" s="41"/>
+      <c r="AL4" s="41">
         <v>1</v>
       </c>
-      <c r="AM4" s="46"/>
-      <c r="AN4" s="46"/>
-      <c r="AO4" s="46"/>
-      <c r="AP4" s="46"/>
-      <c r="AQ4" s="46"/>
-      <c r="AR4" s="46"/>
-      <c r="AS4" s="46">
+      <c r="AM4" s="41"/>
+      <c r="AN4" s="41"/>
+      <c r="AO4" s="41"/>
+      <c r="AP4" s="41"/>
+      <c r="AQ4" s="41"/>
+      <c r="AR4" s="41"/>
+      <c r="AS4" s="41">
         <v>1</v>
       </c>
-      <c r="AT4" s="46">
+      <c r="AT4" s="41">
         <v>1</v>
       </c>
-      <c r="AU4" s="46">
+      <c r="AU4" s="41">
         <v>1</v>
       </c>
-      <c r="AV4" s="46">
+      <c r="AV4" s="41">
         <v>1</v>
       </c>
-      <c r="AW4" s="46">
+      <c r="AW4" s="41">
         <v>1</v>
       </c>
-      <c r="AX4" s="46"/>
-      <c r="AY4" s="46"/>
-      <c r="AZ4" s="46"/>
-      <c r="BA4" s="46"/>
-      <c r="BB4" s="46"/>
-      <c r="BC4" s="46"/>
-      <c r="BD4" s="46"/>
-      <c r="BE4" s="46"/>
-      <c r="BF4" s="46"/>
-      <c r="BG4" s="46"/>
+      <c r="AX4" s="41"/>
+      <c r="AY4" s="41"/>
+      <c r="AZ4" s="41"/>
+      <c r="BA4" s="41"/>
+      <c r="BB4" s="41"/>
+      <c r="BC4" s="41"/>
+      <c r="BD4" s="41"/>
+      <c r="BE4" s="41"/>
+      <c r="BF4" s="41"/>
+      <c r="BG4" s="41"/>
     </row>
-    <row r="5" spans="1:59" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="68" t="s">
+    <row r="5" spans="1:277" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="53" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="29" t="s">
@@ -2715,94 +2667,94 @@
       <c r="D5" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="52">
+      <c r="E5" s="47">
         <v>8</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="105">
         <v>35</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="105">
         <v>18</v>
       </c>
-      <c r="H5" s="42">
+      <c r="H5" s="105">
         <v>24</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="105">
         <v>15</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="105">
         <v>13</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="38">
         <v>6</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="105">
         <v>4</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="137">
         <v>4</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="41">
         <v>4</v>
       </c>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="46">
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41">
         <v>1</v>
       </c>
-      <c r="R5" s="46"/>
-      <c r="S5" s="46"/>
-      <c r="T5" s="46"/>
-      <c r="U5" s="46">
+      <c r="R5" s="41"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="131">
         <v>14</v>
       </c>
-      <c r="V5" s="46"/>
-      <c r="W5" s="46"/>
-      <c r="X5" s="46">
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="41">
         <v>1</v>
       </c>
-      <c r="Y5" s="46">
+      <c r="Y5" s="131">
         <v>9</v>
       </c>
-      <c r="Z5" s="101"/>
-      <c r="AA5" s="46"/>
-      <c r="AB5" s="46"/>
-      <c r="AC5" s="46"/>
-      <c r="AD5" s="46">
+      <c r="Z5" s="77"/>
+      <c r="AA5" s="41"/>
+      <c r="AB5" s="41"/>
+      <c r="AC5" s="41"/>
+      <c r="AD5" s="41">
         <v>1</v>
       </c>
-      <c r="AE5" s="46"/>
-      <c r="AF5" s="46"/>
-      <c r="AG5" s="46"/>
-      <c r="AH5" s="46"/>
-      <c r="AI5" s="101"/>
-      <c r="AJ5" s="46"/>
-      <c r="AK5" s="46"/>
-      <c r="AL5" s="46"/>
-      <c r="AM5" s="46"/>
-      <c r="AN5" s="46"/>
-      <c r="AO5" s="46"/>
-      <c r="AP5" s="46"/>
-      <c r="AQ5" s="46"/>
-      <c r="AR5" s="46"/>
-      <c r="AS5" s="46"/>
-      <c r="AT5" s="46"/>
-      <c r="AU5" s="46"/>
-      <c r="AV5" s="46"/>
-      <c r="AW5" s="46"/>
-      <c r="AX5" s="46"/>
-      <c r="AY5" s="46"/>
-      <c r="AZ5" s="46"/>
-      <c r="BA5" s="46"/>
-      <c r="BB5" s="46"/>
-      <c r="BC5" s="46"/>
-      <c r="BD5" s="46"/>
-      <c r="BE5" s="46"/>
-      <c r="BF5" s="46"/>
-      <c r="BG5" s="46"/>
+      <c r="AE5" s="41"/>
+      <c r="AF5" s="41"/>
+      <c r="AG5" s="41"/>
+      <c r="AH5" s="41"/>
+      <c r="AI5" s="77"/>
+      <c r="AJ5" s="41"/>
+      <c r="AK5" s="41"/>
+      <c r="AL5" s="41"/>
+      <c r="AM5" s="41"/>
+      <c r="AN5" s="41"/>
+      <c r="AO5" s="41"/>
+      <c r="AP5" s="41"/>
+      <c r="AQ5" s="41"/>
+      <c r="AR5" s="41"/>
+      <c r="AS5" s="41"/>
+      <c r="AT5" s="41"/>
+      <c r="AU5" s="41"/>
+      <c r="AV5" s="41"/>
+      <c r="AW5" s="41"/>
+      <c r="AX5" s="41"/>
+      <c r="AY5" s="41"/>
+      <c r="AZ5" s="41"/>
+      <c r="BA5" s="41"/>
+      <c r="BB5" s="41"/>
+      <c r="BC5" s="41"/>
+      <c r="BD5" s="41"/>
+      <c r="BE5" s="41"/>
+      <c r="BF5" s="41"/>
+      <c r="BG5" s="41"/>
     </row>
-    <row r="6" spans="1:59" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="68" t="s">
+    <row r="6" spans="1:277" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="53" t="s">
         <v>95</v>
       </c>
       <c r="B6" s="29" t="s">
@@ -2814,503 +2766,723 @@
       <c r="D6" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="52">
+      <c r="E6" s="47">
         <v>5</v>
       </c>
-      <c r="F6" s="42">
+      <c r="F6" s="105">
         <v>53</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="105">
         <v>43</v>
       </c>
-      <c r="H6" s="42">
+      <c r="H6" s="38">
         <v>5</v>
       </c>
-      <c r="I6" s="42">
+      <c r="I6" s="38">
         <v>1</v>
       </c>
-      <c r="J6" s="42">
+      <c r="J6" s="38">
         <v>4</v>
       </c>
-      <c r="K6" s="42">
+      <c r="K6" s="105">
         <v>9</v>
       </c>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="46">
+      <c r="L6" s="38"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="41">
         <v>8</v>
       </c>
-      <c r="O6" s="46">
+      <c r="O6" s="41">
         <v>4</v>
       </c>
-      <c r="P6" s="46">
+      <c r="P6" s="41">
         <v>1</v>
       </c>
-      <c r="Q6" s="46"/>
-      <c r="R6" s="46">
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41">
         <v>5</v>
       </c>
-      <c r="S6" s="46"/>
-      <c r="T6" s="46"/>
-      <c r="U6" s="46"/>
-      <c r="V6" s="46"/>
-      <c r="W6" s="46"/>
-      <c r="X6" s="46"/>
-      <c r="Y6" s="46"/>
-      <c r="Z6" s="101"/>
-      <c r="AA6" s="46"/>
-      <c r="AB6" s="46"/>
-      <c r="AC6" s="46"/>
-      <c r="AD6" s="47"/>
-      <c r="AE6" s="46"/>
-      <c r="AF6" s="46"/>
-      <c r="AG6" s="46"/>
-      <c r="AH6" s="46"/>
-      <c r="AI6" s="101"/>
-      <c r="AJ6" s="46"/>
-      <c r="AK6" s="46"/>
-      <c r="AL6" s="46"/>
-      <c r="AM6" s="46"/>
-      <c r="AN6" s="46"/>
-      <c r="AO6" s="46"/>
-      <c r="AP6" s="46"/>
-      <c r="AQ6" s="46"/>
-      <c r="AR6" s="46"/>
-      <c r="AS6" s="46"/>
-      <c r="AT6" s="46"/>
-      <c r="AU6" s="46"/>
-      <c r="AV6" s="46"/>
-      <c r="AW6" s="46"/>
-      <c r="AX6" s="46"/>
-      <c r="AY6" s="46"/>
-      <c r="AZ6" s="46"/>
-      <c r="BA6" s="46"/>
-      <c r="BB6" s="46"/>
-      <c r="BC6" s="46"/>
-      <c r="BD6" s="46"/>
-      <c r="BE6" s="46"/>
-      <c r="BF6" s="46"/>
-      <c r="BG6" s="46"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="41"/>
+      <c r="Z6" s="77"/>
+      <c r="AA6" s="41"/>
+      <c r="AB6" s="41"/>
+      <c r="AC6" s="41"/>
+      <c r="AD6" s="42"/>
+      <c r="AE6" s="41"/>
+      <c r="AF6" s="41"/>
+      <c r="AG6" s="41"/>
+      <c r="AH6" s="41"/>
+      <c r="AI6" s="77"/>
+      <c r="AJ6" s="41"/>
+      <c r="AK6" s="41"/>
+      <c r="AL6" s="41"/>
+      <c r="AM6" s="41"/>
+      <c r="AN6" s="41"/>
+      <c r="AO6" s="41"/>
+      <c r="AP6" s="41"/>
+      <c r="AQ6" s="41"/>
+      <c r="AR6" s="41"/>
+      <c r="AS6" s="41"/>
+      <c r="AT6" s="41"/>
+      <c r="AU6" s="41"/>
+      <c r="AV6" s="41"/>
+      <c r="AW6" s="41"/>
+      <c r="AX6" s="41"/>
+      <c r="AY6" s="41"/>
+      <c r="AZ6" s="41"/>
+      <c r="BA6" s="41"/>
+      <c r="BB6" s="41"/>
+      <c r="BC6" s="41"/>
+      <c r="BD6" s="41"/>
+      <c r="BE6" s="41"/>
+      <c r="BF6" s="41"/>
+      <c r="BG6" s="41"/>
     </row>
-    <row r="7" spans="1:59" ht="46.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="69" t="s">
+    <row r="7" spans="1:277" ht="46.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="70" t="s">
+      <c r="B7" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="71">
+      <c r="C7" s="56">
         <v>1905</v>
       </c>
-      <c r="D7" s="72" t="s">
+      <c r="D7" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="73">
+      <c r="E7" s="121">
         <v>39</v>
       </c>
-      <c r="F7" s="74">
+      <c r="F7" s="106">
         <v>72</v>
       </c>
-      <c r="G7" s="74">
+      <c r="G7" s="106">
         <v>17</v>
       </c>
-      <c r="H7" s="74">
+      <c r="H7" s="106">
         <v>22</v>
       </c>
-      <c r="I7" s="74">
+      <c r="I7" s="106">
         <v>13</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="59">
         <v>9</v>
       </c>
-      <c r="K7" s="74"/>
-      <c r="L7" s="74"/>
-      <c r="M7" s="74"/>
-      <c r="N7" s="75">
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="132">
         <v>16</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="60">
         <v>1</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="60">
         <v>1</v>
       </c>
-      <c r="Q7" s="75"/>
-      <c r="R7" s="75"/>
-      <c r="S7" s="75"/>
-      <c r="T7" s="75">
+      <c r="Q7" s="60"/>
+      <c r="R7" s="60"/>
+      <c r="S7" s="60"/>
+      <c r="T7" s="132">
         <v>13</v>
       </c>
-      <c r="U7" s="75"/>
-      <c r="V7" s="75"/>
-      <c r="W7" s="75">
+      <c r="U7" s="60"/>
+      <c r="V7" s="60"/>
+      <c r="W7" s="132">
         <v>10</v>
       </c>
-      <c r="X7" s="75"/>
-      <c r="Y7" s="75"/>
-      <c r="Z7" s="120">
+      <c r="X7" s="60"/>
+      <c r="Y7" s="60"/>
+      <c r="Z7" s="134">
         <v>4</v>
       </c>
-      <c r="AA7" s="75"/>
-      <c r="AB7" s="75"/>
-      <c r="AC7" s="75"/>
-      <c r="AD7" s="75"/>
-      <c r="AE7" s="75">
+      <c r="AA7" s="60"/>
+      <c r="AB7" s="60"/>
+      <c r="AC7" s="60"/>
+      <c r="AD7" s="60"/>
+      <c r="AE7" s="132">
         <v>4</v>
       </c>
-      <c r="AF7" s="75"/>
-      <c r="AG7" s="75"/>
-      <c r="AH7" s="75"/>
-      <c r="AI7" s="120"/>
-      <c r="AJ7" s="75"/>
-      <c r="AK7" s="75"/>
-      <c r="AL7" s="75"/>
-      <c r="AM7" s="75"/>
-      <c r="AN7" s="75"/>
-      <c r="AO7" s="75"/>
-      <c r="AP7" s="75"/>
-      <c r="AQ7" s="75"/>
-      <c r="AR7" s="75"/>
-      <c r="AS7" s="75"/>
-      <c r="AT7" s="75"/>
-      <c r="AU7" s="75"/>
-      <c r="AV7" s="75"/>
-      <c r="AW7" s="75"/>
-      <c r="AX7" s="75"/>
-      <c r="AY7" s="75"/>
-      <c r="AZ7" s="75"/>
-      <c r="BA7" s="75"/>
-      <c r="BB7" s="75"/>
-      <c r="BC7" s="75"/>
-      <c r="BD7" s="75"/>
-      <c r="BE7" s="75"/>
-      <c r="BF7" s="75"/>
-      <c r="BG7" s="75"/>
+      <c r="AF7" s="60">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="60"/>
+      <c r="AH7" s="60"/>
+      <c r="AI7" s="80"/>
+      <c r="AJ7" s="60"/>
+      <c r="AK7" s="60"/>
+      <c r="AL7" s="60"/>
+      <c r="AM7" s="60"/>
+      <c r="AN7" s="60"/>
+      <c r="AO7" s="60"/>
+      <c r="AP7" s="60"/>
+      <c r="AQ7" s="60"/>
+      <c r="AR7" s="60"/>
+      <c r="AS7" s="60"/>
+      <c r="AT7" s="60"/>
+      <c r="AU7" s="60"/>
+      <c r="AV7" s="60"/>
+      <c r="AW7" s="60"/>
+      <c r="AX7" s="60"/>
+      <c r="AY7" s="60"/>
+      <c r="AZ7" s="60"/>
+      <c r="BA7" s="60"/>
+      <c r="BB7" s="60"/>
+      <c r="BC7" s="60"/>
+      <c r="BD7" s="60"/>
+      <c r="BE7" s="60"/>
+      <c r="BF7" s="60"/>
+      <c r="BG7" s="60"/>
     </row>
-    <row r="8" spans="1:59" ht="43.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="76" t="s">
+    <row r="8" spans="1:277" ht="43.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="77" t="s">
+      <c r="B8" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="78">
+      <c r="C8" s="63">
         <v>1908</v>
       </c>
-      <c r="D8" s="79" t="s">
+      <c r="D8" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="80">
+      <c r="E8" s="115">
         <v>27</v>
       </c>
-      <c r="F8" s="81">
+      <c r="F8" s="104">
         <v>92</v>
       </c>
-      <c r="G8" s="81">
+      <c r="G8" s="104">
         <v>90</v>
       </c>
-      <c r="H8" s="81">
+      <c r="H8" s="104">
         <v>42</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="104">
         <v>25</v>
       </c>
-      <c r="J8" s="81">
+      <c r="J8" s="104">
         <v>12</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="65">
         <v>2</v>
       </c>
-      <c r="L8" s="81">
+      <c r="L8" s="65">
         <v>1</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="104">
         <v>5</v>
       </c>
-      <c r="N8" s="57">
+      <c r="N8" s="48">
         <v>9</v>
       </c>
-      <c r="O8" s="57">
+      <c r="O8" s="48">
         <v>5</v>
       </c>
-      <c r="P8" s="82">
+      <c r="P8" s="66">
         <v>5</v>
       </c>
-      <c r="Q8" s="57">
+      <c r="Q8" s="48">
         <v>6</v>
       </c>
-      <c r="R8" s="57">
+      <c r="R8" s="48">
         <v>1</v>
       </c>
-      <c r="S8" s="57">
+      <c r="S8" s="48">
         <v>2</v>
       </c>
-      <c r="T8" s="57"/>
-      <c r="U8" s="57"/>
-      <c r="V8" s="57"/>
-      <c r="W8" s="57"/>
-      <c r="X8" s="57"/>
-      <c r="Y8" s="57"/>
-      <c r="Z8" s="121">
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="48"/>
+      <c r="X8" s="48"/>
+      <c r="Y8" s="48"/>
+      <c r="Z8" s="81">
         <v>2</v>
       </c>
-      <c r="AA8" s="57">
+      <c r="AA8" s="48">
         <v>2</v>
       </c>
-      <c r="AB8" s="47">
+      <c r="AB8" s="129">
         <v>4</v>
       </c>
-      <c r="AC8" s="57">
+      <c r="AC8" s="135">
         <v>4</v>
       </c>
-      <c r="AD8" s="57">
+      <c r="AD8" s="48">
         <v>1</v>
       </c>
-      <c r="AE8" s="57"/>
-      <c r="AF8" s="57">
+      <c r="AE8" s="48"/>
+      <c r="AF8" s="48">
         <v>1</v>
       </c>
-      <c r="AG8" s="47"/>
-      <c r="AH8" s="47">
+      <c r="AG8" s="42"/>
+      <c r="AH8" s="42">
         <v>1</v>
       </c>
-      <c r="AI8" s="47"/>
-      <c r="AJ8" s="47">
+      <c r="AI8" s="42"/>
+      <c r="AJ8" s="42">
         <v>1</v>
       </c>
-      <c r="AK8" s="57">
+      <c r="AK8" s="135">
         <v>2</v>
       </c>
-      <c r="AL8" s="47">
+      <c r="AL8" s="42">
         <v>1</v>
       </c>
-      <c r="AM8" s="47">
+      <c r="AM8" s="129">
         <v>2</v>
       </c>
-      <c r="AN8" s="47">
+      <c r="AN8" s="129">
         <v>2</v>
       </c>
-      <c r="AO8" s="47">
+      <c r="AO8" s="129">
         <v>2</v>
       </c>
-      <c r="AP8" s="47">
+      <c r="AP8" s="42">
         <v>1</v>
       </c>
-      <c r="AQ8" s="47"/>
-      <c r="AR8" s="47"/>
-      <c r="AS8" s="47"/>
-      <c r="AT8" s="47"/>
-      <c r="AU8" s="47"/>
-      <c r="AV8" s="47"/>
-      <c r="AW8" s="47"/>
-      <c r="AX8" s="57"/>
-      <c r="AY8" s="47">
+      <c r="AQ8" s="42"/>
+      <c r="AR8" s="42"/>
+      <c r="AS8" s="42"/>
+      <c r="AT8" s="42"/>
+      <c r="AU8" s="42"/>
+      <c r="AV8" s="42"/>
+      <c r="AW8" s="42"/>
+      <c r="AX8" s="48"/>
+      <c r="AY8" s="42">
         <v>1</v>
       </c>
-      <c r="AZ8" s="47">
+      <c r="AZ8" s="42">
         <v>1</v>
       </c>
-      <c r="BA8" s="47">
+      <c r="BA8" s="42">
         <v>1</v>
       </c>
-      <c r="BB8" s="47"/>
-      <c r="BC8" s="47"/>
-      <c r="BD8" s="47"/>
-      <c r="BE8" s="47"/>
-      <c r="BF8" s="47"/>
-      <c r="BG8" s="47"/>
+      <c r="BB8" s="42"/>
+      <c r="BC8" s="42"/>
+      <c r="BD8" s="42"/>
+      <c r="BE8" s="42"/>
+      <c r="BF8" s="42"/>
+      <c r="BG8" s="42"/>
     </row>
-    <row r="9" spans="1:59" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="83" t="s">
+    <row r="9" spans="1:277" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="30">
         <v>1908</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="54">
+      <c r="E9" s="116">
         <v>16</v>
       </c>
-      <c r="F9" s="45">
+      <c r="F9" s="105">
         <v>62</v>
       </c>
-      <c r="G9" s="45">
+      <c r="G9" s="105">
         <v>16</v>
       </c>
-      <c r="H9" s="45">
+      <c r="H9" s="105">
         <v>55</v>
       </c>
-      <c r="I9" s="45">
+      <c r="I9" s="40">
         <v>2</v>
       </c>
-      <c r="J9" s="45">
+      <c r="J9" s="40">
         <v>1</v>
       </c>
-      <c r="K9" s="45"/>
-      <c r="L9" s="45">
+      <c r="K9" s="40"/>
+      <c r="L9" s="105">
         <v>4</v>
       </c>
-      <c r="M9" s="45"/>
-      <c r="N9" s="49">
+      <c r="M9" s="40"/>
+      <c r="N9" s="131">
         <v>33</v>
       </c>
-      <c r="O9" s="49">
+      <c r="O9" s="131">
         <v>14</v>
       </c>
-      <c r="P9" s="50"/>
-      <c r="Q9" s="49">
+      <c r="P9" s="45"/>
+      <c r="Q9" s="131">
         <v>10</v>
       </c>
-      <c r="R9" s="49"/>
-      <c r="S9" s="49">
+      <c r="R9" s="44"/>
+      <c r="S9" s="44">
         <v>1</v>
       </c>
-      <c r="T9" s="49"/>
-      <c r="U9" s="49"/>
-      <c r="V9" s="49"/>
-      <c r="W9" s="49"/>
-      <c r="X9" s="49"/>
-      <c r="Y9" s="49"/>
-      <c r="Z9" s="122"/>
-      <c r="AA9" s="49"/>
-      <c r="AB9" s="46"/>
-      <c r="AC9" s="49"/>
-      <c r="AD9" s="49"/>
-      <c r="AE9" s="49"/>
-      <c r="AF9" s="49"/>
-      <c r="AG9" s="46"/>
-      <c r="AH9" s="46"/>
-      <c r="AI9" s="46"/>
-      <c r="AJ9" s="46"/>
-      <c r="AK9" s="49"/>
-      <c r="AL9" s="46"/>
-      <c r="AM9" s="46"/>
-      <c r="AN9" s="46"/>
-      <c r="AO9" s="46"/>
-      <c r="AP9" s="46"/>
-      <c r="AQ9" s="46"/>
-      <c r="AR9" s="46"/>
-      <c r="AS9" s="46"/>
-      <c r="AT9" s="46"/>
-      <c r="AU9" s="46"/>
-      <c r="AV9" s="46"/>
-      <c r="AW9" s="46"/>
-      <c r="AX9" s="49"/>
-      <c r="AY9" s="46"/>
-      <c r="AZ9" s="46"/>
-      <c r="BA9" s="46"/>
-      <c r="BB9" s="46"/>
-      <c r="BC9" s="46"/>
-      <c r="BD9" s="46"/>
-      <c r="BE9" s="46"/>
-      <c r="BF9" s="46"/>
-      <c r="BG9" s="46"/>
+      <c r="T9" s="44"/>
+      <c r="U9" s="44"/>
+      <c r="V9" s="44"/>
+      <c r="W9" s="44"/>
+      <c r="X9" s="44"/>
+      <c r="Y9" s="44"/>
+      <c r="Z9" s="82"/>
+      <c r="AA9" s="44"/>
+      <c r="AB9" s="41"/>
+      <c r="AC9" s="44"/>
+      <c r="AD9" s="44"/>
+      <c r="AE9" s="44"/>
+      <c r="AF9" s="44"/>
+      <c r="AG9" s="41"/>
+      <c r="AH9" s="41"/>
+      <c r="AI9" s="41"/>
+      <c r="AJ9" s="41"/>
+      <c r="AK9" s="44"/>
+      <c r="AL9" s="41"/>
+      <c r="AM9" s="41"/>
+      <c r="AN9" s="41"/>
+      <c r="AO9" s="41"/>
+      <c r="AP9" s="41"/>
+      <c r="AQ9" s="41"/>
+      <c r="AR9" s="41"/>
+      <c r="AS9" s="41"/>
+      <c r="AT9" s="41"/>
+      <c r="AU9" s="41"/>
+      <c r="AV9" s="41"/>
+      <c r="AW9" s="41"/>
+      <c r="AX9" s="44"/>
+      <c r="AY9" s="41"/>
+      <c r="AZ9" s="41"/>
+      <c r="BA9" s="41"/>
+      <c r="BB9" s="41"/>
+      <c r="BC9" s="41"/>
+      <c r="BD9" s="41"/>
+      <c r="BE9" s="41"/>
+      <c r="BF9" s="41"/>
+      <c r="BG9" s="41"/>
     </row>
-    <row r="10" spans="1:59" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="68" t="s">
+    <row r="10" spans="1:277" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="53" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="36" t="s">
         <v>100</v>
       </c>
       <c r="C10" s="32">
         <v>1909</v>
       </c>
-      <c r="D10" s="40" t="s">
+      <c r="D10" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="52">
+      <c r="E10" s="47">
         <v>1</v>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="105">
         <v>34</v>
       </c>
-      <c r="G10" s="42">
+      <c r="G10" s="105">
         <v>17</v>
       </c>
-      <c r="H10" s="42">
+      <c r="H10" s="105">
         <v>18</v>
       </c>
-      <c r="I10" s="42">
+      <c r="I10" s="105">
         <v>14</v>
       </c>
-      <c r="J10" s="42">
+      <c r="J10" s="38">
         <v>6</v>
       </c>
-      <c r="K10" s="42">
+      <c r="K10" s="38">
         <v>1</v>
       </c>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="46"/>
-      <c r="O10" s="46">
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41">
         <v>0</v>
       </c>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="46">
+      <c r="P10" s="46"/>
+      <c r="Q10" s="41">
         <v>3</v>
       </c>
-      <c r="R10" s="46"/>
-      <c r="S10" s="46">
+      <c r="R10" s="41"/>
+      <c r="S10" s="41">
         <v>1</v>
       </c>
-      <c r="T10" s="46"/>
-      <c r="U10" s="46"/>
-      <c r="V10" s="46"/>
-      <c r="W10" s="46"/>
-      <c r="X10" s="46"/>
-      <c r="Y10" s="46"/>
-      <c r="Z10" s="101"/>
-      <c r="AA10" s="46"/>
-      <c r="AB10" s="46"/>
-      <c r="AC10" s="46"/>
-      <c r="AD10" s="46">
+      <c r="T10" s="41"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="41"/>
+      <c r="W10" s="41"/>
+      <c r="X10" s="41"/>
+      <c r="Y10" s="41"/>
+      <c r="Z10" s="77"/>
+      <c r="AA10" s="41"/>
+      <c r="AB10" s="41"/>
+      <c r="AC10" s="41"/>
+      <c r="AD10" s="131">
         <v>2</v>
       </c>
-      <c r="AE10" s="46"/>
-      <c r="AF10" s="46"/>
-      <c r="AG10" s="46"/>
-      <c r="AH10" s="46"/>
-      <c r="AI10" s="46"/>
-      <c r="AJ10" s="46">
+      <c r="AE10" s="41"/>
+      <c r="AF10" s="41"/>
+      <c r="AG10" s="41"/>
+      <c r="AH10" s="41"/>
+      <c r="AI10" s="41"/>
+      <c r="AJ10" s="131">
         <v>2</v>
       </c>
-      <c r="AK10" s="46"/>
-      <c r="AL10" s="46"/>
-      <c r="AM10" s="46"/>
-      <c r="AN10" s="46"/>
-      <c r="AO10" s="46"/>
-      <c r="AP10" s="46"/>
-      <c r="AQ10" s="46">
+      <c r="AK10" s="41"/>
+      <c r="AL10" s="41"/>
+      <c r="AM10" s="41"/>
+      <c r="AN10" s="41"/>
+      <c r="AO10" s="41"/>
+      <c r="AP10" s="41"/>
+      <c r="AQ10" s="41">
         <v>1</v>
       </c>
-      <c r="AR10" s="46"/>
-      <c r="AS10" s="46"/>
-      <c r="AT10" s="46"/>
-      <c r="AU10" s="46"/>
-      <c r="AV10" s="46"/>
-      <c r="AW10" s="46"/>
-      <c r="AX10" s="46"/>
-      <c r="AY10" s="46"/>
-      <c r="AZ10" s="46"/>
-      <c r="BA10" s="46"/>
-      <c r="BB10" s="46">
+      <c r="AR10" s="41"/>
+      <c r="AS10" s="41"/>
+      <c r="AT10" s="41"/>
+      <c r="AU10" s="41"/>
+      <c r="AV10" s="41"/>
+      <c r="AW10" s="41"/>
+      <c r="AX10" s="41"/>
+      <c r="AY10" s="41"/>
+      <c r="AZ10" s="41"/>
+      <c r="BA10" s="41"/>
+      <c r="BB10" s="41">
         <v>1</v>
       </c>
-      <c r="BC10" s="46"/>
-      <c r="BD10" s="46"/>
-      <c r="BE10" s="46"/>
-      <c r="BF10" s="46"/>
-      <c r="BG10" s="46"/>
+      <c r="BC10" s="41"/>
+      <c r="BD10" s="41"/>
+      <c r="BE10" s="41"/>
+      <c r="BF10" s="41"/>
+      <c r="BG10" s="77"/>
+      <c r="BH10" s="103"/>
+      <c r="BI10" s="103"/>
+      <c r="BJ10" s="103"/>
+      <c r="BK10" s="103"/>
+      <c r="BL10" s="103"/>
+      <c r="BM10" s="103"/>
+      <c r="BN10" s="103"/>
+      <c r="BO10" s="103"/>
+      <c r="BP10" s="103"/>
+      <c r="BQ10" s="103"/>
+      <c r="BR10" s="103"/>
+      <c r="BS10" s="103"/>
+      <c r="BT10" s="103"/>
+      <c r="BU10" s="103"/>
+      <c r="BV10" s="103"/>
+      <c r="BW10" s="103"/>
+      <c r="BX10" s="103"/>
+      <c r="BY10" s="103"/>
+      <c r="BZ10" s="103"/>
+      <c r="CA10" s="103"/>
+      <c r="CB10" s="103"/>
+      <c r="CC10" s="103"/>
+      <c r="CD10" s="103"/>
+      <c r="CE10" s="103"/>
+      <c r="CF10" s="103"/>
+      <c r="CG10" s="103"/>
+      <c r="CH10" s="103"/>
+      <c r="CI10" s="103"/>
+      <c r="CJ10" s="103"/>
+      <c r="CK10" s="103"/>
+      <c r="CL10" s="103"/>
+      <c r="CM10" s="103"/>
+      <c r="CN10" s="103"/>
+      <c r="CO10" s="103"/>
+      <c r="CP10" s="103"/>
+      <c r="CQ10" s="103"/>
+      <c r="CR10" s="103"/>
+      <c r="CS10" s="103"/>
+      <c r="CT10" s="103"/>
+      <c r="CU10" s="103"/>
+      <c r="CV10" s="103"/>
+      <c r="CW10" s="103"/>
+      <c r="CX10" s="103"/>
+      <c r="CY10" s="103"/>
+      <c r="CZ10" s="103"/>
+      <c r="DA10" s="103"/>
+      <c r="DB10" s="103"/>
+      <c r="DC10" s="103"/>
+      <c r="DD10" s="103"/>
+      <c r="DE10" s="103"/>
+      <c r="DF10" s="103"/>
+      <c r="DG10" s="103"/>
+      <c r="DH10" s="103"/>
+      <c r="DI10" s="103"/>
+      <c r="DJ10" s="103"/>
+      <c r="DK10" s="103"/>
+      <c r="DL10" s="103"/>
+      <c r="DM10" s="103"/>
+      <c r="DN10" s="103"/>
+      <c r="DO10" s="103"/>
+      <c r="DP10" s="103"/>
+      <c r="DQ10" s="103"/>
+      <c r="DR10" s="103"/>
+      <c r="DS10" s="103"/>
+      <c r="DT10" s="103"/>
+      <c r="DU10" s="103"/>
+      <c r="DV10" s="103"/>
+      <c r="DW10" s="103"/>
+      <c r="DX10" s="103"/>
+      <c r="DY10" s="103"/>
+      <c r="DZ10" s="103"/>
+      <c r="EA10" s="103"/>
+      <c r="EB10" s="103"/>
+      <c r="EC10" s="103"/>
+      <c r="ED10" s="103"/>
+      <c r="EE10" s="103"/>
+      <c r="EF10" s="103"/>
+      <c r="EG10" s="103"/>
+      <c r="EH10" s="103"/>
+      <c r="EI10" s="103"/>
+      <c r="EJ10" s="103"/>
+      <c r="EK10" s="103"/>
+      <c r="EL10" s="103"/>
+      <c r="EM10" s="103"/>
+      <c r="EN10" s="103"/>
+      <c r="EO10" s="103"/>
+      <c r="EP10" s="103"/>
+      <c r="EQ10" s="103"/>
+      <c r="ER10" s="103"/>
+      <c r="ES10" s="103"/>
+      <c r="ET10" s="103"/>
+      <c r="EU10" s="103"/>
+      <c r="EV10" s="103"/>
+      <c r="EW10" s="103"/>
+      <c r="EX10" s="103"/>
+      <c r="EY10" s="103"/>
+      <c r="EZ10" s="103"/>
+      <c r="FA10" s="103"/>
+      <c r="FB10" s="103"/>
+      <c r="FC10" s="103"/>
+      <c r="FD10" s="103"/>
+      <c r="FE10" s="103"/>
+      <c r="FF10" s="103"/>
+      <c r="FG10" s="103"/>
+      <c r="FH10" s="103"/>
+      <c r="FI10" s="103"/>
+      <c r="FJ10" s="103"/>
+      <c r="FK10" s="103"/>
+      <c r="FL10" s="103"/>
+      <c r="FM10" s="103"/>
+      <c r="FN10" s="103"/>
+      <c r="FO10" s="103"/>
+      <c r="FP10" s="103"/>
+      <c r="FQ10" s="103"/>
+      <c r="FR10" s="103"/>
+      <c r="FS10" s="103"/>
+      <c r="FT10" s="103"/>
+      <c r="FU10" s="103"/>
+      <c r="FV10" s="103"/>
+      <c r="FW10" s="103"/>
+      <c r="FX10" s="103"/>
+      <c r="FY10" s="103"/>
+      <c r="FZ10" s="103"/>
+      <c r="GA10" s="103"/>
+      <c r="GB10" s="103"/>
+      <c r="GC10" s="103"/>
+      <c r="GD10" s="103"/>
+      <c r="GE10" s="103"/>
+      <c r="GF10" s="103"/>
+      <c r="GG10" s="103"/>
+      <c r="GH10" s="103"/>
+      <c r="GI10" s="103"/>
+      <c r="GJ10" s="103"/>
+      <c r="GK10" s="103"/>
+      <c r="GL10" s="103"/>
+      <c r="GM10" s="103"/>
+      <c r="GN10" s="103"/>
+      <c r="GO10" s="103"/>
+      <c r="GP10" s="103"/>
+      <c r="GQ10" s="103"/>
+      <c r="GR10" s="103"/>
+      <c r="GS10" s="103"/>
+      <c r="GT10" s="103"/>
+      <c r="GU10" s="103"/>
+      <c r="GV10" s="103"/>
+      <c r="GW10" s="103"/>
+      <c r="GX10" s="103"/>
+      <c r="GY10" s="103"/>
+      <c r="GZ10" s="103"/>
+      <c r="HA10" s="103"/>
+      <c r="HB10" s="103"/>
+      <c r="HC10" s="103"/>
+      <c r="HD10" s="103"/>
+      <c r="HE10" s="103"/>
+      <c r="HF10" s="103"/>
+      <c r="HG10" s="103"/>
+      <c r="HH10" s="103"/>
+      <c r="HI10" s="103"/>
+      <c r="HJ10" s="103"/>
+      <c r="HK10" s="103"/>
+      <c r="HL10" s="103"/>
+      <c r="HM10" s="103"/>
+      <c r="HN10" s="103"/>
+      <c r="HO10" s="103"/>
+      <c r="HP10" s="103"/>
+      <c r="HQ10" s="103"/>
+      <c r="HR10" s="103"/>
+      <c r="HS10" s="103"/>
+      <c r="HT10" s="103"/>
+      <c r="HU10" s="103"/>
+      <c r="HV10" s="103"/>
+      <c r="HW10" s="103"/>
+      <c r="HX10" s="103"/>
+      <c r="HY10" s="103"/>
+      <c r="HZ10" s="103"/>
+      <c r="IA10" s="103"/>
+      <c r="IB10" s="103"/>
+      <c r="IC10" s="103"/>
+      <c r="ID10" s="103"/>
+      <c r="IE10" s="103"/>
+      <c r="IF10" s="103"/>
+      <c r="IG10" s="103"/>
+      <c r="IH10" s="103"/>
+      <c r="II10" s="103"/>
+      <c r="IJ10" s="103"/>
+      <c r="IK10" s="103"/>
+      <c r="IL10" s="103"/>
+      <c r="IM10" s="103"/>
+      <c r="IN10" s="103"/>
+      <c r="IO10" s="103"/>
+      <c r="IP10" s="103"/>
+      <c r="IQ10" s="103"/>
+      <c r="IR10" s="103"/>
+      <c r="IS10" s="103"/>
+      <c r="IT10" s="103"/>
+      <c r="IU10" s="103"/>
+      <c r="IV10" s="103"/>
+      <c r="IW10" s="103"/>
+      <c r="IX10" s="103"/>
+      <c r="IY10" s="103"/>
+      <c r="IZ10" s="103"/>
+      <c r="JA10" s="103"/>
+      <c r="JB10" s="103"/>
+      <c r="JC10" s="103"/>
+      <c r="JD10" s="103"/>
+      <c r="JE10" s="103"/>
+      <c r="JF10" s="103"/>
+      <c r="JG10" s="103"/>
+      <c r="JH10" s="103"/>
+      <c r="JI10" s="103"/>
+      <c r="JJ10" s="103"/>
+      <c r="JK10" s="103"/>
+      <c r="JL10" s="103"/>
+      <c r="JM10" s="103"/>
+      <c r="JN10" s="103"/>
+      <c r="JO10" s="103"/>
+      <c r="JP10" s="103"/>
+      <c r="JQ10" s="103"/>
     </row>
-    <row r="11" spans="1:59" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="84" t="s">
-        <v>74</v>
+    <row r="11" spans="1:277" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="67" t="s">
+        <v>157</v>
       </c>
       <c r="B11" s="29" t="s">
         <v>11</v>
@@ -3318,82 +3490,300 @@
       <c r="C11" s="32">
         <v>1909</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="D11" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="52">
+      <c r="E11" s="47">
         <v>3</v>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="105">
         <v>18</v>
       </c>
-      <c r="G11" s="42">
+      <c r="G11" s="105">
         <v>12</v>
       </c>
-      <c r="H11" s="42">
+      <c r="H11" s="105">
         <v>12</v>
       </c>
-      <c r="I11" s="42">
+      <c r="I11" s="38">
         <v>9</v>
       </c>
-      <c r="J11" s="42">
+      <c r="J11" s="105">
         <v>11</v>
       </c>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="46">
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="41">
         <v>1</v>
       </c>
-      <c r="O11" s="46"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="46">
+      <c r="O11" s="41"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="41">
         <v>1</v>
       </c>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="46"/>
-      <c r="V11" s="46"/>
-      <c r="W11" s="46"/>
-      <c r="X11" s="46"/>
-      <c r="Y11" s="46"/>
-      <c r="Z11" s="101"/>
-      <c r="AA11" s="46"/>
-      <c r="AB11" s="46"/>
-      <c r="AC11" s="46"/>
-      <c r="AD11" s="46"/>
-      <c r="AE11" s="46"/>
-      <c r="AF11" s="46"/>
-      <c r="AG11" s="46"/>
-      <c r="AH11" s="46"/>
-      <c r="AI11" s="46"/>
-      <c r="AJ11" s="46"/>
-      <c r="AK11" s="46"/>
-      <c r="AL11" s="46"/>
-      <c r="AM11" s="46"/>
-      <c r="AN11" s="46"/>
-      <c r="AO11" s="46"/>
-      <c r="AP11" s="46"/>
-      <c r="AQ11" s="46"/>
-      <c r="AR11" s="46"/>
-      <c r="AS11" s="46"/>
-      <c r="AT11" s="46"/>
-      <c r="AU11" s="46"/>
-      <c r="AV11" s="46"/>
-      <c r="AW11" s="46"/>
-      <c r="AX11" s="46"/>
-      <c r="AY11" s="46"/>
-      <c r="AZ11" s="46"/>
-      <c r="BA11" s="46"/>
-      <c r="BB11" s="46"/>
-      <c r="BC11" s="46"/>
-      <c r="BD11" s="46"/>
-      <c r="BE11" s="46"/>
-      <c r="BF11" s="46"/>
-      <c r="BG11" s="46"/>
+      <c r="R11" s="41"/>
+      <c r="S11" s="41"/>
+      <c r="T11" s="41"/>
+      <c r="U11" s="41"/>
+      <c r="V11" s="41"/>
+      <c r="W11" s="41"/>
+      <c r="X11" s="41"/>
+      <c r="Y11" s="41"/>
+      <c r="Z11" s="77"/>
+      <c r="AA11" s="41"/>
+      <c r="AB11" s="41"/>
+      <c r="AC11" s="41"/>
+      <c r="AD11" s="41"/>
+      <c r="AE11" s="41"/>
+      <c r="AF11" s="41"/>
+      <c r="AG11" s="41"/>
+      <c r="AH11" s="41"/>
+      <c r="AI11" s="41"/>
+      <c r="AJ11" s="41"/>
+      <c r="AK11" s="41"/>
+      <c r="AL11" s="41"/>
+      <c r="AM11" s="41"/>
+      <c r="AN11" s="41"/>
+      <c r="AO11" s="41"/>
+      <c r="AP11" s="41"/>
+      <c r="AQ11" s="41"/>
+      <c r="AR11" s="41"/>
+      <c r="AS11" s="41"/>
+      <c r="AT11" s="41"/>
+      <c r="AU11" s="41"/>
+      <c r="AV11" s="41"/>
+      <c r="AW11" s="41"/>
+      <c r="AX11" s="41"/>
+      <c r="AY11" s="41"/>
+      <c r="AZ11" s="41"/>
+      <c r="BA11" s="41"/>
+      <c r="BB11" s="41"/>
+      <c r="BC11" s="41"/>
+      <c r="BD11" s="41"/>
+      <c r="BE11" s="41"/>
+      <c r="BF11" s="41"/>
+      <c r="BG11" s="77"/>
+      <c r="BH11" s="103"/>
+      <c r="BI11" s="103"/>
+      <c r="BJ11" s="103"/>
+      <c r="BK11" s="103"/>
+      <c r="BL11" s="103"/>
+      <c r="BM11" s="103"/>
+      <c r="BN11" s="103"/>
+      <c r="BO11" s="103"/>
+      <c r="BP11" s="103"/>
+      <c r="BQ11" s="103"/>
+      <c r="BR11" s="103"/>
+      <c r="BS11" s="103"/>
+      <c r="BT11" s="103"/>
+      <c r="BU11" s="103"/>
+      <c r="BV11" s="103"/>
+      <c r="BW11" s="103"/>
+      <c r="BX11" s="103"/>
+      <c r="BY11" s="103"/>
+      <c r="BZ11" s="103"/>
+      <c r="CA11" s="103"/>
+      <c r="CB11" s="103"/>
+      <c r="CC11" s="103"/>
+      <c r="CD11" s="103"/>
+      <c r="CE11" s="103"/>
+      <c r="CF11" s="103"/>
+      <c r="CG11" s="103"/>
+      <c r="CH11" s="103"/>
+      <c r="CI11" s="103"/>
+      <c r="CJ11" s="103"/>
+      <c r="CK11" s="103"/>
+      <c r="CL11" s="103"/>
+      <c r="CM11" s="103"/>
+      <c r="CN11" s="103"/>
+      <c r="CO11" s="103"/>
+      <c r="CP11" s="103"/>
+      <c r="CQ11" s="103"/>
+      <c r="CR11" s="103"/>
+      <c r="CS11" s="103"/>
+      <c r="CT11" s="103"/>
+      <c r="CU11" s="103"/>
+      <c r="CV11" s="103"/>
+      <c r="CW11" s="103"/>
+      <c r="CX11" s="103"/>
+      <c r="CY11" s="103"/>
+      <c r="CZ11" s="103"/>
+      <c r="DA11" s="103"/>
+      <c r="DB11" s="103"/>
+      <c r="DC11" s="103"/>
+      <c r="DD11" s="103"/>
+      <c r="DE11" s="103"/>
+      <c r="DF11" s="103"/>
+      <c r="DG11" s="103"/>
+      <c r="DH11" s="103"/>
+      <c r="DI11" s="103"/>
+      <c r="DJ11" s="103"/>
+      <c r="DK11" s="103"/>
+      <c r="DL11" s="103"/>
+      <c r="DM11" s="103"/>
+      <c r="DN11" s="103"/>
+      <c r="DO11" s="103"/>
+      <c r="DP11" s="103"/>
+      <c r="DQ11" s="103"/>
+      <c r="DR11" s="103"/>
+      <c r="DS11" s="103"/>
+      <c r="DT11" s="103"/>
+      <c r="DU11" s="103"/>
+      <c r="DV11" s="103"/>
+      <c r="DW11" s="103"/>
+      <c r="DX11" s="103"/>
+      <c r="DY11" s="103"/>
+      <c r="DZ11" s="103"/>
+      <c r="EA11" s="103"/>
+      <c r="EB11" s="103"/>
+      <c r="EC11" s="103"/>
+      <c r="ED11" s="103"/>
+      <c r="EE11" s="103"/>
+      <c r="EF11" s="103"/>
+      <c r="EG11" s="103"/>
+      <c r="EH11" s="103"/>
+      <c r="EI11" s="103"/>
+      <c r="EJ11" s="103"/>
+      <c r="EK11" s="103"/>
+      <c r="EL11" s="103"/>
+      <c r="EM11" s="103"/>
+      <c r="EN11" s="103"/>
+      <c r="EO11" s="103"/>
+      <c r="EP11" s="103"/>
+      <c r="EQ11" s="103"/>
+      <c r="ER11" s="103"/>
+      <c r="ES11" s="103"/>
+      <c r="ET11" s="103"/>
+      <c r="EU11" s="103"/>
+      <c r="EV11" s="103"/>
+      <c r="EW11" s="103"/>
+      <c r="EX11" s="103"/>
+      <c r="EY11" s="103"/>
+      <c r="EZ11" s="103"/>
+      <c r="FA11" s="103"/>
+      <c r="FB11" s="103"/>
+      <c r="FC11" s="103"/>
+      <c r="FD11" s="103"/>
+      <c r="FE11" s="103"/>
+      <c r="FF11" s="103"/>
+      <c r="FG11" s="103"/>
+      <c r="FH11" s="103"/>
+      <c r="FI11" s="103"/>
+      <c r="FJ11" s="103"/>
+      <c r="FK11" s="103"/>
+      <c r="FL11" s="103"/>
+      <c r="FM11" s="103"/>
+      <c r="FN11" s="103"/>
+      <c r="FO11" s="103"/>
+      <c r="FP11" s="103"/>
+      <c r="FQ11" s="103"/>
+      <c r="FR11" s="103"/>
+      <c r="FS11" s="103"/>
+      <c r="FT11" s="103"/>
+      <c r="FU11" s="103"/>
+      <c r="FV11" s="103"/>
+      <c r="FW11" s="103"/>
+      <c r="FX11" s="103"/>
+      <c r="FY11" s="103"/>
+      <c r="FZ11" s="103"/>
+      <c r="GA11" s="103"/>
+      <c r="GB11" s="103"/>
+      <c r="GC11" s="103"/>
+      <c r="GD11" s="103"/>
+      <c r="GE11" s="103"/>
+      <c r="GF11" s="103"/>
+      <c r="GG11" s="103"/>
+      <c r="GH11" s="103"/>
+      <c r="GI11" s="103"/>
+      <c r="GJ11" s="103"/>
+      <c r="GK11" s="103"/>
+      <c r="GL11" s="103"/>
+      <c r="GM11" s="103"/>
+      <c r="GN11" s="103"/>
+      <c r="GO11" s="103"/>
+      <c r="GP11" s="103"/>
+      <c r="GQ11" s="103"/>
+      <c r="GR11" s="103"/>
+      <c r="GS11" s="103"/>
+      <c r="GT11" s="103"/>
+      <c r="GU11" s="103"/>
+      <c r="GV11" s="103"/>
+      <c r="GW11" s="103"/>
+      <c r="GX11" s="103"/>
+      <c r="GY11" s="103"/>
+      <c r="GZ11" s="103"/>
+      <c r="HA11" s="103"/>
+      <c r="HB11" s="103"/>
+      <c r="HC11" s="103"/>
+      <c r="HD11" s="103"/>
+      <c r="HE11" s="103"/>
+      <c r="HF11" s="103"/>
+      <c r="HG11" s="103"/>
+      <c r="HH11" s="103"/>
+      <c r="HI11" s="103"/>
+      <c r="HJ11" s="103"/>
+      <c r="HK11" s="103"/>
+      <c r="HL11" s="103"/>
+      <c r="HM11" s="103"/>
+      <c r="HN11" s="103"/>
+      <c r="HO11" s="103"/>
+      <c r="HP11" s="103"/>
+      <c r="HQ11" s="103"/>
+      <c r="HR11" s="103"/>
+      <c r="HS11" s="103"/>
+      <c r="HT11" s="103"/>
+      <c r="HU11" s="103"/>
+      <c r="HV11" s="103"/>
+      <c r="HW11" s="103"/>
+      <c r="HX11" s="103"/>
+      <c r="HY11" s="103"/>
+      <c r="HZ11" s="103"/>
+      <c r="IA11" s="103"/>
+      <c r="IB11" s="103"/>
+      <c r="IC11" s="103"/>
+      <c r="ID11" s="103"/>
+      <c r="IE11" s="103"/>
+      <c r="IF11" s="103"/>
+      <c r="IG11" s="103"/>
+      <c r="IH11" s="103"/>
+      <c r="II11" s="103"/>
+      <c r="IJ11" s="103"/>
+      <c r="IK11" s="103"/>
+      <c r="IL11" s="103"/>
+      <c r="IM11" s="103"/>
+      <c r="IN11" s="103"/>
+      <c r="IO11" s="103"/>
+      <c r="IP11" s="103"/>
+      <c r="IQ11" s="103"/>
+      <c r="IR11" s="103"/>
+      <c r="IS11" s="103"/>
+      <c r="IT11" s="103"/>
+      <c r="IU11" s="103"/>
+      <c r="IV11" s="103"/>
+      <c r="IW11" s="103"/>
+      <c r="IX11" s="103"/>
+      <c r="IY11" s="103"/>
+      <c r="IZ11" s="103"/>
+      <c r="JA11" s="103"/>
+      <c r="JB11" s="103"/>
+      <c r="JC11" s="103"/>
+      <c r="JD11" s="103"/>
+      <c r="JE11" s="103"/>
+      <c r="JF11" s="103"/>
+      <c r="JG11" s="103"/>
+      <c r="JH11" s="103"/>
+      <c r="JI11" s="103"/>
+      <c r="JJ11" s="103"/>
+      <c r="JK11" s="103"/>
+      <c r="JL11" s="103"/>
+      <c r="JM11" s="103"/>
+      <c r="JN11" s="103"/>
+      <c r="JO11" s="103"/>
+      <c r="JP11" s="103"/>
+      <c r="JQ11" s="103"/>
     </row>
-    <row r="12" spans="1:59" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:277" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="32" t="s">
         <v>98</v>
       </c>
@@ -3403,381 +3793,1253 @@
       <c r="C12" s="30">
         <v>1910</v>
       </c>
-      <c r="D12" s="40" t="s">
+      <c r="D12" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="52">
+      <c r="E12" s="116">
         <v>13</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="105">
         <v>12</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="38">
         <v>3</v>
       </c>
-      <c r="H12" s="42">
+      <c r="H12" s="38">
         <v>6</v>
       </c>
-      <c r="I12" s="42">
+      <c r="I12" s="38">
         <v>4</v>
       </c>
-      <c r="J12" s="42">
+      <c r="J12" s="38">
         <v>2</v>
       </c>
-      <c r="K12" s="42">
+      <c r="K12" s="38">
         <v>5</v>
       </c>
-      <c r="L12" s="42">
+      <c r="L12" s="38">
         <v>1</v>
       </c>
-      <c r="M12" s="42"/>
-      <c r="N12" s="46">
+      <c r="M12" s="38"/>
+      <c r="N12" s="41">
         <v>9</v>
       </c>
-      <c r="O12" s="46"/>
-      <c r="P12" s="51">
+      <c r="O12" s="41"/>
+      <c r="P12" s="133">
         <v>9</v>
       </c>
-      <c r="Q12" s="46"/>
-      <c r="R12" s="46"/>
-      <c r="S12" s="46"/>
-      <c r="T12" s="46">
+      <c r="Q12" s="41"/>
+      <c r="R12" s="41"/>
+      <c r="S12" s="41"/>
+      <c r="T12" s="41">
         <v>2</v>
       </c>
-      <c r="U12" s="46"/>
-      <c r="V12" s="46">
+      <c r="U12" s="41"/>
+      <c r="V12" s="131">
         <v>14</v>
       </c>
-      <c r="W12" s="46">
+      <c r="W12" s="41">
         <v>1</v>
       </c>
-      <c r="X12" s="46"/>
-      <c r="Y12" s="46"/>
-      <c r="Z12" s="101"/>
-      <c r="AA12" s="46"/>
-      <c r="AB12" s="46">
+      <c r="X12" s="41"/>
+      <c r="Y12" s="41"/>
+      <c r="Z12" s="77"/>
+      <c r="AA12" s="41"/>
+      <c r="AB12" s="41">
         <v>2</v>
       </c>
-      <c r="AC12" s="46"/>
-      <c r="AD12" s="46"/>
-      <c r="AE12" s="46"/>
-      <c r="AF12" s="46"/>
-      <c r="AG12" s="46">
+      <c r="AC12" s="41"/>
+      <c r="AD12" s="41"/>
+      <c r="AE12" s="41"/>
+      <c r="AF12" s="41"/>
+      <c r="AG12" s="41">
         <v>1</v>
       </c>
-      <c r="AH12" s="46">
+      <c r="AH12" s="131">
         <v>2</v>
       </c>
-      <c r="AI12" s="46"/>
-      <c r="AJ12" s="46"/>
-      <c r="AK12" s="46"/>
-      <c r="AL12" s="46"/>
-      <c r="AM12" s="46"/>
-      <c r="AN12" s="46"/>
-      <c r="AO12" s="46"/>
-      <c r="AP12" s="46">
+      <c r="AI12" s="41"/>
+      <c r="AJ12" s="41"/>
+      <c r="AK12" s="41"/>
+      <c r="AL12" s="41"/>
+      <c r="AM12" s="41"/>
+      <c r="AN12" s="41"/>
+      <c r="AO12" s="41"/>
+      <c r="AP12" s="41">
         <v>1</v>
       </c>
-      <c r="AQ12" s="46"/>
-      <c r="AR12" s="46">
+      <c r="AQ12" s="41"/>
+      <c r="AR12" s="41">
         <v>1</v>
       </c>
-      <c r="AS12" s="46"/>
-      <c r="AT12" s="46"/>
-      <c r="AU12" s="46"/>
-      <c r="AV12" s="46"/>
-      <c r="AW12" s="46"/>
-      <c r="AX12" s="46"/>
-      <c r="AY12" s="46"/>
-      <c r="AZ12" s="46"/>
-      <c r="BA12" s="46"/>
-      <c r="BB12" s="46"/>
-      <c r="BC12" s="46">
+      <c r="AS12" s="41"/>
+      <c r="AT12" s="41"/>
+      <c r="AU12" s="41"/>
+      <c r="AV12" s="41"/>
+      <c r="AW12" s="41"/>
+      <c r="AX12" s="41"/>
+      <c r="AY12" s="41"/>
+      <c r="AZ12" s="41"/>
+      <c r="BA12" s="41"/>
+      <c r="BB12" s="41"/>
+      <c r="BC12" s="41">
         <v>1</v>
       </c>
-      <c r="BD12" s="46">
+      <c r="BD12" s="41">
         <v>1</v>
       </c>
-      <c r="BE12" s="46">
+      <c r="BE12" s="41">
         <v>1</v>
       </c>
-      <c r="BF12" s="46"/>
-      <c r="BG12" s="46"/>
+      <c r="BF12" s="41"/>
+      <c r="BG12" s="77"/>
+      <c r="BH12" s="103"/>
+      <c r="BI12" s="103"/>
+      <c r="BJ12" s="103"/>
+      <c r="BK12" s="103"/>
+      <c r="BL12" s="103"/>
+      <c r="BM12" s="103"/>
+      <c r="BN12" s="103"/>
+      <c r="BO12" s="103"/>
+      <c r="BP12" s="103"/>
+      <c r="BQ12" s="103"/>
+      <c r="BR12" s="103"/>
+      <c r="BS12" s="103"/>
+      <c r="BT12" s="103"/>
+      <c r="BU12" s="103"/>
+      <c r="BV12" s="103"/>
+      <c r="BW12" s="103"/>
+      <c r="BX12" s="103"/>
+      <c r="BY12" s="103"/>
+      <c r="BZ12" s="103"/>
+      <c r="CA12" s="103"/>
+      <c r="CB12" s="103"/>
+      <c r="CC12" s="103"/>
+      <c r="CD12" s="103"/>
+      <c r="CE12" s="103"/>
+      <c r="CF12" s="103"/>
+      <c r="CG12" s="103"/>
+      <c r="CH12" s="103"/>
+      <c r="CI12" s="103"/>
+      <c r="CJ12" s="103"/>
+      <c r="CK12" s="103"/>
+      <c r="CL12" s="103"/>
+      <c r="CM12" s="103"/>
+      <c r="CN12" s="103"/>
+      <c r="CO12" s="103"/>
+      <c r="CP12" s="103"/>
+      <c r="CQ12" s="103"/>
+      <c r="CR12" s="103"/>
+      <c r="CS12" s="103"/>
+      <c r="CT12" s="103"/>
+      <c r="CU12" s="103"/>
+      <c r="CV12" s="103"/>
+      <c r="CW12" s="103"/>
+      <c r="CX12" s="103"/>
+      <c r="CY12" s="103"/>
+      <c r="CZ12" s="103"/>
+      <c r="DA12" s="103"/>
+      <c r="DB12" s="103"/>
+      <c r="DC12" s="103"/>
+      <c r="DD12" s="103"/>
+      <c r="DE12" s="103"/>
+      <c r="DF12" s="103"/>
+      <c r="DG12" s="103"/>
+      <c r="DH12" s="103"/>
+      <c r="DI12" s="103"/>
+      <c r="DJ12" s="103"/>
+      <c r="DK12" s="103"/>
+      <c r="DL12" s="103"/>
+      <c r="DM12" s="103"/>
+      <c r="DN12" s="103"/>
+      <c r="DO12" s="103"/>
+      <c r="DP12" s="103"/>
+      <c r="DQ12" s="103"/>
+      <c r="DR12" s="103"/>
+      <c r="DS12" s="103"/>
+      <c r="DT12" s="103"/>
+      <c r="DU12" s="103"/>
+      <c r="DV12" s="103"/>
+      <c r="DW12" s="103"/>
+      <c r="DX12" s="103"/>
+      <c r="DY12" s="103"/>
+      <c r="DZ12" s="103"/>
+      <c r="EA12" s="103"/>
+      <c r="EB12" s="103"/>
+      <c r="EC12" s="103"/>
+      <c r="ED12" s="103"/>
+      <c r="EE12" s="103"/>
+      <c r="EF12" s="103"/>
+      <c r="EG12" s="103"/>
+      <c r="EH12" s="103"/>
+      <c r="EI12" s="103"/>
+      <c r="EJ12" s="103"/>
+      <c r="EK12" s="103"/>
+      <c r="EL12" s="103"/>
+      <c r="EM12" s="103"/>
+      <c r="EN12" s="103"/>
+      <c r="EO12" s="103"/>
+      <c r="EP12" s="103"/>
+      <c r="EQ12" s="103"/>
+      <c r="ER12" s="103"/>
+      <c r="ES12" s="103"/>
+      <c r="ET12" s="103"/>
+      <c r="EU12" s="103"/>
+      <c r="EV12" s="103"/>
+      <c r="EW12" s="103"/>
+      <c r="EX12" s="103"/>
+      <c r="EY12" s="103"/>
+      <c r="EZ12" s="103"/>
+      <c r="FA12" s="103"/>
+      <c r="FB12" s="103"/>
+      <c r="FC12" s="103"/>
+      <c r="FD12" s="103"/>
+      <c r="FE12" s="103"/>
+      <c r="FF12" s="103"/>
+      <c r="FG12" s="103"/>
+      <c r="FH12" s="103"/>
+      <c r="FI12" s="103"/>
+      <c r="FJ12" s="103"/>
+      <c r="FK12" s="103"/>
+      <c r="FL12" s="103"/>
+      <c r="FM12" s="103"/>
+      <c r="FN12" s="103"/>
+      <c r="FO12" s="103"/>
+      <c r="FP12" s="103"/>
+      <c r="FQ12" s="103"/>
+      <c r="FR12" s="103"/>
+      <c r="FS12" s="103"/>
+      <c r="FT12" s="103"/>
+      <c r="FU12" s="103"/>
+      <c r="FV12" s="103"/>
+      <c r="FW12" s="103"/>
+      <c r="FX12" s="103"/>
+      <c r="FY12" s="103"/>
+      <c r="FZ12" s="103"/>
+      <c r="GA12" s="103"/>
+      <c r="GB12" s="103"/>
+      <c r="GC12" s="103"/>
+      <c r="GD12" s="103"/>
+      <c r="GE12" s="103"/>
+      <c r="GF12" s="103"/>
+      <c r="GG12" s="103"/>
+      <c r="GH12" s="103"/>
+      <c r="GI12" s="103"/>
+      <c r="GJ12" s="103"/>
+      <c r="GK12" s="103"/>
+      <c r="GL12" s="103"/>
+      <c r="GM12" s="103"/>
+      <c r="GN12" s="103"/>
+      <c r="GO12" s="103"/>
+      <c r="GP12" s="103"/>
+      <c r="GQ12" s="103"/>
+      <c r="GR12" s="103"/>
+      <c r="GS12" s="103"/>
+      <c r="GT12" s="103"/>
+      <c r="GU12" s="103"/>
+      <c r="GV12" s="103"/>
+      <c r="GW12" s="103"/>
+      <c r="GX12" s="103"/>
+      <c r="GY12" s="103"/>
+      <c r="GZ12" s="103"/>
+      <c r="HA12" s="103"/>
+      <c r="HB12" s="103"/>
+      <c r="HC12" s="103"/>
+      <c r="HD12" s="103"/>
+      <c r="HE12" s="103"/>
+      <c r="HF12" s="103"/>
+      <c r="HG12" s="103"/>
+      <c r="HH12" s="103"/>
+      <c r="HI12" s="103"/>
+      <c r="HJ12" s="103"/>
+      <c r="HK12" s="103"/>
+      <c r="HL12" s="103"/>
+      <c r="HM12" s="103"/>
+      <c r="HN12" s="103"/>
+      <c r="HO12" s="103"/>
+      <c r="HP12" s="103"/>
+      <c r="HQ12" s="103"/>
+      <c r="HR12" s="103"/>
+      <c r="HS12" s="103"/>
+      <c r="HT12" s="103"/>
+      <c r="HU12" s="103"/>
+      <c r="HV12" s="103"/>
+      <c r="HW12" s="103"/>
+      <c r="HX12" s="103"/>
+      <c r="HY12" s="103"/>
+      <c r="HZ12" s="103"/>
+      <c r="IA12" s="103"/>
+      <c r="IB12" s="103"/>
+      <c r="IC12" s="103"/>
+      <c r="ID12" s="103"/>
+      <c r="IE12" s="103"/>
+      <c r="IF12" s="103"/>
+      <c r="IG12" s="103"/>
+      <c r="IH12" s="103"/>
+      <c r="II12" s="103"/>
+      <c r="IJ12" s="103"/>
+      <c r="IK12" s="103"/>
+      <c r="IL12" s="103"/>
+      <c r="IM12" s="103"/>
+      <c r="IN12" s="103"/>
+      <c r="IO12" s="103"/>
+      <c r="IP12" s="103"/>
+      <c r="IQ12" s="103"/>
+      <c r="IR12" s="103"/>
+      <c r="IS12" s="103"/>
+      <c r="IT12" s="103"/>
+      <c r="IU12" s="103"/>
+      <c r="IV12" s="103"/>
+      <c r="IW12" s="103"/>
+      <c r="IX12" s="103"/>
+      <c r="IY12" s="103"/>
+      <c r="IZ12" s="103"/>
+      <c r="JA12" s="103"/>
+      <c r="JB12" s="103"/>
+      <c r="JC12" s="103"/>
+      <c r="JD12" s="103"/>
+      <c r="JE12" s="103"/>
+      <c r="JF12" s="103"/>
+      <c r="JG12" s="103"/>
+      <c r="JH12" s="103"/>
+      <c r="JI12" s="103"/>
+      <c r="JJ12" s="103"/>
+      <c r="JK12" s="103"/>
+      <c r="JL12" s="103"/>
+      <c r="JM12" s="103"/>
+      <c r="JN12" s="103"/>
+      <c r="JO12" s="103"/>
+      <c r="JP12" s="103"/>
+      <c r="JQ12" s="103"/>
     </row>
-    <row r="13" spans="1:59" s="34" customFormat="1" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="93" t="s">
+    <row r="13" spans="1:277" s="34" customFormat="1" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="119" t="s">
         <v>113</v>
       </c>
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="95">
+      <c r="C13" s="56">
         <v>1910</v>
       </c>
-      <c r="D13" s="96" t="s">
+      <c r="D13" s="120" t="s">
         <v>108</v>
       </c>
-      <c r="E13" s="97">
+      <c r="E13" s="58">
         <v>8</v>
       </c>
-      <c r="F13" s="98">
+      <c r="F13" s="106">
         <v>56</v>
       </c>
-      <c r="G13" s="98">
+      <c r="G13" s="106">
         <v>14</v>
       </c>
-      <c r="H13" s="98">
+      <c r="H13" s="74">
         <v>8</v>
       </c>
-      <c r="I13" s="98">
+      <c r="I13" s="106">
         <v>17</v>
       </c>
-      <c r="J13" s="98"/>
-      <c r="K13" s="98"/>
-      <c r="L13" s="98"/>
-      <c r="M13" s="98"/>
-      <c r="N13" s="99">
+      <c r="J13" s="74"/>
+      <c r="K13" s="74"/>
+      <c r="L13" s="74"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="75">
         <v>1</v>
       </c>
-      <c r="O13" s="99"/>
-      <c r="P13" s="100">
+      <c r="O13" s="75"/>
+      <c r="P13" s="76">
         <v>2</v>
       </c>
-      <c r="Q13" s="99">
+      <c r="Q13" s="75">
         <v>3</v>
       </c>
-      <c r="R13" s="99">
+      <c r="R13" s="75">
         <v>1</v>
       </c>
-      <c r="S13" s="99"/>
-      <c r="T13" s="99"/>
-      <c r="U13" s="99"/>
-      <c r="V13" s="99"/>
-      <c r="W13" s="99"/>
-      <c r="X13" s="99"/>
-      <c r="Y13" s="99"/>
-      <c r="Z13" s="123">
+      <c r="S13" s="75"/>
+      <c r="T13" s="75"/>
+      <c r="U13" s="75"/>
+      <c r="V13" s="75"/>
+      <c r="W13" s="75"/>
+      <c r="X13" s="75"/>
+      <c r="Y13" s="75"/>
+      <c r="Z13" s="83">
         <v>1</v>
       </c>
-      <c r="AA13" s="99"/>
-      <c r="AB13" s="127"/>
-      <c r="AC13" s="99"/>
-      <c r="AD13" s="99"/>
-      <c r="AE13" s="99"/>
-      <c r="AF13" s="99"/>
-      <c r="AG13" s="127"/>
-      <c r="AH13" s="127"/>
-      <c r="AI13" s="127"/>
-      <c r="AJ13" s="127"/>
-      <c r="AK13" s="99"/>
-      <c r="AL13" s="127"/>
-      <c r="AM13" s="127"/>
-      <c r="AN13" s="127"/>
-      <c r="AO13" s="127"/>
-      <c r="AP13" s="127"/>
-      <c r="AQ13" s="127">
+      <c r="AA13" s="75"/>
+      <c r="AB13" s="86"/>
+      <c r="AC13" s="75"/>
+      <c r="AD13" s="75"/>
+      <c r="AE13" s="75"/>
+      <c r="AF13" s="75"/>
+      <c r="AG13" s="86"/>
+      <c r="AH13" s="86"/>
+      <c r="AI13" s="86"/>
+      <c r="AJ13" s="86"/>
+      <c r="AK13" s="75"/>
+      <c r="AL13" s="86"/>
+      <c r="AM13" s="86"/>
+      <c r="AN13" s="86"/>
+      <c r="AO13" s="86"/>
+      <c r="AP13" s="86"/>
+      <c r="AQ13" s="86">
         <v>1</v>
       </c>
-      <c r="AR13" s="127"/>
-      <c r="AS13" s="127"/>
-      <c r="AT13" s="127"/>
-      <c r="AU13" s="127"/>
-      <c r="AV13" s="127"/>
-      <c r="AW13" s="127"/>
-      <c r="AX13" s="99"/>
-      <c r="AY13" s="127"/>
-      <c r="AZ13" s="127"/>
-      <c r="BA13" s="127"/>
-      <c r="BB13" s="127"/>
-      <c r="BC13" s="127"/>
-      <c r="BD13" s="127"/>
-      <c r="BE13" s="127"/>
-      <c r="BF13" s="127"/>
-      <c r="BG13" s="127"/>
+      <c r="AR13" s="86"/>
+      <c r="AS13" s="86"/>
+      <c r="AT13" s="86"/>
+      <c r="AU13" s="86"/>
+      <c r="AV13" s="86"/>
+      <c r="AW13" s="86"/>
+      <c r="AX13" s="75"/>
+      <c r="AY13" s="86"/>
+      <c r="AZ13" s="86"/>
+      <c r="BA13" s="86"/>
+      <c r="BB13" s="86"/>
+      <c r="BC13" s="86"/>
+      <c r="BD13" s="86"/>
+      <c r="BE13" s="86"/>
+      <c r="BF13" s="86"/>
+      <c r="BG13" s="102"/>
+      <c r="BH13" s="103"/>
+      <c r="BI13" s="103"/>
+      <c r="BJ13" s="103"/>
+      <c r="BK13" s="103"/>
+      <c r="BL13" s="103"/>
+      <c r="BM13" s="103"/>
+      <c r="BN13" s="103"/>
+      <c r="BO13" s="103"/>
+      <c r="BP13" s="103"/>
+      <c r="BQ13" s="103"/>
+      <c r="BR13" s="103"/>
+      <c r="BS13" s="103"/>
+      <c r="BT13" s="103"/>
+      <c r="BU13" s="103"/>
+      <c r="BV13" s="103"/>
+      <c r="BW13" s="103"/>
+      <c r="BX13" s="103"/>
+      <c r="BY13" s="103"/>
+      <c r="BZ13" s="103"/>
+      <c r="CA13" s="103"/>
+      <c r="CB13" s="103"/>
+      <c r="CC13" s="103"/>
+      <c r="CD13" s="103"/>
+      <c r="CE13" s="103"/>
+      <c r="CF13" s="103"/>
+      <c r="CG13" s="103"/>
+      <c r="CH13" s="103"/>
+      <c r="CI13" s="103"/>
+      <c r="CJ13" s="103"/>
+      <c r="CK13" s="103"/>
+      <c r="CL13" s="103"/>
+      <c r="CM13" s="103"/>
+      <c r="CN13" s="103"/>
+      <c r="CO13" s="103"/>
+      <c r="CP13" s="103"/>
+      <c r="CQ13" s="103"/>
+      <c r="CR13" s="103"/>
+      <c r="CS13" s="103"/>
+      <c r="CT13" s="103"/>
+      <c r="CU13" s="103"/>
+      <c r="CV13" s="103"/>
+      <c r="CW13" s="103"/>
+      <c r="CX13" s="103"/>
+      <c r="CY13" s="103"/>
+      <c r="CZ13" s="103"/>
+      <c r="DA13" s="103"/>
+      <c r="DB13" s="103"/>
+      <c r="DC13" s="103"/>
+      <c r="DD13" s="103"/>
+      <c r="DE13" s="103"/>
+      <c r="DF13" s="103"/>
+      <c r="DG13" s="103"/>
+      <c r="DH13" s="103"/>
+      <c r="DI13" s="103"/>
+      <c r="DJ13" s="103"/>
+      <c r="DK13" s="103"/>
+      <c r="DL13" s="103"/>
+      <c r="DM13" s="103"/>
+      <c r="DN13" s="103"/>
+      <c r="DO13" s="103"/>
+      <c r="DP13" s="103"/>
+      <c r="DQ13" s="103"/>
+      <c r="DR13" s="103"/>
+      <c r="DS13" s="103"/>
+      <c r="DT13" s="103"/>
+      <c r="DU13" s="103"/>
+      <c r="DV13" s="103"/>
+      <c r="DW13" s="103"/>
+      <c r="DX13" s="103"/>
+      <c r="DY13" s="103"/>
+      <c r="DZ13" s="103"/>
+      <c r="EA13" s="103"/>
+      <c r="EB13" s="103"/>
+      <c r="EC13" s="103"/>
+      <c r="ED13" s="103"/>
+      <c r="EE13" s="103"/>
+      <c r="EF13" s="103"/>
+      <c r="EG13" s="103"/>
+      <c r="EH13" s="103"/>
+      <c r="EI13" s="103"/>
+      <c r="EJ13" s="103"/>
+      <c r="EK13" s="103"/>
+      <c r="EL13" s="103"/>
+      <c r="EM13" s="103"/>
+      <c r="EN13" s="103"/>
+      <c r="EO13" s="103"/>
+      <c r="EP13" s="103"/>
+      <c r="EQ13" s="103"/>
+      <c r="ER13" s="103"/>
+      <c r="ES13" s="103"/>
+      <c r="ET13" s="103"/>
+      <c r="EU13" s="103"/>
+      <c r="EV13" s="103"/>
+      <c r="EW13" s="103"/>
+      <c r="EX13" s="103"/>
+      <c r="EY13" s="103"/>
+      <c r="EZ13" s="103"/>
+      <c r="FA13" s="103"/>
+      <c r="FB13" s="103"/>
+      <c r="FC13" s="103"/>
+      <c r="FD13" s="103"/>
+      <c r="FE13" s="103"/>
+      <c r="FF13" s="103"/>
+      <c r="FG13" s="103"/>
+      <c r="FH13" s="103"/>
+      <c r="FI13" s="103"/>
+      <c r="FJ13" s="103"/>
+      <c r="FK13" s="103"/>
+      <c r="FL13" s="103"/>
+      <c r="FM13" s="103"/>
+      <c r="FN13" s="103"/>
+      <c r="FO13" s="103"/>
+      <c r="FP13" s="103"/>
+      <c r="FQ13" s="103"/>
+      <c r="FR13" s="103"/>
+      <c r="FS13" s="103"/>
+      <c r="FT13" s="103"/>
+      <c r="FU13" s="103"/>
+      <c r="FV13" s="103"/>
+      <c r="FW13" s="103"/>
+      <c r="FX13" s="103"/>
+      <c r="FY13" s="103"/>
+      <c r="FZ13" s="103"/>
+      <c r="GA13" s="103"/>
+      <c r="GB13" s="103"/>
+      <c r="GC13" s="103"/>
+      <c r="GD13" s="103"/>
+      <c r="GE13" s="103"/>
+      <c r="GF13" s="103"/>
+      <c r="GG13" s="103"/>
+      <c r="GH13" s="103"/>
+      <c r="GI13" s="103"/>
+      <c r="GJ13" s="103"/>
+      <c r="GK13" s="103"/>
+      <c r="GL13" s="103"/>
+      <c r="GM13" s="103"/>
+      <c r="GN13" s="103"/>
+      <c r="GO13" s="103"/>
+      <c r="GP13" s="103"/>
+      <c r="GQ13" s="103"/>
+      <c r="GR13" s="103"/>
+      <c r="GS13" s="103"/>
+      <c r="GT13" s="103"/>
+      <c r="GU13" s="103"/>
+      <c r="GV13" s="103"/>
+      <c r="GW13" s="103"/>
+      <c r="GX13" s="103"/>
+      <c r="GY13" s="103"/>
+      <c r="GZ13" s="103"/>
+      <c r="HA13" s="103"/>
+      <c r="HB13" s="103"/>
+      <c r="HC13" s="103"/>
+      <c r="HD13" s="103"/>
+      <c r="HE13" s="103"/>
+      <c r="HF13" s="103"/>
+      <c r="HG13" s="103"/>
+      <c r="HH13" s="103"/>
+      <c r="HI13" s="103"/>
+      <c r="HJ13" s="103"/>
+      <c r="HK13" s="103"/>
+      <c r="HL13" s="103"/>
+      <c r="HM13" s="103"/>
+      <c r="HN13" s="103"/>
+      <c r="HO13" s="103"/>
+      <c r="HP13" s="103"/>
+      <c r="HQ13" s="103"/>
+      <c r="HR13" s="103"/>
+      <c r="HS13" s="103"/>
+      <c r="HT13" s="103"/>
+      <c r="HU13" s="103"/>
+      <c r="HV13" s="103"/>
+      <c r="HW13" s="103"/>
+      <c r="HX13" s="103"/>
+      <c r="HY13" s="103"/>
+      <c r="HZ13" s="103"/>
+      <c r="IA13" s="103"/>
+      <c r="IB13" s="103"/>
+      <c r="IC13" s="103"/>
+      <c r="ID13" s="103"/>
+      <c r="IE13" s="103"/>
+      <c r="IF13" s="103"/>
+      <c r="IG13" s="103"/>
+      <c r="IH13" s="103"/>
+      <c r="II13" s="103"/>
+      <c r="IJ13" s="103"/>
+      <c r="IK13" s="103"/>
+      <c r="IL13" s="103"/>
+      <c r="IM13" s="103"/>
+      <c r="IN13" s="103"/>
+      <c r="IO13" s="103"/>
+      <c r="IP13" s="103"/>
+      <c r="IQ13" s="103"/>
+      <c r="IR13" s="103"/>
+      <c r="IS13" s="103"/>
+      <c r="IT13" s="103"/>
+      <c r="IU13" s="103"/>
+      <c r="IV13" s="103"/>
+      <c r="IW13" s="103"/>
+      <c r="IX13" s="103"/>
+      <c r="IY13" s="103"/>
+      <c r="IZ13" s="103"/>
+      <c r="JA13" s="103"/>
+      <c r="JB13" s="103"/>
+      <c r="JC13" s="103"/>
+      <c r="JD13" s="103"/>
+      <c r="JE13" s="103"/>
+      <c r="JF13" s="103"/>
+      <c r="JG13" s="103"/>
+      <c r="JH13" s="103"/>
+      <c r="JI13" s="103"/>
+      <c r="JJ13" s="103"/>
+      <c r="JK13" s="103"/>
+      <c r="JL13" s="103"/>
+      <c r="JM13" s="103"/>
+      <c r="JN13" s="103"/>
+      <c r="JO13" s="103"/>
+      <c r="JP13" s="103"/>
+      <c r="JQ13" s="103"/>
     </row>
-    <row r="14" spans="1:59" ht="40.200000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="90" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="91" t="s">
+    <row r="14" spans="1:277" ht="40.200000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="71" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="91">
+      <c r="C14" s="72">
         <v>1911</v>
       </c>
-      <c r="D14" s="92" t="s">
+      <c r="D14" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="53">
+      <c r="E14" s="122">
         <v>13</v>
       </c>
-      <c r="F14" s="44">
+      <c r="F14" s="111">
         <v>25</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="111">
         <v>11</v>
       </c>
-      <c r="H14" s="44">
+      <c r="H14" s="111">
         <v>11</v>
       </c>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44">
+      <c r="I14" s="39"/>
+      <c r="J14" s="39">
         <v>2</v>
       </c>
-      <c r="K14" s="44">
+      <c r="K14" s="111">
         <v>9</v>
       </c>
-      <c r="L14" s="44"/>
-      <c r="M14" s="44"/>
-      <c r="N14" s="47">
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="42">
         <v>7</v>
       </c>
-      <c r="O14" s="47">
+      <c r="O14" s="42">
         <v>6</v>
       </c>
-      <c r="P14" s="48"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47">
+      <c r="P14" s="43"/>
+      <c r="Q14" s="42"/>
+      <c r="R14" s="42">
         <v>2</v>
       </c>
-      <c r="S14" s="47">
+      <c r="S14" s="42">
         <v>1</v>
       </c>
-      <c r="T14" s="47"/>
-      <c r="U14" s="47"/>
-      <c r="V14" s="47"/>
-      <c r="W14" s="47"/>
-      <c r="X14" s="47"/>
-      <c r="Y14" s="47"/>
-      <c r="Z14" s="124">
+      <c r="T14" s="42"/>
+      <c r="U14" s="42"/>
+      <c r="V14" s="42"/>
+      <c r="W14" s="42"/>
+      <c r="X14" s="42"/>
+      <c r="Y14" s="42"/>
+      <c r="Z14" s="84">
         <v>2</v>
       </c>
-      <c r="AA14" s="47"/>
-      <c r="AB14" s="57"/>
-      <c r="AC14" s="47"/>
-      <c r="AD14" s="47">
+      <c r="AA14" s="42"/>
+      <c r="AB14" s="48"/>
+      <c r="AC14" s="42"/>
+      <c r="AD14" s="42">
         <v>1</v>
       </c>
-      <c r="AE14" s="47"/>
-      <c r="AF14" s="47"/>
-      <c r="AG14" s="57"/>
-      <c r="AH14" s="57"/>
-      <c r="AI14" s="121"/>
-      <c r="AJ14" s="57"/>
-      <c r="AK14" s="47"/>
-      <c r="AL14" s="57"/>
-      <c r="AM14" s="57"/>
-      <c r="AN14" s="57"/>
-      <c r="AO14" s="57"/>
-      <c r="AP14" s="57"/>
-      <c r="AQ14" s="57"/>
-      <c r="AR14" s="57">
+      <c r="AE14" s="42"/>
+      <c r="AF14" s="42"/>
+      <c r="AG14" s="48"/>
+      <c r="AH14" s="48"/>
+      <c r="AI14" s="81"/>
+      <c r="AJ14" s="48"/>
+      <c r="AK14" s="42"/>
+      <c r="AL14" s="48"/>
+      <c r="AM14" s="48"/>
+      <c r="AN14" s="48"/>
+      <c r="AO14" s="48"/>
+      <c r="AP14" s="48"/>
+      <c r="AQ14" s="48"/>
+      <c r="AR14" s="48">
         <v>1</v>
       </c>
-      <c r="AS14" s="57"/>
-      <c r="AT14" s="57"/>
-      <c r="AU14" s="57"/>
-      <c r="AV14" s="57"/>
-      <c r="AW14" s="57"/>
-      <c r="AX14" s="47"/>
-      <c r="AY14" s="57"/>
-      <c r="AZ14" s="57"/>
-      <c r="BA14" s="57"/>
-      <c r="BB14" s="57"/>
-      <c r="BC14" s="57"/>
-      <c r="BD14" s="57"/>
-      <c r="BE14" s="57"/>
-      <c r="BF14" s="57">
+      <c r="AS14" s="48"/>
+      <c r="AT14" s="48"/>
+      <c r="AU14" s="48"/>
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="42"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
+      <c r="BB14" s="48"/>
+      <c r="BC14" s="48"/>
+      <c r="BD14" s="48"/>
+      <c r="BE14" s="48"/>
+      <c r="BF14" s="48">
         <v>1</v>
       </c>
-      <c r="BG14" s="57">
+      <c r="BG14" s="81">
         <v>1</v>
       </c>
+      <c r="BH14" s="103"/>
+      <c r="BI14" s="103"/>
+      <c r="BJ14" s="103"/>
+      <c r="BK14" s="103"/>
+      <c r="BL14" s="103"/>
+      <c r="BM14" s="103"/>
+      <c r="BN14" s="103"/>
+      <c r="BO14" s="103"/>
+      <c r="BP14" s="103"/>
+      <c r="BQ14" s="103"/>
+      <c r="BR14" s="103"/>
+      <c r="BS14" s="103"/>
+      <c r="BT14" s="103"/>
+      <c r="BU14" s="103"/>
+      <c r="BV14" s="103"/>
+      <c r="BW14" s="103"/>
+      <c r="BX14" s="103"/>
+      <c r="BY14" s="103"/>
+      <c r="BZ14" s="103"/>
+      <c r="CA14" s="103"/>
+      <c r="CB14" s="103"/>
+      <c r="CC14" s="103"/>
+      <c r="CD14" s="103"/>
+      <c r="CE14" s="103"/>
+      <c r="CF14" s="103"/>
+      <c r="CG14" s="103"/>
+      <c r="CH14" s="103"/>
+      <c r="CI14" s="103"/>
+      <c r="CJ14" s="103"/>
+      <c r="CK14" s="103"/>
+      <c r="CL14" s="103"/>
+      <c r="CM14" s="103"/>
+      <c r="CN14" s="103"/>
+      <c r="CO14" s="103"/>
+      <c r="CP14" s="103"/>
+      <c r="CQ14" s="103"/>
+      <c r="CR14" s="103"/>
+      <c r="CS14" s="103"/>
+      <c r="CT14" s="103"/>
+      <c r="CU14" s="103"/>
+      <c r="CV14" s="103"/>
+      <c r="CW14" s="103"/>
+      <c r="CX14" s="103"/>
+      <c r="CY14" s="103"/>
+      <c r="CZ14" s="103"/>
+      <c r="DA14" s="103"/>
+      <c r="DB14" s="103"/>
+      <c r="DC14" s="103"/>
+      <c r="DD14" s="103"/>
+      <c r="DE14" s="103"/>
+      <c r="DF14" s="103"/>
+      <c r="DG14" s="103"/>
+      <c r="DH14" s="103"/>
+      <c r="DI14" s="103"/>
+      <c r="DJ14" s="103"/>
+      <c r="DK14" s="103"/>
+      <c r="DL14" s="103"/>
+      <c r="DM14" s="103"/>
+      <c r="DN14" s="103"/>
+      <c r="DO14" s="103"/>
+      <c r="DP14" s="103"/>
+      <c r="DQ14" s="103"/>
+      <c r="DR14" s="103"/>
+      <c r="DS14" s="103"/>
+      <c r="DT14" s="103"/>
+      <c r="DU14" s="103"/>
+      <c r="DV14" s="103"/>
+      <c r="DW14" s="103"/>
+      <c r="DX14" s="103"/>
+      <c r="DY14" s="103"/>
+      <c r="DZ14" s="103"/>
+      <c r="EA14" s="103"/>
+      <c r="EB14" s="103"/>
+      <c r="EC14" s="103"/>
+      <c r="ED14" s="103"/>
+      <c r="EE14" s="103"/>
+      <c r="EF14" s="103"/>
+      <c r="EG14" s="103"/>
+      <c r="EH14" s="103"/>
+      <c r="EI14" s="103"/>
+      <c r="EJ14" s="103"/>
+      <c r="EK14" s="103"/>
+      <c r="EL14" s="103"/>
+      <c r="EM14" s="103"/>
+      <c r="EN14" s="103"/>
+      <c r="EO14" s="103"/>
+      <c r="EP14" s="103"/>
+      <c r="EQ14" s="103"/>
+      <c r="ER14" s="103"/>
+      <c r="ES14" s="103"/>
+      <c r="ET14" s="103"/>
+      <c r="EU14" s="103"/>
+      <c r="EV14" s="103"/>
+      <c r="EW14" s="103"/>
+      <c r="EX14" s="103"/>
+      <c r="EY14" s="103"/>
+      <c r="EZ14" s="103"/>
+      <c r="FA14" s="103"/>
+      <c r="FB14" s="103"/>
+      <c r="FC14" s="103"/>
+      <c r="FD14" s="103"/>
+      <c r="FE14" s="103"/>
+      <c r="FF14" s="103"/>
+      <c r="FG14" s="103"/>
+      <c r="FH14" s="103"/>
+      <c r="FI14" s="103"/>
+      <c r="FJ14" s="103"/>
+      <c r="FK14" s="103"/>
+      <c r="FL14" s="103"/>
+      <c r="FM14" s="103"/>
+      <c r="FN14" s="103"/>
+      <c r="FO14" s="103"/>
+      <c r="FP14" s="103"/>
+      <c r="FQ14" s="103"/>
+      <c r="FR14" s="103"/>
+      <c r="FS14" s="103"/>
+      <c r="FT14" s="103"/>
+      <c r="FU14" s="103"/>
+      <c r="FV14" s="103"/>
+      <c r="FW14" s="103"/>
+      <c r="FX14" s="103"/>
+      <c r="FY14" s="103"/>
+      <c r="FZ14" s="103"/>
+      <c r="GA14" s="103"/>
+      <c r="GB14" s="103"/>
+      <c r="GC14" s="103"/>
+      <c r="GD14" s="103"/>
+      <c r="GE14" s="103"/>
+      <c r="GF14" s="103"/>
+      <c r="GG14" s="103"/>
+      <c r="GH14" s="103"/>
+      <c r="GI14" s="103"/>
+      <c r="GJ14" s="103"/>
+      <c r="GK14" s="103"/>
+      <c r="GL14" s="103"/>
+      <c r="GM14" s="103"/>
+      <c r="GN14" s="103"/>
+      <c r="GO14" s="103"/>
+      <c r="GP14" s="103"/>
+      <c r="GQ14" s="103"/>
+      <c r="GR14" s="103"/>
+      <c r="GS14" s="103"/>
+      <c r="GT14" s="103"/>
+      <c r="GU14" s="103"/>
+      <c r="GV14" s="103"/>
+      <c r="GW14" s="103"/>
+      <c r="GX14" s="103"/>
+      <c r="GY14" s="103"/>
+      <c r="GZ14" s="103"/>
+      <c r="HA14" s="103"/>
+      <c r="HB14" s="103"/>
+      <c r="HC14" s="103"/>
+      <c r="HD14" s="103"/>
+      <c r="HE14" s="103"/>
+      <c r="HF14" s="103"/>
+      <c r="HG14" s="103"/>
+      <c r="HH14" s="103"/>
+      <c r="HI14" s="103"/>
+      <c r="HJ14" s="103"/>
+      <c r="HK14" s="103"/>
+      <c r="HL14" s="103"/>
+      <c r="HM14" s="103"/>
+      <c r="HN14" s="103"/>
+      <c r="HO14" s="103"/>
+      <c r="HP14" s="103"/>
+      <c r="HQ14" s="103"/>
+      <c r="HR14" s="103"/>
+      <c r="HS14" s="103"/>
+      <c r="HT14" s="103"/>
+      <c r="HU14" s="103"/>
+      <c r="HV14" s="103"/>
+      <c r="HW14" s="103"/>
+      <c r="HX14" s="103"/>
+      <c r="HY14" s="103"/>
+      <c r="HZ14" s="103"/>
+      <c r="IA14" s="103"/>
+      <c r="IB14" s="103"/>
+      <c r="IC14" s="103"/>
+      <c r="ID14" s="103"/>
+      <c r="IE14" s="103"/>
+      <c r="IF14" s="103"/>
+      <c r="IG14" s="103"/>
+      <c r="IH14" s="103"/>
+      <c r="II14" s="103"/>
+      <c r="IJ14" s="103"/>
+      <c r="IK14" s="103"/>
+      <c r="IL14" s="103"/>
+      <c r="IM14" s="103"/>
+      <c r="IN14" s="103"/>
+      <c r="IO14" s="103"/>
+      <c r="IP14" s="103"/>
+      <c r="IQ14" s="103"/>
+      <c r="IR14" s="103"/>
+      <c r="IS14" s="103"/>
+      <c r="IT14" s="103"/>
+      <c r="IU14" s="103"/>
+      <c r="IV14" s="103"/>
+      <c r="IW14" s="103"/>
+      <c r="IX14" s="103"/>
+      <c r="IY14" s="103"/>
+      <c r="IZ14" s="103"/>
+      <c r="JA14" s="103"/>
+      <c r="JB14" s="103"/>
+      <c r="JC14" s="103"/>
+      <c r="JD14" s="103"/>
+      <c r="JE14" s="103"/>
+      <c r="JF14" s="103"/>
+      <c r="JG14" s="103"/>
+      <c r="JH14" s="103"/>
+      <c r="JI14" s="103"/>
+      <c r="JJ14" s="103"/>
+      <c r="JK14" s="103"/>
+      <c r="JL14" s="103"/>
+      <c r="JM14" s="103"/>
+      <c r="JN14" s="103"/>
+      <c r="JO14" s="103"/>
+      <c r="JP14" s="103"/>
+      <c r="JQ14" s="103"/>
     </row>
-    <row r="15" spans="1:59" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="83" t="s">
+    <row r="15" spans="1:277" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="30">
         <v>1912</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="54">
+      <c r="E15" s="47">
         <v>5</v>
       </c>
-      <c r="F15" s="45">
+      <c r="F15" s="105">
         <v>30</v>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="105">
         <v>15</v>
       </c>
-      <c r="H15" s="45">
+      <c r="H15" s="105">
         <v>12</v>
       </c>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45">
+      <c r="I15" s="40"/>
+      <c r="J15" s="40">
         <v>1</v>
       </c>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="49"/>
-      <c r="O15" s="49"/>
-      <c r="P15" s="50"/>
-      <c r="Q15" s="49"/>
-      <c r="R15" s="49"/>
-      <c r="S15" s="49"/>
-      <c r="T15" s="49"/>
-      <c r="U15" s="49"/>
-      <c r="V15" s="49"/>
-      <c r="W15" s="49"/>
-      <c r="X15" s="49"/>
-      <c r="Y15" s="49"/>
-      <c r="Z15" s="122"/>
-      <c r="AA15" s="49"/>
-      <c r="AB15" s="46"/>
-      <c r="AC15" s="49"/>
-      <c r="AD15" s="49"/>
-      <c r="AE15" s="49"/>
-      <c r="AF15" s="49">
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="45"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="44"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
+      <c r="U15" s="44"/>
+      <c r="V15" s="44"/>
+      <c r="W15" s="44"/>
+      <c r="X15" s="44"/>
+      <c r="Y15" s="44"/>
+      <c r="Z15" s="82"/>
+      <c r="AA15" s="44"/>
+      <c r="AB15" s="41"/>
+      <c r="AC15" s="44"/>
+      <c r="AD15" s="44"/>
+      <c r="AE15" s="44"/>
+      <c r="AF15" s="44">
         <v>1</v>
       </c>
-      <c r="AG15" s="46"/>
-      <c r="AH15" s="46"/>
-      <c r="AI15" s="101"/>
-      <c r="AJ15" s="46"/>
-      <c r="AK15" s="49"/>
-      <c r="AL15" s="46"/>
-      <c r="AM15" s="46"/>
-      <c r="AN15" s="46"/>
-      <c r="AO15" s="46"/>
-      <c r="AP15" s="46"/>
-      <c r="AQ15" s="46"/>
-      <c r="AR15" s="46"/>
-      <c r="AS15" s="46"/>
-      <c r="AT15" s="46"/>
-      <c r="AU15" s="46"/>
-      <c r="AV15" s="46"/>
-      <c r="AW15" s="46"/>
-      <c r="AX15" s="49"/>
-      <c r="AY15" s="46"/>
-      <c r="AZ15" s="46"/>
-      <c r="BA15" s="46"/>
-      <c r="BB15" s="46"/>
-      <c r="BC15" s="46"/>
-      <c r="BD15" s="46"/>
-      <c r="BE15" s="46"/>
-      <c r="BF15" s="46"/>
-      <c r="BG15" s="46"/>
+      <c r="AG15" s="41"/>
+      <c r="AH15" s="41"/>
+      <c r="AI15" s="77"/>
+      <c r="AJ15" s="41"/>
+      <c r="AK15" s="44"/>
+      <c r="AL15" s="41"/>
+      <c r="AM15" s="41"/>
+      <c r="AN15" s="41"/>
+      <c r="AO15" s="41"/>
+      <c r="AP15" s="41"/>
+      <c r="AQ15" s="41"/>
+      <c r="AR15" s="41"/>
+      <c r="AS15" s="41"/>
+      <c r="AT15" s="41"/>
+      <c r="AU15" s="41"/>
+      <c r="AV15" s="41"/>
+      <c r="AW15" s="41"/>
+      <c r="AX15" s="44"/>
+      <c r="AY15" s="41"/>
+      <c r="AZ15" s="41"/>
+      <c r="BA15" s="41"/>
+      <c r="BB15" s="41"/>
+      <c r="BC15" s="41"/>
+      <c r="BD15" s="41"/>
+      <c r="BE15" s="41"/>
+      <c r="BF15" s="41"/>
+      <c r="BG15" s="77"/>
+      <c r="BH15" s="103"/>
+      <c r="BI15" s="103"/>
+      <c r="BJ15" s="103"/>
+      <c r="BK15" s="103"/>
+      <c r="BL15" s="103"/>
+      <c r="BM15" s="103"/>
+      <c r="BN15" s="103"/>
+      <c r="BO15" s="103"/>
+      <c r="BP15" s="103"/>
+      <c r="BQ15" s="103"/>
+      <c r="BR15" s="103"/>
+      <c r="BS15" s="103"/>
+      <c r="BT15" s="103"/>
+      <c r="BU15" s="103"/>
+      <c r="BV15" s="103"/>
+      <c r="BW15" s="103"/>
+      <c r="BX15" s="103"/>
+      <c r="BY15" s="103"/>
+      <c r="BZ15" s="103"/>
+      <c r="CA15" s="103"/>
+      <c r="CB15" s="103"/>
+      <c r="CC15" s="103"/>
+      <c r="CD15" s="103"/>
+      <c r="CE15" s="103"/>
+      <c r="CF15" s="103"/>
+      <c r="CG15" s="103"/>
+      <c r="CH15" s="103"/>
+      <c r="CI15" s="103"/>
+      <c r="CJ15" s="103"/>
+      <c r="CK15" s="103"/>
+      <c r="CL15" s="103"/>
+      <c r="CM15" s="103"/>
+      <c r="CN15" s="103"/>
+      <c r="CO15" s="103"/>
+      <c r="CP15" s="103"/>
+      <c r="CQ15" s="103"/>
+      <c r="CR15" s="103"/>
+      <c r="CS15" s="103"/>
+      <c r="CT15" s="103"/>
+      <c r="CU15" s="103"/>
+      <c r="CV15" s="103"/>
+      <c r="CW15" s="103"/>
+      <c r="CX15" s="103"/>
+      <c r="CY15" s="103"/>
+      <c r="CZ15" s="103"/>
+      <c r="DA15" s="103"/>
+      <c r="DB15" s="103"/>
+      <c r="DC15" s="103"/>
+      <c r="DD15" s="103"/>
+      <c r="DE15" s="103"/>
+      <c r="DF15" s="103"/>
+      <c r="DG15" s="103"/>
+      <c r="DH15" s="103"/>
+      <c r="DI15" s="103"/>
+      <c r="DJ15" s="103"/>
+      <c r="DK15" s="103"/>
+      <c r="DL15" s="103"/>
+      <c r="DM15" s="103"/>
+      <c r="DN15" s="103"/>
+      <c r="DO15" s="103"/>
+      <c r="DP15" s="103"/>
+      <c r="DQ15" s="103"/>
+      <c r="DR15" s="103"/>
+      <c r="DS15" s="103"/>
+      <c r="DT15" s="103"/>
+      <c r="DU15" s="103"/>
+      <c r="DV15" s="103"/>
+      <c r="DW15" s="103"/>
+      <c r="DX15" s="103"/>
+      <c r="DY15" s="103"/>
+      <c r="DZ15" s="103"/>
+      <c r="EA15" s="103"/>
+      <c r="EB15" s="103"/>
+      <c r="EC15" s="103"/>
+      <c r="ED15" s="103"/>
+      <c r="EE15" s="103"/>
+      <c r="EF15" s="103"/>
+      <c r="EG15" s="103"/>
+      <c r="EH15" s="103"/>
+      <c r="EI15" s="103"/>
+      <c r="EJ15" s="103"/>
+      <c r="EK15" s="103"/>
+      <c r="EL15" s="103"/>
+      <c r="EM15" s="103"/>
+      <c r="EN15" s="103"/>
+      <c r="EO15" s="103"/>
+      <c r="EP15" s="103"/>
+      <c r="EQ15" s="103"/>
+      <c r="ER15" s="103"/>
+      <c r="ES15" s="103"/>
+      <c r="ET15" s="103"/>
+      <c r="EU15" s="103"/>
+      <c r="EV15" s="103"/>
+      <c r="EW15" s="103"/>
+      <c r="EX15" s="103"/>
+      <c r="EY15" s="103"/>
+      <c r="EZ15" s="103"/>
+      <c r="FA15" s="103"/>
+      <c r="FB15" s="103"/>
+      <c r="FC15" s="103"/>
+      <c r="FD15" s="103"/>
+      <c r="FE15" s="103"/>
+      <c r="FF15" s="103"/>
+      <c r="FG15" s="103"/>
+      <c r="FH15" s="103"/>
+      <c r="FI15" s="103"/>
+      <c r="FJ15" s="103"/>
+      <c r="FK15" s="103"/>
+      <c r="FL15" s="103"/>
+      <c r="FM15" s="103"/>
+      <c r="FN15" s="103"/>
+      <c r="FO15" s="103"/>
+      <c r="FP15" s="103"/>
+      <c r="FQ15" s="103"/>
+      <c r="FR15" s="103"/>
+      <c r="FS15" s="103"/>
+      <c r="FT15" s="103"/>
+      <c r="FU15" s="103"/>
+      <c r="FV15" s="103"/>
+      <c r="FW15" s="103"/>
+      <c r="FX15" s="103"/>
+      <c r="FY15" s="103"/>
+      <c r="FZ15" s="103"/>
+      <c r="GA15" s="103"/>
+      <c r="GB15" s="103"/>
+      <c r="GC15" s="103"/>
+      <c r="GD15" s="103"/>
+      <c r="GE15" s="103"/>
+      <c r="GF15" s="103"/>
+      <c r="GG15" s="103"/>
+      <c r="GH15" s="103"/>
+      <c r="GI15" s="103"/>
+      <c r="GJ15" s="103"/>
+      <c r="GK15" s="103"/>
+      <c r="GL15" s="103"/>
+      <c r="GM15" s="103"/>
+      <c r="GN15" s="103"/>
+      <c r="GO15" s="103"/>
+      <c r="GP15" s="103"/>
+      <c r="GQ15" s="103"/>
+      <c r="GR15" s="103"/>
+      <c r="GS15" s="103"/>
+      <c r="GT15" s="103"/>
+      <c r="GU15" s="103"/>
+      <c r="GV15" s="103"/>
+      <c r="GW15" s="103"/>
+      <c r="GX15" s="103"/>
+      <c r="GY15" s="103"/>
+      <c r="GZ15" s="103"/>
+      <c r="HA15" s="103"/>
+      <c r="HB15" s="103"/>
+      <c r="HC15" s="103"/>
+      <c r="HD15" s="103"/>
+      <c r="HE15" s="103"/>
+      <c r="HF15" s="103"/>
+      <c r="HG15" s="103"/>
+      <c r="HH15" s="103"/>
+      <c r="HI15" s="103"/>
+      <c r="HJ15" s="103"/>
+      <c r="HK15" s="103"/>
+      <c r="HL15" s="103"/>
+      <c r="HM15" s="103"/>
+      <c r="HN15" s="103"/>
+      <c r="HO15" s="103"/>
+      <c r="HP15" s="103"/>
+      <c r="HQ15" s="103"/>
+      <c r="HR15" s="103"/>
+      <c r="HS15" s="103"/>
+      <c r="HT15" s="103"/>
+      <c r="HU15" s="103"/>
+      <c r="HV15" s="103"/>
+      <c r="HW15" s="103"/>
+      <c r="HX15" s="103"/>
+      <c r="HY15" s="103"/>
+      <c r="HZ15" s="103"/>
+      <c r="IA15" s="103"/>
+      <c r="IB15" s="103"/>
+      <c r="IC15" s="103"/>
+      <c r="ID15" s="103"/>
+      <c r="IE15" s="103"/>
+      <c r="IF15" s="103"/>
+      <c r="IG15" s="103"/>
+      <c r="IH15" s="103"/>
+      <c r="II15" s="103"/>
+      <c r="IJ15" s="103"/>
+      <c r="IK15" s="103"/>
+      <c r="IL15" s="103"/>
+      <c r="IM15" s="103"/>
+      <c r="IN15" s="103"/>
+      <c r="IO15" s="103"/>
+      <c r="IP15" s="103"/>
+      <c r="IQ15" s="103"/>
+      <c r="IR15" s="103"/>
+      <c r="IS15" s="103"/>
+      <c r="IT15" s="103"/>
+      <c r="IU15" s="103"/>
+      <c r="IV15" s="103"/>
+      <c r="IW15" s="103"/>
+      <c r="IX15" s="103"/>
+      <c r="IY15" s="103"/>
+      <c r="IZ15" s="103"/>
+      <c r="JA15" s="103"/>
+      <c r="JB15" s="103"/>
+      <c r="JC15" s="103"/>
+      <c r="JD15" s="103"/>
+      <c r="JE15" s="103"/>
+      <c r="JF15" s="103"/>
+      <c r="JG15" s="103"/>
+      <c r="JH15" s="103"/>
+      <c r="JI15" s="103"/>
+      <c r="JJ15" s="103"/>
+      <c r="JK15" s="103"/>
+      <c r="JL15" s="103"/>
+      <c r="JM15" s="103"/>
+      <c r="JN15" s="103"/>
+      <c r="JO15" s="103"/>
+      <c r="JP15" s="103"/>
+      <c r="JQ15" s="103"/>
     </row>
-    <row r="16" spans="1:59" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="68" t="s">
-        <v>30</v>
+    <row r="16" spans="1:277" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="53" t="s">
+        <v>159</v>
       </c>
       <c r="B16" s="29" t="s">
         <v>18</v>
@@ -3785,548 +5047,984 @@
       <c r="C16" s="30">
         <v>1913</v>
       </c>
-      <c r="D16" s="40" t="s">
+      <c r="D16" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="52">
+      <c r="E16" s="116">
         <v>12</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="105">
         <v>96</v>
       </c>
-      <c r="G16" s="42">
+      <c r="G16" s="105">
         <v>29</v>
       </c>
-      <c r="H16" s="42">
+      <c r="H16" s="105">
         <v>48</v>
       </c>
-      <c r="I16" s="42">
+      <c r="I16" s="38">
         <v>5</v>
       </c>
-      <c r="J16" s="42">
+      <c r="J16" s="38">
         <v>4</v>
       </c>
-      <c r="K16" s="42"/>
-      <c r="L16" s="42"/>
-      <c r="M16" s="42"/>
-      <c r="N16" s="46">
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="131">
         <v>26</v>
       </c>
-      <c r="O16" s="46">
+      <c r="O16" s="131">
         <v>19</v>
       </c>
-      <c r="P16" s="51">
+      <c r="P16" s="46">
         <v>1</v>
       </c>
-      <c r="Q16" s="46">
+      <c r="Q16" s="41">
         <v>3</v>
       </c>
-      <c r="R16" s="46">
+      <c r="R16" s="41">
         <v>5</v>
       </c>
-      <c r="S16" s="46">
+      <c r="S16" s="131">
         <v>15</v>
       </c>
-      <c r="T16" s="46"/>
-      <c r="U16" s="46"/>
-      <c r="V16" s="46"/>
-      <c r="W16" s="46"/>
-      <c r="X16" s="46"/>
-      <c r="Y16" s="46"/>
-      <c r="Z16" s="101"/>
-      <c r="AA16" s="46"/>
-      <c r="AB16" s="46"/>
-      <c r="AC16" s="46"/>
-      <c r="AD16" s="46"/>
-      <c r="AE16" s="46"/>
-      <c r="AF16" s="46"/>
-      <c r="AG16" s="46"/>
-      <c r="AH16" s="46"/>
-      <c r="AI16" s="101">
+      <c r="T16" s="41"/>
+      <c r="U16" s="41"/>
+      <c r="V16" s="41"/>
+      <c r="W16" s="41"/>
+      <c r="X16" s="41"/>
+      <c r="Y16" s="41"/>
+      <c r="Z16" s="77"/>
+      <c r="AA16" s="41"/>
+      <c r="AB16" s="41"/>
+      <c r="AC16" s="41"/>
+      <c r="AD16" s="41"/>
+      <c r="AE16" s="41"/>
+      <c r="AF16" s="41"/>
+      <c r="AG16" s="41"/>
+      <c r="AH16" s="41"/>
+      <c r="AI16" s="136">
         <v>3</v>
       </c>
-      <c r="AJ16" s="46"/>
-      <c r="AK16" s="46"/>
-      <c r="AL16" s="46"/>
-      <c r="AM16" s="46"/>
-      <c r="AN16" s="46"/>
-      <c r="AO16" s="46"/>
-      <c r="AP16" s="46"/>
-      <c r="AQ16" s="46"/>
-      <c r="AR16" s="46"/>
-      <c r="AS16" s="46"/>
-      <c r="AT16" s="46"/>
-      <c r="AU16" s="46"/>
-      <c r="AV16" s="46"/>
-      <c r="AW16" s="46"/>
-      <c r="AX16" s="46"/>
-      <c r="AY16" s="46"/>
-      <c r="AZ16" s="46"/>
-      <c r="BA16" s="46"/>
-      <c r="BB16" s="46"/>
-      <c r="BC16" s="46"/>
-      <c r="BD16" s="46"/>
-      <c r="BE16" s="46"/>
-      <c r="BF16" s="46"/>
-      <c r="BG16" s="46"/>
+      <c r="AJ16" s="41"/>
+      <c r="AK16" s="41"/>
+      <c r="AL16" s="41"/>
+      <c r="AM16" s="41"/>
+      <c r="AN16" s="41"/>
+      <c r="AO16" s="41"/>
+      <c r="AP16" s="41"/>
+      <c r="AQ16" s="41"/>
+      <c r="AR16" s="41"/>
+      <c r="AS16" s="41"/>
+      <c r="AT16" s="41"/>
+      <c r="AU16" s="41"/>
+      <c r="AV16" s="41"/>
+      <c r="AW16" s="41"/>
+      <c r="AX16" s="41"/>
+      <c r="AY16" s="41"/>
+      <c r="AZ16" s="41"/>
+      <c r="BA16" s="41"/>
+      <c r="BB16" s="41"/>
+      <c r="BC16" s="41"/>
+      <c r="BD16" s="41"/>
+      <c r="BE16" s="41"/>
+      <c r="BF16" s="41"/>
+      <c r="BG16" s="77"/>
+      <c r="BH16" s="103"/>
+      <c r="BI16" s="103"/>
+      <c r="BJ16" s="103"/>
+      <c r="BK16" s="103"/>
+      <c r="BL16" s="103"/>
+      <c r="BM16" s="103"/>
+      <c r="BN16" s="103"/>
+      <c r="BO16" s="103"/>
+      <c r="BP16" s="103"/>
+      <c r="BQ16" s="103"/>
+      <c r="BR16" s="103"/>
+      <c r="BS16" s="103"/>
+      <c r="BT16" s="103"/>
+      <c r="BU16" s="103"/>
+      <c r="BV16" s="103"/>
+      <c r="BW16" s="103"/>
+      <c r="BX16" s="103"/>
+      <c r="BY16" s="103"/>
+      <c r="BZ16" s="103"/>
+      <c r="CA16" s="103"/>
+      <c r="CB16" s="103"/>
+      <c r="CC16" s="103"/>
+      <c r="CD16" s="103"/>
+      <c r="CE16" s="103"/>
+      <c r="CF16" s="103"/>
+      <c r="CG16" s="103"/>
+      <c r="CH16" s="103"/>
+      <c r="CI16" s="103"/>
+      <c r="CJ16" s="103"/>
+      <c r="CK16" s="103"/>
+      <c r="CL16" s="103"/>
+      <c r="CM16" s="103"/>
+      <c r="CN16" s="103"/>
+      <c r="CO16" s="103"/>
+      <c r="CP16" s="103"/>
+      <c r="CQ16" s="103"/>
+      <c r="CR16" s="103"/>
+      <c r="CS16" s="103"/>
+      <c r="CT16" s="103"/>
+      <c r="CU16" s="103"/>
+      <c r="CV16" s="103"/>
+      <c r="CW16" s="103"/>
+      <c r="CX16" s="103"/>
+      <c r="CY16" s="103"/>
+      <c r="CZ16" s="103"/>
+      <c r="DA16" s="103"/>
+      <c r="DB16" s="103"/>
+      <c r="DC16" s="103"/>
+      <c r="DD16" s="103"/>
+      <c r="DE16" s="103"/>
+      <c r="DF16" s="103"/>
+      <c r="DG16" s="103"/>
+      <c r="DH16" s="103"/>
+      <c r="DI16" s="103"/>
+      <c r="DJ16" s="103"/>
+      <c r="DK16" s="103"/>
+      <c r="DL16" s="103"/>
+      <c r="DM16" s="103"/>
+      <c r="DN16" s="103"/>
+      <c r="DO16" s="103"/>
+      <c r="DP16" s="103"/>
+      <c r="DQ16" s="103"/>
+      <c r="DR16" s="103"/>
+      <c r="DS16" s="103"/>
+      <c r="DT16" s="103"/>
+      <c r="DU16" s="103"/>
+      <c r="DV16" s="103"/>
+      <c r="DW16" s="103"/>
+      <c r="DX16" s="103"/>
+      <c r="DY16" s="103"/>
+      <c r="DZ16" s="103"/>
+      <c r="EA16" s="103"/>
+      <c r="EB16" s="103"/>
+      <c r="EC16" s="103"/>
+      <c r="ED16" s="103"/>
+      <c r="EE16" s="103"/>
+      <c r="EF16" s="103"/>
+      <c r="EG16" s="103"/>
+      <c r="EH16" s="103"/>
+      <c r="EI16" s="103"/>
+      <c r="EJ16" s="103"/>
+      <c r="EK16" s="103"/>
+      <c r="EL16" s="103"/>
+      <c r="EM16" s="103"/>
+      <c r="EN16" s="103"/>
+      <c r="EO16" s="103"/>
+      <c r="EP16" s="103"/>
+      <c r="EQ16" s="103"/>
+      <c r="ER16" s="103"/>
+      <c r="ES16" s="103"/>
+      <c r="ET16" s="103"/>
+      <c r="EU16" s="103"/>
+      <c r="EV16" s="103"/>
+      <c r="EW16" s="103"/>
+      <c r="EX16" s="103"/>
+      <c r="EY16" s="103"/>
+      <c r="EZ16" s="103"/>
+      <c r="FA16" s="103"/>
+      <c r="FB16" s="103"/>
+      <c r="FC16" s="103"/>
+      <c r="FD16" s="103"/>
+      <c r="FE16" s="103"/>
+      <c r="FF16" s="103"/>
+      <c r="FG16" s="103"/>
+      <c r="FH16" s="103"/>
+      <c r="FI16" s="103"/>
+      <c r="FJ16" s="103"/>
+      <c r="FK16" s="103"/>
+      <c r="FL16" s="103"/>
+      <c r="FM16" s="103"/>
+      <c r="FN16" s="103"/>
+      <c r="FO16" s="103"/>
+      <c r="FP16" s="103"/>
+      <c r="FQ16" s="103"/>
+      <c r="FR16" s="103"/>
+      <c r="FS16" s="103"/>
+      <c r="FT16" s="103"/>
+      <c r="FU16" s="103"/>
+      <c r="FV16" s="103"/>
+      <c r="FW16" s="103"/>
+      <c r="FX16" s="103"/>
+      <c r="FY16" s="103"/>
+      <c r="FZ16" s="103"/>
+      <c r="GA16" s="103"/>
+      <c r="GB16" s="103"/>
+      <c r="GC16" s="103"/>
+      <c r="GD16" s="103"/>
+      <c r="GE16" s="103"/>
+      <c r="GF16" s="103"/>
+      <c r="GG16" s="103"/>
+      <c r="GH16" s="103"/>
+      <c r="GI16" s="103"/>
+      <c r="GJ16" s="103"/>
+      <c r="GK16" s="103"/>
+      <c r="GL16" s="103"/>
+      <c r="GM16" s="103"/>
+      <c r="GN16" s="103"/>
+      <c r="GO16" s="103"/>
+      <c r="GP16" s="103"/>
+      <c r="GQ16" s="103"/>
+      <c r="GR16" s="103"/>
+      <c r="GS16" s="103"/>
+      <c r="GT16" s="103"/>
+      <c r="GU16" s="103"/>
+      <c r="GV16" s="103"/>
+      <c r="GW16" s="103"/>
+      <c r="GX16" s="103"/>
+      <c r="GY16" s="103"/>
+      <c r="GZ16" s="103"/>
+      <c r="HA16" s="103"/>
+      <c r="HB16" s="103"/>
+      <c r="HC16" s="103"/>
+      <c r="HD16" s="103"/>
+      <c r="HE16" s="103"/>
+      <c r="HF16" s="103"/>
+      <c r="HG16" s="103"/>
+      <c r="HH16" s="103"/>
+      <c r="HI16" s="103"/>
+      <c r="HJ16" s="103"/>
+      <c r="HK16" s="103"/>
+      <c r="HL16" s="103"/>
+      <c r="HM16" s="103"/>
+      <c r="HN16" s="103"/>
+      <c r="HO16" s="103"/>
+      <c r="HP16" s="103"/>
+      <c r="HQ16" s="103"/>
+      <c r="HR16" s="103"/>
+      <c r="HS16" s="103"/>
+      <c r="HT16" s="103"/>
+      <c r="HU16" s="103"/>
+      <c r="HV16" s="103"/>
+      <c r="HW16" s="103"/>
+      <c r="HX16" s="103"/>
+      <c r="HY16" s="103"/>
+      <c r="HZ16" s="103"/>
+      <c r="IA16" s="103"/>
+      <c r="IB16" s="103"/>
+      <c r="IC16" s="103"/>
+      <c r="ID16" s="103"/>
+      <c r="IE16" s="103"/>
+      <c r="IF16" s="103"/>
+      <c r="IG16" s="103"/>
+      <c r="IH16" s="103"/>
+      <c r="II16" s="103"/>
+      <c r="IJ16" s="103"/>
+      <c r="IK16" s="103"/>
+      <c r="IL16" s="103"/>
+      <c r="IM16" s="103"/>
+      <c r="IN16" s="103"/>
+      <c r="IO16" s="103"/>
+      <c r="IP16" s="103"/>
+      <c r="IQ16" s="103"/>
+      <c r="IR16" s="103"/>
+      <c r="IS16" s="103"/>
+      <c r="IT16" s="103"/>
+      <c r="IU16" s="103"/>
+      <c r="IV16" s="103"/>
+      <c r="IW16" s="103"/>
+      <c r="IX16" s="103"/>
+      <c r="IY16" s="103"/>
+      <c r="IZ16" s="103"/>
+      <c r="JA16" s="103"/>
+      <c r="JB16" s="103"/>
+      <c r="JC16" s="103"/>
+      <c r="JD16" s="103"/>
+      <c r="JE16" s="103"/>
+      <c r="JF16" s="103"/>
+      <c r="JG16" s="103"/>
+      <c r="JH16" s="103"/>
+      <c r="JI16" s="103"/>
+      <c r="JJ16" s="103"/>
+      <c r="JK16" s="103"/>
+      <c r="JL16" s="103"/>
+      <c r="JM16" s="103"/>
+      <c r="JN16" s="103"/>
+      <c r="JO16" s="103"/>
+      <c r="JP16" s="103"/>
+      <c r="JQ16" s="103"/>
     </row>
-    <row r="17" spans="1:59" s="35" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="69" t="s">
+    <row r="17" spans="1:277" s="35" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="70" t="s">
+      <c r="B17" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="71">
+      <c r="C17" s="56">
         <v>1914</v>
       </c>
-      <c r="D17" s="72" t="s">
+      <c r="D17" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="73">
+      <c r="E17" s="58">
         <v>1</v>
       </c>
-      <c r="F17" s="74">
+      <c r="F17" s="106">
         <v>36</v>
       </c>
-      <c r="G17" s="74">
+      <c r="G17" s="106">
         <v>43</v>
       </c>
-      <c r="H17" s="74">
+      <c r="H17" s="106">
         <v>30</v>
       </c>
-      <c r="I17" s="74">
+      <c r="I17" s="106">
         <v>18</v>
       </c>
-      <c r="J17" s="74"/>
-      <c r="K17" s="74"/>
-      <c r="L17" s="74"/>
-      <c r="M17" s="74"/>
-      <c r="N17" s="75">
+      <c r="J17" s="59"/>
+      <c r="K17" s="59"/>
+      <c r="L17" s="59"/>
+      <c r="M17" s="59"/>
+      <c r="N17" s="132">
         <v>24</v>
       </c>
-      <c r="O17" s="75">
+      <c r="O17" s="132">
         <v>13</v>
       </c>
-      <c r="P17" s="85">
+      <c r="P17" s="68">
         <v>6</v>
       </c>
-      <c r="Q17" s="75"/>
-      <c r="R17" s="75">
+      <c r="Q17" s="60"/>
+      <c r="R17" s="132">
         <v>9</v>
       </c>
-      <c r="S17" s="75"/>
-      <c r="T17" s="75"/>
-      <c r="U17" s="75"/>
-      <c r="V17" s="75"/>
-      <c r="W17" s="75"/>
-      <c r="X17" s="75">
+      <c r="S17" s="60"/>
+      <c r="T17" s="60"/>
+      <c r="U17" s="60"/>
+      <c r="V17" s="60"/>
+      <c r="W17" s="60"/>
+      <c r="X17" s="132">
         <v>8</v>
       </c>
-      <c r="Y17" s="75"/>
-      <c r="Z17" s="120"/>
-      <c r="AA17" s="75">
+      <c r="Y17" s="60"/>
+      <c r="Z17" s="80"/>
+      <c r="AA17" s="132">
         <v>4</v>
       </c>
-      <c r="AB17" s="75"/>
-      <c r="AC17" s="75"/>
-      <c r="AD17" s="75"/>
-      <c r="AE17" s="75"/>
-      <c r="AF17" s="75"/>
-      <c r="AG17" s="75"/>
-      <c r="AH17" s="75"/>
-      <c r="AI17" s="120"/>
-      <c r="AJ17" s="75"/>
-      <c r="AK17" s="75"/>
-      <c r="AL17" s="75"/>
-      <c r="AM17" s="75"/>
-      <c r="AN17" s="75"/>
-      <c r="AO17" s="75"/>
-      <c r="AP17" s="75"/>
-      <c r="AQ17" s="75"/>
-      <c r="AR17" s="75"/>
-      <c r="AS17" s="75"/>
-      <c r="AT17" s="75"/>
-      <c r="AU17" s="75"/>
-      <c r="AV17" s="75"/>
-      <c r="AW17" s="75"/>
-      <c r="AX17" s="75"/>
-      <c r="AY17" s="75"/>
-      <c r="AZ17" s="75"/>
-      <c r="BA17" s="75"/>
-      <c r="BB17" s="75"/>
-      <c r="BC17" s="75"/>
-      <c r="BD17" s="75"/>
-      <c r="BE17" s="75"/>
-      <c r="BF17" s="75"/>
-      <c r="BG17" s="75"/>
+      <c r="AB17" s="60"/>
+      <c r="AC17" s="60"/>
+      <c r="AD17" s="60"/>
+      <c r="AE17" s="60"/>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="80"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="60"/>
+      <c r="AN17" s="60"/>
+      <c r="AO17" s="60"/>
+      <c r="AP17" s="60"/>
+      <c r="AQ17" s="60"/>
+      <c r="AR17" s="60"/>
+      <c r="AS17" s="60"/>
+      <c r="AT17" s="60"/>
+      <c r="AU17" s="60"/>
+      <c r="AV17" s="60"/>
+      <c r="AW17" s="60"/>
+      <c r="AX17" s="60"/>
+      <c r="AY17" s="60"/>
+      <c r="AZ17" s="60"/>
+      <c r="BA17" s="60"/>
+      <c r="BB17" s="60"/>
+      <c r="BC17" s="60"/>
+      <c r="BD17" s="60"/>
+      <c r="BE17" s="60"/>
+      <c r="BF17" s="60"/>
+      <c r="BG17" s="80"/>
+      <c r="BH17" s="103"/>
+      <c r="BI17" s="103"/>
+      <c r="BJ17" s="103"/>
+      <c r="BK17" s="103"/>
+      <c r="BL17" s="103"/>
+      <c r="BM17" s="103"/>
+      <c r="BN17" s="103"/>
+      <c r="BO17" s="103"/>
+      <c r="BP17" s="103"/>
+      <c r="BQ17" s="103"/>
+      <c r="BR17" s="103"/>
+      <c r="BS17" s="103"/>
+      <c r="BT17" s="103"/>
+      <c r="BU17" s="103"/>
+      <c r="BV17" s="103"/>
+      <c r="BW17" s="103"/>
+      <c r="BX17" s="103"/>
+      <c r="BY17" s="103"/>
+      <c r="BZ17" s="103"/>
+      <c r="CA17" s="103"/>
+      <c r="CB17" s="103"/>
+      <c r="CC17" s="103"/>
+      <c r="CD17" s="103"/>
+      <c r="CE17" s="103"/>
+      <c r="CF17" s="103"/>
+      <c r="CG17" s="103"/>
+      <c r="CH17" s="103"/>
+      <c r="CI17" s="103"/>
+      <c r="CJ17" s="103"/>
+      <c r="CK17" s="103"/>
+      <c r="CL17" s="103"/>
+      <c r="CM17" s="103"/>
+      <c r="CN17" s="103"/>
+      <c r="CO17" s="103"/>
+      <c r="CP17" s="103"/>
+      <c r="CQ17" s="103"/>
+      <c r="CR17" s="103"/>
+      <c r="CS17" s="103"/>
+      <c r="CT17" s="103"/>
+      <c r="CU17" s="103"/>
+      <c r="CV17" s="103"/>
+      <c r="CW17" s="103"/>
+      <c r="CX17" s="103"/>
+      <c r="CY17" s="103"/>
+      <c r="CZ17" s="103"/>
+      <c r="DA17" s="103"/>
+      <c r="DB17" s="103"/>
+      <c r="DC17" s="103"/>
+      <c r="DD17" s="103"/>
+      <c r="DE17" s="103"/>
+      <c r="DF17" s="103"/>
+      <c r="DG17" s="103"/>
+      <c r="DH17" s="103"/>
+      <c r="DI17" s="103"/>
+      <c r="DJ17" s="103"/>
+      <c r="DK17" s="103"/>
+      <c r="DL17" s="103"/>
+      <c r="DM17" s="103"/>
+      <c r="DN17" s="103"/>
+      <c r="DO17" s="103"/>
+      <c r="DP17" s="103"/>
+      <c r="DQ17" s="103"/>
+      <c r="DR17" s="103"/>
+      <c r="DS17" s="103"/>
+      <c r="DT17" s="103"/>
+      <c r="DU17" s="103"/>
+      <c r="DV17" s="103"/>
+      <c r="DW17" s="103"/>
+      <c r="DX17" s="103"/>
+      <c r="DY17" s="103"/>
+      <c r="DZ17" s="103"/>
+      <c r="EA17" s="103"/>
+      <c r="EB17" s="103"/>
+      <c r="EC17" s="103"/>
+      <c r="ED17" s="103"/>
+      <c r="EE17" s="103"/>
+      <c r="EF17" s="103"/>
+      <c r="EG17" s="103"/>
+      <c r="EH17" s="103"/>
+      <c r="EI17" s="103"/>
+      <c r="EJ17" s="103"/>
+      <c r="EK17" s="103"/>
+      <c r="EL17" s="103"/>
+      <c r="EM17" s="103"/>
+      <c r="EN17" s="103"/>
+      <c r="EO17" s="103"/>
+      <c r="EP17" s="103"/>
+      <c r="EQ17" s="103"/>
+      <c r="ER17" s="103"/>
+      <c r="ES17" s="103"/>
+      <c r="ET17" s="103"/>
+      <c r="EU17" s="103"/>
+      <c r="EV17" s="103"/>
+      <c r="EW17" s="103"/>
+      <c r="EX17" s="103"/>
+      <c r="EY17" s="103"/>
+      <c r="EZ17" s="103"/>
+      <c r="FA17" s="103"/>
+      <c r="FB17" s="103"/>
+      <c r="FC17" s="103"/>
+      <c r="FD17" s="103"/>
+      <c r="FE17" s="103"/>
+      <c r="FF17" s="103"/>
+      <c r="FG17" s="103"/>
+      <c r="FH17" s="103"/>
+      <c r="FI17" s="103"/>
+      <c r="FJ17" s="103"/>
+      <c r="FK17" s="103"/>
+      <c r="FL17" s="103"/>
+      <c r="FM17" s="103"/>
+      <c r="FN17" s="103"/>
+      <c r="FO17" s="103"/>
+      <c r="FP17" s="103"/>
+      <c r="FQ17" s="103"/>
+      <c r="FR17" s="103"/>
+      <c r="FS17" s="103"/>
+      <c r="FT17" s="103"/>
+      <c r="FU17" s="103"/>
+      <c r="FV17" s="103"/>
+      <c r="FW17" s="103"/>
+      <c r="FX17" s="103"/>
+      <c r="FY17" s="103"/>
+      <c r="FZ17" s="103"/>
+      <c r="GA17" s="103"/>
+      <c r="GB17" s="103"/>
+      <c r="GC17" s="103"/>
+      <c r="GD17" s="103"/>
+      <c r="GE17" s="103"/>
+      <c r="GF17" s="103"/>
+      <c r="GG17" s="103"/>
+      <c r="GH17" s="103"/>
+      <c r="GI17" s="103"/>
+      <c r="GJ17" s="103"/>
+      <c r="GK17" s="103"/>
+      <c r="GL17" s="103"/>
+      <c r="GM17" s="103"/>
+      <c r="GN17" s="103"/>
+      <c r="GO17" s="103"/>
+      <c r="GP17" s="103"/>
+      <c r="GQ17" s="103"/>
+      <c r="GR17" s="103"/>
+      <c r="GS17" s="103"/>
+      <c r="GT17" s="103"/>
+      <c r="GU17" s="103"/>
+      <c r="GV17" s="103"/>
+      <c r="GW17" s="103"/>
+      <c r="GX17" s="103"/>
+      <c r="GY17" s="103"/>
+      <c r="GZ17" s="103"/>
+      <c r="HA17" s="103"/>
+      <c r="HB17" s="103"/>
+      <c r="HC17" s="103"/>
+      <c r="HD17" s="103"/>
+      <c r="HE17" s="103"/>
+      <c r="HF17" s="103"/>
+      <c r="HG17" s="103"/>
+      <c r="HH17" s="103"/>
+      <c r="HI17" s="103"/>
+      <c r="HJ17" s="103"/>
+      <c r="HK17" s="103"/>
+      <c r="HL17" s="103"/>
+      <c r="HM17" s="103"/>
+      <c r="HN17" s="103"/>
+      <c r="HO17" s="103"/>
+      <c r="HP17" s="103"/>
+      <c r="HQ17" s="103"/>
+      <c r="HR17" s="103"/>
+      <c r="HS17" s="103"/>
+      <c r="HT17" s="103"/>
+      <c r="HU17" s="103"/>
+      <c r="HV17" s="103"/>
+      <c r="HW17" s="103"/>
+      <c r="HX17" s="103"/>
+      <c r="HY17" s="103"/>
+      <c r="HZ17" s="103"/>
+      <c r="IA17" s="103"/>
+      <c r="IB17" s="103"/>
+      <c r="IC17" s="103"/>
+      <c r="ID17" s="103"/>
+      <c r="IE17" s="103"/>
+      <c r="IF17" s="103"/>
+      <c r="IG17" s="103"/>
+      <c r="IH17" s="103"/>
+      <c r="II17" s="103"/>
+      <c r="IJ17" s="103"/>
+      <c r="IK17" s="103"/>
+      <c r="IL17" s="103"/>
+      <c r="IM17" s="103"/>
+      <c r="IN17" s="103"/>
+      <c r="IO17" s="103"/>
+      <c r="IP17" s="103"/>
+      <c r="IQ17" s="103"/>
+      <c r="IR17" s="103"/>
+      <c r="IS17" s="103"/>
+      <c r="IT17" s="103"/>
+      <c r="IU17" s="103"/>
+      <c r="IV17" s="103"/>
+      <c r="IW17" s="103"/>
+      <c r="IX17" s="103"/>
+      <c r="IY17" s="103"/>
+      <c r="IZ17" s="103"/>
+      <c r="JA17" s="103"/>
+      <c r="JB17" s="103"/>
+      <c r="JC17" s="103"/>
+      <c r="JD17" s="103"/>
+      <c r="JE17" s="103"/>
+      <c r="JF17" s="103"/>
+      <c r="JG17" s="103"/>
+      <c r="JH17" s="103"/>
+      <c r="JI17" s="103"/>
+      <c r="JJ17" s="103"/>
+      <c r="JK17" s="103"/>
+      <c r="JL17" s="103"/>
+      <c r="JM17" s="103"/>
+      <c r="JN17" s="103"/>
+      <c r="JO17" s="103"/>
+      <c r="JP17" s="103"/>
+      <c r="JQ17" s="103"/>
     </row>
-    <row r="18" spans="1:59" ht="33.6" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:277" ht="33.6" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A18" s="27"/>
       <c r="B18" s="28"/>
       <c r="C18" s="28"/>
       <c r="D18" s="28"/>
-      <c r="E18" s="117">
+      <c r="E18" s="78">
         <f t="shared" ref="E18:BG18" si="0">SUM(E3:E17)</f>
         <v>194</v>
       </c>
-      <c r="F18" s="86">
+      <c r="F18" s="69">
         <f t="shared" ref="F18:G18" si="1">SUM(F3:F17)</f>
         <v>696</v>
       </c>
-      <c r="G18" s="86">
+      <c r="G18" s="69">
         <f t="shared" si="1"/>
         <v>382</v>
       </c>
-      <c r="H18" s="86">
+      <c r="H18" s="69">
         <f>SUM(H3:H17)</f>
         <v>312</v>
       </c>
-      <c r="I18" s="86">
+      <c r="I18" s="69">
         <f t="shared" ref="I18:L18" si="2">SUM(I3:I17)</f>
         <v>151</v>
       </c>
-      <c r="J18" s="86">
+      <c r="J18" s="69">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="K18" s="86">
+      <c r="K18" s="69">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="L18" s="86">
+      <c r="L18" s="69">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="M18" s="86">
+      <c r="M18" s="69">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="N18" s="87">
+      <c r="N18" s="128">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
-      <c r="O18" s="87">
+      <c r="O18" s="128">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="P18" s="87">
+      <c r="P18" s="128">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="Q18" s="87">
+      <c r="Q18" s="128">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="R18" s="87">
+      <c r="R18" s="128">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="S18" s="87">
+      <c r="S18" s="128">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="T18" s="87">
+      <c r="T18" s="128">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="U18" s="87">
+      <c r="U18" s="128">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="V18" s="87">
+      <c r="V18" s="128">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="W18" s="87">
+      <c r="W18" s="128">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="X18" s="87">
+      <c r="X18" s="128">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="Y18" s="87">
+      <c r="Y18" s="128">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="Z18" s="87">
+      <c r="Z18" s="128">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="AA18" s="87">
+      <c r="AA18" s="128">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="AB18" s="87">
+      <c r="AB18" s="128">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="AC18" s="87">
+      <c r="AC18" s="128">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="AD18" s="88">
+      <c r="AD18" s="129">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="AE18" s="88">
+      <c r="AE18" s="129">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="AF18" s="88">
+      <c r="AF18" s="129">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="AG18" s="88">
+      <c r="AG18" s="129">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="AH18" s="88">
+      <c r="AH18" s="129">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="AI18" s="88">
+      <c r="AI18" s="129">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="AJ18" s="88">
+      <c r="AJ18" s="129">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="AK18" s="88">
+      <c r="AK18" s="129">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AL18" s="88">
+      <c r="AL18" s="129">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AM18" s="125">
+      <c r="AM18" s="130">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AN18" s="125">
+      <c r="AN18" s="130">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AO18" s="125">
+      <c r="AO18" s="130">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AP18" s="125">
+      <c r="AP18" s="130">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AQ18" s="125">
+      <c r="AQ18" s="130">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AR18" s="125">
+      <c r="AR18" s="130">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AS18" s="125">
+      <c r="AS18" s="130">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AT18" s="125">
+      <c r="AT18" s="130">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AU18" s="125">
+      <c r="AU18" s="130">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AV18" s="125">
+      <c r="AV18" s="130">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AW18" s="125">
+      <c r="AW18" s="130">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AX18" s="125">
+      <c r="AX18" s="130">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AY18" s="125">
+      <c r="AY18" s="130">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AZ18" s="125">
+      <c r="AZ18" s="130">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BA18" s="125">
+      <c r="BA18" s="130">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BB18" s="125">
+      <c r="BB18" s="130">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BC18" s="125">
+      <c r="BC18" s="130">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BD18" s="125">
+      <c r="BD18" s="130">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE18" s="125">
+      <c r="BE18" s="130">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BF18" s="125">
+      <c r="BF18" s="130">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BG18" s="125">
+      <c r="BG18" s="130">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:59" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="106" t="s">
+    <row r="19" spans="1:277" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="B19" s="107"/>
-      <c r="E19" s="131" t="s">
+      <c r="B19" s="92"/>
+      <c r="E19" s="112" t="s">
         <v>131</v>
       </c>
-      <c r="F19" s="134" t="s">
+      <c r="F19" s="107" t="s">
         <v>155</v>
       </c>
-      <c r="G19" s="134"/>
-      <c r="H19" s="134"/>
-      <c r="I19" s="134"/>
-      <c r="J19" s="134"/>
-      <c r="K19" s="134"/>
-      <c r="L19" s="134"/>
-      <c r="M19" s="134"/>
-      <c r="N19" s="132" t="s">
+      <c r="G19" s="107"/>
+      <c r="H19" s="107"/>
+      <c r="I19" s="107"/>
+      <c r="J19" s="107"/>
+      <c r="K19" s="107"/>
+      <c r="L19" s="107"/>
+      <c r="M19" s="107"/>
+      <c r="N19" s="124" t="s">
         <v>156</v>
       </c>
-      <c r="O19" s="132"/>
-      <c r="P19" s="132"/>
-      <c r="Q19" s="132"/>
-      <c r="R19" s="132"/>
-      <c r="S19" s="132"/>
-      <c r="T19" s="132"/>
-      <c r="U19" s="132"/>
-      <c r="V19" s="132"/>
-      <c r="W19" s="132"/>
-      <c r="X19" s="132"/>
-      <c r="Y19" s="132"/>
-      <c r="Z19" s="132"/>
-      <c r="AA19" s="132"/>
-      <c r="AB19" s="132"/>
-      <c r="AC19" s="132"/>
-      <c r="AD19" s="132"/>
-      <c r="AE19" s="132"/>
-      <c r="AF19" s="132"/>
-      <c r="AG19" s="132"/>
-      <c r="AH19" s="132"/>
-      <c r="AI19" s="132"/>
-      <c r="AJ19" s="132"/>
-      <c r="AK19" s="132"/>
-      <c r="AL19" s="132"/>
-      <c r="AM19" s="132"/>
-      <c r="AN19" s="132"/>
-      <c r="AO19" s="132"/>
-      <c r="AP19" s="132"/>
-      <c r="AQ19" s="132"/>
-      <c r="AR19" s="132"/>
-      <c r="AS19" s="132"/>
-      <c r="AT19" s="132"/>
-      <c r="AU19" s="132"/>
-      <c r="AV19" s="132"/>
-      <c r="AW19" s="132"/>
-      <c r="AX19" s="132"/>
-      <c r="AY19" s="132"/>
-      <c r="AZ19" s="132"/>
-      <c r="BA19" s="132"/>
-      <c r="BB19" s="132"/>
-      <c r="BC19" s="132"/>
-      <c r="BD19" s="132"/>
-      <c r="BE19" s="132"/>
-      <c r="BF19" s="132"/>
-      <c r="BG19" s="132"/>
+      <c r="O19" s="124"/>
+      <c r="P19" s="124"/>
+      <c r="Q19" s="124"/>
+      <c r="R19" s="124"/>
+      <c r="S19" s="124"/>
+      <c r="T19" s="124"/>
+      <c r="U19" s="124"/>
+      <c r="V19" s="124"/>
+      <c r="W19" s="124"/>
+      <c r="X19" s="124"/>
+      <c r="Y19" s="124"/>
+      <c r="Z19" s="124"/>
+      <c r="AA19" s="124"/>
+      <c r="AB19" s="124"/>
+      <c r="AC19" s="124"/>
+      <c r="AD19" s="124"/>
+      <c r="AE19" s="124"/>
+      <c r="AF19" s="124"/>
+      <c r="AG19" s="124"/>
+      <c r="AH19" s="124"/>
+      <c r="AI19" s="124"/>
+      <c r="AJ19" s="124"/>
+      <c r="AK19" s="124"/>
+      <c r="AL19" s="124"/>
+      <c r="AM19" s="124"/>
+      <c r="AN19" s="124"/>
+      <c r="AO19" s="124"/>
+      <c r="AP19" s="124"/>
+      <c r="AQ19" s="124"/>
+      <c r="AR19" s="124"/>
+      <c r="AS19" s="124"/>
+      <c r="AT19" s="124"/>
+      <c r="AU19" s="124"/>
+      <c r="AV19" s="124"/>
+      <c r="AW19" s="124"/>
+      <c r="AX19" s="124"/>
+      <c r="AY19" s="124"/>
+      <c r="AZ19" s="124"/>
+      <c r="BA19" s="124"/>
+      <c r="BB19" s="124"/>
+      <c r="BC19" s="124"/>
+      <c r="BD19" s="124"/>
+      <c r="BE19" s="124"/>
+      <c r="BF19" s="124"/>
+      <c r="BG19" s="124"/>
     </row>
-    <row r="20" spans="1:59" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="108"/>
-      <c r="B20" s="107"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="135"/>
-      <c r="G20" s="135"/>
-      <c r="H20" s="135"/>
-      <c r="I20" s="135"/>
-      <c r="J20" s="135"/>
-      <c r="K20" s="135"/>
-      <c r="L20" s="135"/>
-      <c r="M20" s="135"/>
-      <c r="N20" s="133"/>
-      <c r="O20" s="133"/>
-      <c r="P20" s="133"/>
-      <c r="Q20" s="133"/>
-      <c r="R20" s="133"/>
-      <c r="S20" s="133"/>
-      <c r="T20" s="133"/>
-      <c r="U20" s="133"/>
-      <c r="V20" s="133"/>
-      <c r="W20" s="133"/>
-      <c r="X20" s="133"/>
-      <c r="Y20" s="133"/>
-      <c r="Z20" s="133"/>
-      <c r="AA20" s="133"/>
-      <c r="AB20" s="133"/>
-      <c r="AC20" s="133"/>
-      <c r="AD20" s="133"/>
-      <c r="AE20" s="133"/>
-      <c r="AF20" s="133"/>
-      <c r="AG20" s="133"/>
-      <c r="AH20" s="133"/>
-      <c r="AI20" s="133"/>
-      <c r="AJ20" s="133"/>
-      <c r="AK20" s="133"/>
-      <c r="AL20" s="133"/>
-      <c r="AM20" s="133"/>
-      <c r="AN20" s="133"/>
-      <c r="AO20" s="133"/>
-      <c r="AP20" s="133"/>
-      <c r="AQ20" s="133"/>
-      <c r="AR20" s="133"/>
-      <c r="AS20" s="133"/>
-      <c r="AT20" s="133"/>
-      <c r="AU20" s="133"/>
-      <c r="AV20" s="133"/>
-      <c r="AW20" s="133"/>
-      <c r="AX20" s="133"/>
-      <c r="AY20" s="133"/>
-      <c r="AZ20" s="133"/>
-      <c r="BA20" s="133"/>
-      <c r="BB20" s="133"/>
-      <c r="BC20" s="133"/>
-      <c r="BD20" s="133"/>
-      <c r="BE20" s="133"/>
-      <c r="BF20" s="133"/>
-      <c r="BG20" s="133"/>
+    <row r="20" spans="1:277" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="93"/>
+      <c r="B20" s="92"/>
+      <c r="E20" s="113"/>
+      <c r="F20" s="108"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="108"/>
+      <c r="I20" s="108"/>
+      <c r="J20" s="108"/>
+      <c r="K20" s="108"/>
+      <c r="L20" s="108"/>
+      <c r="M20" s="108"/>
+      <c r="N20" s="125"/>
+      <c r="O20" s="125"/>
+      <c r="P20" s="125"/>
+      <c r="Q20" s="125"/>
+      <c r="R20" s="125"/>
+      <c r="S20" s="125"/>
+      <c r="T20" s="125"/>
+      <c r="U20" s="125"/>
+      <c r="V20" s="125"/>
+      <c r="W20" s="125"/>
+      <c r="X20" s="125"/>
+      <c r="Y20" s="125"/>
+      <c r="Z20" s="125"/>
+      <c r="AA20" s="125"/>
+      <c r="AB20" s="125"/>
+      <c r="AC20" s="125"/>
+      <c r="AD20" s="125"/>
+      <c r="AE20" s="125"/>
+      <c r="AF20" s="125"/>
+      <c r="AG20" s="125"/>
+      <c r="AH20" s="125"/>
+      <c r="AI20" s="125"/>
+      <c r="AJ20" s="125"/>
+      <c r="AK20" s="125"/>
+      <c r="AL20" s="125"/>
+      <c r="AM20" s="125"/>
+      <c r="AN20" s="125"/>
+      <c r="AO20" s="125"/>
+      <c r="AP20" s="125"/>
+      <c r="AQ20" s="125"/>
+      <c r="AR20" s="125"/>
+      <c r="AS20" s="125"/>
+      <c r="AT20" s="125"/>
+      <c r="AU20" s="125"/>
+      <c r="AV20" s="125"/>
+      <c r="AW20" s="125"/>
+      <c r="AX20" s="125"/>
+      <c r="AY20" s="125"/>
+      <c r="AZ20" s="125"/>
+      <c r="BA20" s="125"/>
+      <c r="BB20" s="125"/>
+      <c r="BC20" s="125"/>
+      <c r="BD20" s="125"/>
+      <c r="BE20" s="125"/>
+      <c r="BF20" s="125"/>
+      <c r="BG20" s="125"/>
     </row>
-    <row r="21" spans="1:59" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="102" t="s">
+    <row r="21" spans="1:277" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="87" t="s">
         <v>103</v>
       </c>
-      <c r="B21" s="103"/>
+      <c r="B21" s="88"/>
     </row>
-    <row r="22" spans="1:59" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="102"/>
-      <c r="B22" s="103"/>
+    <row r="22" spans="1:277" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="87"/>
+      <c r="B22" s="88"/>
     </row>
-    <row r="23" spans="1:59" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="AV23" s="126"/>
+    <row r="23" spans="1:277" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AV23" s="85"/>
     </row>
-    <row r="24" spans="1:59" ht="16.2" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:277" ht="16.2" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="A1:AS22">
     <sortCondition ref="O2:AN2"/>
@@ -4336,10 +6034,10 @@
     <mergeCell ref="A21:B22"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A19:B20"/>
-    <mergeCell ref="O1:BG1"/>
     <mergeCell ref="F1:M1"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="F19:M20"/>
+    <mergeCell ref="N1:BG1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A10 A12 A14:A17">
     <cfRule type="colorScale" priority="110">
@@ -4364,53 +6062,53 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E17">
-    <cfRule type="cellIs" dxfId="15" priority="25" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="25" operator="greaterThan">
       <formula>116.5</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F4">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="greaterThan">
+      <formula>160</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G4">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="greaterThan">
+      <formula>139</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H4">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
+      <formula>110</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I4">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+      <formula>35</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J4">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
+      <formula>20</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K4">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+      <formula>12</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M3:M4">
-    <cfRule type="cellIs" dxfId="14" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="21" operator="greaterThan">
       <formula>4.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3:O4">
-    <cfRule type="cellIs" dxfId="7" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="13" operator="greaterThan">
       <formula>24</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X3:X17">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="greaterThan">
       <formula>53</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F4">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="greaterThan">
-      <formula>160</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G4">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThan">
-      <formula>139</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H4">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
-      <formula>110</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I4">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
-      <formula>35</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J3:J4">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>20</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K4">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
-      <formula>12</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -4502,40 +6200,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
       <c r="E1" s="6"/>
       <c r="F1" s="7"/>
-      <c r="G1" s="113" t="s">
+      <c r="G1" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="114" t="s">
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
+      <c r="U1" s="99"/>
+      <c r="V1" s="99"/>
+      <c r="W1" s="99"/>
+      <c r="X1" s="99"/>
+      <c r="Y1" s="99"/>
+      <c r="Z1" s="99"/>
+      <c r="AA1" s="99"/>
+      <c r="AB1" s="99"/>
       <c r="AC1" s="8" t="s">
         <v>26</v>
       </c>
@@ -5584,12 +7282,12 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
-      <c r="H20" s="109" t="s">
+      <c r="H20" s="95" t="s">
         <v>93</v>
       </c>
-      <c r="I20" s="109"/>
-      <c r="J20" s="109"/>
-      <c r="K20" s="109"/>
+      <c r="I20" s="95"/>
+      <c r="J20" s="95"/>
+      <c r="K20" s="95"/>
       <c r="L20" s="21" t="s">
         <v>93</v>
       </c>
@@ -5602,40 +7300,40 @@
       <c r="Q20" s="21"/>
       <c r="R20" s="21"/>
       <c r="S20" s="21"/>
-      <c r="T20" s="109"/>
-      <c r="U20" s="109"/>
-      <c r="V20" s="109"/>
-      <c r="W20" s="109"/>
+      <c r="T20" s="95"/>
+      <c r="U20" s="95"/>
+      <c r="V20" s="95"/>
+      <c r="W20" s="95"/>
       <c r="X20" s="21" t="s">
         <v>93</v>
       </c>
       <c r="Y20" s="21"/>
       <c r="Z20" s="21"/>
       <c r="AA20" s="21"/>
-      <c r="AB20" s="109"/>
-      <c r="AC20" s="109"/>
-      <c r="AD20" s="109"/>
-      <c r="AE20" s="109"/>
+      <c r="AB20" s="95"/>
+      <c r="AC20" s="95"/>
+      <c r="AD20" s="95"/>
+      <c r="AE20" s="95"/>
       <c r="AF20" s="21" t="s">
         <v>93</v>
       </c>
       <c r="AG20" s="21"/>
       <c r="AH20" s="21"/>
       <c r="AI20" s="21"/>
-      <c r="AJ20" s="109"/>
-      <c r="AK20" s="109"/>
-      <c r="AL20" s="109"/>
-      <c r="AM20" s="109"/>
-      <c r="AN20" s="109"/>
-      <c r="AO20" s="109"/>
-      <c r="AP20" s="109"/>
-      <c r="AQ20" s="109"/>
+      <c r="AJ20" s="95"/>
+      <c r="AK20" s="95"/>
+      <c r="AL20" s="95"/>
+      <c r="AM20" s="95"/>
+      <c r="AN20" s="95"/>
+      <c r="AO20" s="95"/>
+      <c r="AP20" s="95"/>
+      <c r="AQ20" s="95"/>
     </row>
     <row r="21" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A21" s="115" t="s">
+      <c r="A21" s="100" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="116"/>
+      <c r="B21" s="101"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -5679,10 +7377,10 @@
       <c r="AQ21" s="7"/>
     </row>
     <row r="22" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A22" s="110" t="s">
+      <c r="A22" s="96" t="s">
         <v>90</v>
       </c>
-      <c r="B22" s="110"/>
+      <c r="B22" s="96"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -5726,8 +7424,8 @@
       <c r="AQ22" s="7"/>
     </row>
     <row r="23" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A23" s="110"/>
-      <c r="B23" s="110"/>
+      <c r="A23" s="96"/>
+      <c r="B23" s="96"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
